--- a/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Service/SearchResultService_クラス仕様書.xlsx
+++ b/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Service/SearchResultService_クラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308A9849-E32E-4A66-A211-96A96E5FC2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C4E258-59CD-4E39-A792-5FB10CEE500D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="204" yWindow="2244" windowWidth="20052" windowHeight="10224" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3576" yWindow="852" windowWidth="17244" windowHeight="8868" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空文字またはnull</t>
+    <t>空文字</t>
     <rPh sb="0" eb="3">
       <t>カラモジ</t>
     </rPh>
@@ -2374,15 +2374,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2430,6 +2421,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2489,8 +2489,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3990976" y="11154244"/>
-          <a:ext cx="4981574" cy="2553900"/>
+          <a:off x="3912291" y="11248252"/>
+          <a:ext cx="4882514" cy="2575434"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2502,22 +2502,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>30481</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>58986</xdr:rowOff>
+      <xdr:colOff>13252</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>184795</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
+      <xdr:colOff>152599</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>105286</xdr:rowOff>
+      <xdr:rowOff>112643</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DDBF4F4-22CA-4EBE-B239-A4113247923F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D60AAF4B-BBEB-4BDB-A3EB-403F5CAAFE23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2533,8 +2533,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3939541" y="8852466"/>
-          <a:ext cx="4808219" cy="2334205"/>
+          <a:off x="3916017" y="8858343"/>
+          <a:ext cx="4863747" cy="2425883"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21996,7 +21996,7 @@
       <c r="P77" s="16"/>
       <c r="Q77" s="16"/>
       <c r="R77" s="26"/>
-      <c r="S77" s="22"/>
+      <c r="S77" s="49"/>
       <c r="T77" s="22"/>
       <c r="U77" s="22"/>
       <c r="V77" s="16"/>
@@ -22005,6 +22005,22 @@
       <c r="Y77" s="16"/>
       <c r="Z77" s="16"/>
       <c r="AA77" s="16"/>
+      <c r="AB77" s="22"/>
+      <c r="AC77" s="22"/>
+      <c r="AD77" s="22"/>
+      <c r="AE77" s="22"/>
+      <c r="AF77" s="22"/>
+      <c r="AG77" s="22"/>
+      <c r="AH77" s="22"/>
+      <c r="AI77" s="22"/>
+      <c r="AJ77" s="22"/>
+      <c r="AK77" s="22"/>
+      <c r="AL77" s="22"/>
+      <c r="AM77" s="22"/>
+      <c r="AN77" s="22"/>
+      <c r="AO77" s="22"/>
+      <c r="AP77" s="22"/>
+      <c r="AQ77" s="22"/>
       <c r="AR77" s="16"/>
       <c r="AS77" s="19"/>
       <c r="AT77" s="8"/>
@@ -22020,22 +22036,26 @@
       <c r="S78" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB78" s="16"/>
-      <c r="AC78" s="16"/>
-      <c r="AD78" s="16"/>
-      <c r="AE78" s="16"/>
-      <c r="AF78" s="16"/>
-      <c r="AG78" s="16"/>
-      <c r="AH78" s="16"/>
-      <c r="AI78" s="16"/>
-      <c r="AJ78" s="16"/>
-      <c r="AK78" s="16"/>
-      <c r="AL78" s="16"/>
-      <c r="AM78" s="16"/>
-      <c r="AN78" s="16"/>
-      <c r="AO78" s="16"/>
-      <c r="AP78" s="16"/>
-      <c r="AQ78" s="16"/>
+      <c r="X78" s="33"/>
+      <c r="Y78" s="33"/>
+      <c r="Z78" s="33"/>
+      <c r="AA78" s="33"/>
+      <c r="AB78" s="20"/>
+      <c r="AC78" s="20"/>
+      <c r="AD78" s="20"/>
+      <c r="AE78" s="20"/>
+      <c r="AF78" s="20"/>
+      <c r="AG78" s="20"/>
+      <c r="AH78" s="20"/>
+      <c r="AI78" s="20"/>
+      <c r="AJ78" s="20"/>
+      <c r="AK78" s="20"/>
+      <c r="AL78" s="20"/>
+      <c r="AM78" s="20"/>
+      <c r="AN78" s="20"/>
+      <c r="AO78" s="20"/>
+      <c r="AP78" s="20"/>
+      <c r="AQ78" s="20"/>
       <c r="AT78" s="8"/>
     </row>
     <row r="79" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22069,6 +22089,7 @@
       <c r="S81" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="AP81" s="33"/>
       <c r="AT81" s="8"/>
     </row>
     <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22302,19 +22323,19 @@
       <c r="R10" s="99"/>
     </row>
     <row r="11" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="126" t="s">
+      <c r="E11" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="128"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="144"/>
       <c r="P11" s="99"/>
       <c r="Q11" s="99"/>
       <c r="R11" s="99"/>
@@ -22357,7 +22378,7 @@
       <c r="P12" s="99"/>
       <c r="Q12" s="99"/>
       <c r="R12" s="99"/>
-      <c r="T12" s="129" t="s">
+      <c r="T12" s="126" t="s">
         <v>100</v>
       </c>
       <c r="U12" s="85" t="s">
@@ -22369,10 +22390,10 @@
       <c r="Y12" s="88"/>
     </row>
     <row r="13" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="129" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="135" t="s">
+      <c r="C13" s="132" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="66" t="s">
@@ -22414,7 +22435,7 @@
       <c r="P13" s="99"/>
       <c r="Q13" s="99"/>
       <c r="R13" s="99"/>
-      <c r="T13" s="130"/>
+      <c r="T13" s="127"/>
       <c r="U13" s="89"/>
       <c r="V13" s="57" t="s">
         <v>75</v>
@@ -22424,8 +22445,8 @@
       <c r="Y13" s="90"/>
     </row>
     <row r="14" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="133"/>
-      <c r="C14" s="136"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="67" t="s">
         <v>98</v>
       </c>
@@ -22465,7 +22486,7 @@
       <c r="P14" s="99"/>
       <c r="Q14" s="99"/>
       <c r="R14" s="99"/>
-      <c r="T14" s="130" t="s">
+      <c r="T14" s="127" t="s">
         <v>101</v>
       </c>
       <c r="U14" s="91" t="s">
@@ -22477,8 +22498,8 @@
       <c r="Y14" s="92"/>
     </row>
     <row r="15" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="133"/>
-      <c r="C15" s="137" t="s">
+      <c r="B15" s="130"/>
+      <c r="C15" s="134" t="s">
         <v>132</v>
       </c>
       <c r="D15" s="67" t="s">
@@ -22519,7 +22540,7 @@
       </c>
       <c r="P15" s="99"/>
       <c r="R15" s="99"/>
-      <c r="T15" s="130"/>
+      <c r="T15" s="127"/>
       <c r="U15" s="93"/>
       <c r="V15" s="20" t="s">
         <v>127</v>
@@ -22529,8 +22550,8 @@
       <c r="Y15" s="94"/>
     </row>
     <row r="16" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="133"/>
-      <c r="C16" s="135"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="132"/>
       <c r="D16" s="67" t="s">
         <v>136</v>
       </c>
@@ -22569,7 +22590,7 @@
       </c>
       <c r="P16" s="99"/>
       <c r="R16" s="99"/>
-      <c r="T16" s="130"/>
+      <c r="T16" s="127"/>
       <c r="U16" s="95"/>
       <c r="V16" s="57" t="s">
         <v>75</v>
@@ -22579,8 +22600,8 @@
       <c r="Y16" s="90"/>
     </row>
     <row r="17" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="134"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="135"/>
       <c r="D17" s="102" t="s">
         <v>137</v>
       </c>
@@ -22617,7 +22638,7 @@
       <c r="O17" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="T17" s="130" t="s">
+      <c r="T17" s="127" t="s">
         <v>102</v>
       </c>
       <c r="U17" s="91" t="s">
@@ -22629,10 +22650,10 @@
       <c r="Y17" s="92"/>
     </row>
     <row r="18" spans="2:25" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="139" t="s">
+      <c r="B18" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="140"/>
+      <c r="C18" s="137"/>
       <c r="D18" s="69" t="s">
         <v>100</v>
       </c>
@@ -22651,7 +22672,7 @@
       <c r="O18" s="80"/>
       <c r="P18" s="99"/>
       <c r="R18" s="99"/>
-      <c r="T18" s="130"/>
+      <c r="T18" s="127"/>
       <c r="U18" s="93"/>
       <c r="V18" s="20" t="s">
         <v>94</v>
@@ -22661,8 +22682,8 @@
       <c r="Y18" s="94"/>
     </row>
     <row r="19" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="141"/>
-      <c r="C19" s="142"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="139"/>
       <c r="D19" s="68" t="s">
         <v>101</v>
       </c>
@@ -22683,7 +22704,7 @@
       <c r="O19" s="75"/>
       <c r="P19" s="99"/>
       <c r="R19" s="99"/>
-      <c r="T19" s="130"/>
+      <c r="T19" s="127"/>
       <c r="U19" s="95"/>
       <c r="V19" s="57" t="s">
         <v>75</v>
@@ -22693,8 +22714,8 @@
       <c r="Y19" s="90"/>
     </row>
     <row r="20" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="141"/>
-      <c r="C20" s="142"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="139"/>
       <c r="D20" s="68" t="s">
         <v>102</v>
       </c>
@@ -22714,7 +22735,7 @@
       <c r="P20" s="99"/>
       <c r="Q20" s="99"/>
       <c r="R20" s="99"/>
-      <c r="T20" s="130" t="s">
+      <c r="T20" s="127" t="s">
         <v>103</v>
       </c>
       <c r="U20" s="91" t="s">
@@ -22726,8 +22747,8 @@
       <c r="Y20" s="92"/>
     </row>
     <row r="21" spans="2:25" ht="15" x14ac:dyDescent="0.3">
-      <c r="B21" s="141"/>
-      <c r="C21" s="142"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="139"/>
       <c r="D21" s="68" t="s">
         <v>103</v>
       </c>
@@ -22749,7 +22770,7 @@
       <c r="P21" s="99"/>
       <c r="Q21" s="99"/>
       <c r="R21" s="99"/>
-      <c r="T21" s="130"/>
+      <c r="T21" s="127"/>
       <c r="U21" s="93"/>
       <c r="V21" s="20" t="s">
         <v>125</v>
@@ -22759,8 +22780,8 @@
       <c r="Y21" s="94"/>
     </row>
     <row r="22" spans="2:25" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="143"/>
-      <c r="C22" s="144"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
       <c r="D22" s="70" t="s">
         <v>109</v>
       </c>
@@ -22788,7 +22809,7 @@
       <c r="P22" s="99"/>
       <c r="Q22" s="99"/>
       <c r="R22" s="99"/>
-      <c r="T22" s="131"/>
+      <c r="T22" s="128"/>
       <c r="U22" s="96"/>
       <c r="V22" s="97" t="s">
         <v>75</v>
@@ -22805,15 +22826,15 @@
     <row r="26" spans="2:25" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="B18:C22"/>
     <mergeCell ref="E11:O11"/>
     <mergeCell ref="T12:T13"/>
     <mergeCell ref="T14:T16"/>
     <mergeCell ref="T17:T19"/>
     <mergeCell ref="T20:T22"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="B18:C22"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22821,15 +22842,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -22961,21 +22973,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22993,11 +23006,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Service/SearchResultService_クラス仕様書.xlsx
+++ b/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Service/SearchResultService_クラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C4E258-59CD-4E39-A792-5FB10CEE500D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E1CFD9-8F5F-4257-A5D7-20DB4EEBB6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3576" yWindow="852" windowWidth="17244" windowHeight="8868" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（itemSearch）'!$A$1:$BI$86</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（itemSearch）'!$A$1:$BI$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="148">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -376,10 +376,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>findForItems</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>findList</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -613,13 +609,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>5.1 変数宣言[findForItems]</t>
-    <rPh sb="4" eb="8">
-      <t>ヘンスウセンゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>5.2 変数宣言[findList]</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -834,13 +823,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4.1 変数宣言[items]</t>
-    <rPh sb="4" eb="8">
-      <t>ヘンスウセンゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>入力値を</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -926,19 +908,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4.3 変数itemsのsetItemNameメソッド呼出</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>引数：itemName</t>
     <rPh sb="0" eb="2">
       <t>ヒキスウ</t>
@@ -1002,7 +971,88 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4.2 変数items内のCategoriesDTOインスタンスのsetCategoryIdメソッド呼出</t>
+    <t>空文字</t>
+    <rPh sb="0" eb="3">
+      <t>カラモジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>5.1 変数宣言[findForDao]</t>
+    <rPh sb="4" eb="8">
+      <t>ヘンスウセンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>findForDao</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cates</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CategoriesDTO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ItemsDTOのインスタンスを持つ変数</t>
+    <rPh sb="16" eb="17">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ItemsDTO型の変数に引数に格納するインスタンス用の変数</t>
+    <rPh sb="8" eb="9">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.3変数items内のsetCategoryメソッドの呼び出し</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数：cates</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.4 変数items内のCategoriesDTOインスタンスのsetCategoryIdメソッド呼出</t>
     <rPh sb="4" eb="6">
       <t>ヘンスウ</t>
     </rPh>
@@ -1018,11 +1068,31 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空文字</t>
-    <rPh sb="0" eb="3">
-      <t>カラモジ</t>
+    <t>4.5 変数itemsのsetItemNameメソッド呼出</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <rPh sb="27" eb="28">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1 変数宣言[items]</t>
+    <rPh sb="4" eb="8">
+      <t>ヘンスウセンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.2 変数宣言[cates]</t>
+    <rPh sb="4" eb="8">
+      <t>ヘンスウセンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1032,7 +1102,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1063,6 +1133,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1995,7 +2073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2305,6 +2383,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2329,6 +2410,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2337,9 +2421,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2352,9 +2433,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2372,6 +2450,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2422,15 +2512,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -2459,13 +2540,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>76669</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>154069</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2503,13 +2584,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>13252</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>184795</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>152599</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>112643</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2874,85 +2955,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="103" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="104" t="s">
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
-      <c r="W1" s="104"/>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="103" t="s">
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="104" t="s">
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="104"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="104"/>
-      <c r="AN1" s="104"/>
-      <c r="AO1" s="104"/>
-      <c r="AP1" s="104"/>
-      <c r="AQ1" s="103" t="s">
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="103"/>
-      <c r="AS1" s="103"/>
-      <c r="AT1" s="104" t="s">
+      <c r="AR1" s="104"/>
+      <c r="AS1" s="104"/>
+      <c r="AT1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="AU1" s="104"/>
-      <c r="AV1" s="104"/>
-      <c r="AW1" s="104"/>
-      <c r="AX1" s="104"/>
-      <c r="AY1" s="104"/>
-      <c r="AZ1" s="104"/>
-      <c r="BA1" s="103" t="s">
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="103"/>
-      <c r="BC1" s="103"/>
-      <c r="BD1" s="105">
+      <c r="BB1" s="104"/>
+      <c r="BC1" s="104"/>
+      <c r="BD1" s="106">
         <v>45560</v>
       </c>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="105"/>
-      <c r="BI1" s="105"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3152,77 +3233,77 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="103" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="109"/>
-      <c r="V2" s="109"/>
-      <c r="W2" s="109"/>
-      <c r="X2" s="109"/>
-      <c r="Y2" s="109"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="109"/>
-      <c r="AB2" s="103" t="s">
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="103"/>
-      <c r="AE2" s="104" t="s">
+      <c r="AC2" s="104"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="104"/>
-      <c r="AG2" s="104"/>
-      <c r="AH2" s="104"/>
-      <c r="AI2" s="104"/>
-      <c r="AJ2" s="104"/>
-      <c r="AK2" s="104"/>
-      <c r="AL2" s="104"/>
-      <c r="AM2" s="104"/>
-      <c r="AN2" s="104"/>
-      <c r="AO2" s="104"/>
-      <c r="AP2" s="104"/>
-      <c r="AQ2" s="103" t="s">
+      <c r="AF2" s="105"/>
+      <c r="AG2" s="105"/>
+      <c r="AH2" s="105"/>
+      <c r="AI2" s="105"/>
+      <c r="AJ2" s="105"/>
+      <c r="AK2" s="105"/>
+      <c r="AL2" s="105"/>
+      <c r="AM2" s="105"/>
+      <c r="AN2" s="105"/>
+      <c r="AO2" s="105"/>
+      <c r="AP2" s="105"/>
+      <c r="AQ2" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="103"/>
-      <c r="AS2" s="103"/>
-      <c r="AT2" s="104"/>
-      <c r="AU2" s="104"/>
-      <c r="AV2" s="104"/>
-      <c r="AW2" s="104"/>
-      <c r="AX2" s="104"/>
-      <c r="AY2" s="104"/>
-      <c r="AZ2" s="104"/>
-      <c r="BA2" s="103" t="s">
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="104"/>
+      <c r="AT2" s="105"/>
+      <c r="AU2" s="105"/>
+      <c r="AV2" s="105"/>
+      <c r="AW2" s="105"/>
+      <c r="AX2" s="105"/>
+      <c r="AY2" s="105"/>
+      <c r="AZ2" s="105"/>
+      <c r="BA2" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="103"/>
-      <c r="BC2" s="103"/>
-      <c r="BD2" s="105"/>
-      <c r="BE2" s="105"/>
-      <c r="BF2" s="105"/>
-      <c r="BG2" s="105"/>
-      <c r="BH2" s="105"/>
-      <c r="BI2" s="105"/>
+      <c r="BB2" s="104"/>
+      <c r="BC2" s="104"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3485,916 +3566,916 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="106" t="s">
+      <c r="A4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="107"/>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
-      <c r="AB4" s="107"/>
-      <c r="AC4" s="107"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
-      <c r="AQ4" s="107"/>
-      <c r="AR4" s="107"/>
-      <c r="AS4" s="107"/>
-      <c r="AT4" s="107"/>
-      <c r="AU4" s="107"/>
-      <c r="AV4" s="107"/>
-      <c r="AW4" s="107"/>
-      <c r="AX4" s="107"/>
-      <c r="AY4" s="107"/>
-      <c r="AZ4" s="107"/>
-      <c r="BA4" s="107"/>
-      <c r="BB4" s="107"/>
-      <c r="BC4" s="107"/>
-      <c r="BD4" s="107"/>
-      <c r="BE4" s="107"/>
-      <c r="BF4" s="107"/>
-      <c r="BG4" s="107"/>
-      <c r="BH4" s="107"/>
-      <c r="BI4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
+      <c r="X4" s="108"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="108"/>
+      <c r="AA4" s="108"/>
+      <c r="AB4" s="108"/>
+      <c r="AC4" s="108"/>
+      <c r="AD4" s="108"/>
+      <c r="AE4" s="108"/>
+      <c r="AF4" s="108"/>
+      <c r="AG4" s="108"/>
+      <c r="AH4" s="108"/>
+      <c r="AI4" s="108"/>
+      <c r="AJ4" s="108"/>
+      <c r="AK4" s="108"/>
+      <c r="AL4" s="108"/>
+      <c r="AM4" s="108"/>
+      <c r="AN4" s="108"/>
+      <c r="AO4" s="108"/>
+      <c r="AP4" s="108"/>
+      <c r="AQ4" s="108"/>
+      <c r="AR4" s="108"/>
+      <c r="AS4" s="108"/>
+      <c r="AT4" s="108"/>
+      <c r="AU4" s="108"/>
+      <c r="AV4" s="108"/>
+      <c r="AW4" s="108"/>
+      <c r="AX4" s="108"/>
+      <c r="AY4" s="108"/>
+      <c r="AZ4" s="108"/>
+      <c r="BA4" s="108"/>
+      <c r="BB4" s="108"/>
+      <c r="BC4" s="108"/>
+      <c r="BD4" s="108"/>
+      <c r="BE4" s="108"/>
+      <c r="BF4" s="108"/>
+      <c r="BG4" s="108"/>
+      <c r="BH4" s="108"/>
+      <c r="BI4" s="108"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="107" t="s">
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="107"/>
-      <c r="V5" s="107"/>
-      <c r="W5" s="107"/>
-      <c r="X5" s="107"/>
-      <c r="Y5" s="107"/>
-      <c r="Z5" s="107"/>
-      <c r="AA5" s="107"/>
-      <c r="AB5" s="107"/>
-      <c r="AC5" s="107"/>
-      <c r="AD5" s="107"/>
-      <c r="AE5" s="107"/>
-      <c r="AF5" s="107"/>
-      <c r="AG5" s="107"/>
-      <c r="AH5" s="107"/>
-      <c r="AI5" s="107"/>
-      <c r="AJ5" s="107"/>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="107"/>
-      <c r="AM5" s="107"/>
-      <c r="AN5" s="107"/>
-      <c r="AO5" s="107"/>
-      <c r="AP5" s="107"/>
-      <c r="AQ5" s="107"/>
-      <c r="AR5" s="107"/>
-      <c r="AS5" s="107"/>
-      <c r="AT5" s="107"/>
-      <c r="AU5" s="107"/>
-      <c r="AV5" s="107"/>
-      <c r="AW5" s="107"/>
-      <c r="AX5" s="107"/>
-      <c r="AY5" s="107"/>
-      <c r="AZ5" s="107"/>
-      <c r="BA5" s="107"/>
-      <c r="BB5" s="107"/>
-      <c r="BC5" s="107"/>
-      <c r="BD5" s="107"/>
-      <c r="BE5" s="107"/>
-      <c r="BF5" s="107"/>
-      <c r="BG5" s="107"/>
-      <c r="BH5" s="107"/>
-      <c r="BI5" s="107"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="108"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="108"/>
+      <c r="AF5" s="108"/>
+      <c r="AG5" s="108"/>
+      <c r="AH5" s="108"/>
+      <c r="AI5" s="108"/>
+      <c r="AJ5" s="108"/>
+      <c r="AK5" s="108"/>
+      <c r="AL5" s="108"/>
+      <c r="AM5" s="108"/>
+      <c r="AN5" s="108"/>
+      <c r="AO5" s="108"/>
+      <c r="AP5" s="108"/>
+      <c r="AQ5" s="108"/>
+      <c r="AR5" s="108"/>
+      <c r="AS5" s="108"/>
+      <c r="AT5" s="108"/>
+      <c r="AU5" s="108"/>
+      <c r="AV5" s="108"/>
+      <c r="AW5" s="108"/>
+      <c r="AX5" s="108"/>
+      <c r="AY5" s="108"/>
+      <c r="AZ5" s="108"/>
+      <c r="BA5" s="108"/>
+      <c r="BB5" s="108"/>
+      <c r="BC5" s="108"/>
+      <c r="BD5" s="108"/>
+      <c r="BE5" s="108"/>
+      <c r="BF5" s="108"/>
+      <c r="BG5" s="108"/>
+      <c r="BH5" s="108"/>
+      <c r="BI5" s="108"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="107" t="s">
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="107"/>
-      <c r="P6" s="107"/>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="107"/>
-      <c r="S6" s="107"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="107"/>
-      <c r="V6" s="107"/>
-      <c r="W6" s="107"/>
-      <c r="X6" s="107"/>
-      <c r="Y6" s="107"/>
-      <c r="Z6" s="107"/>
-      <c r="AA6" s="107"/>
-      <c r="AB6" s="107"/>
-      <c r="AC6" s="107"/>
-      <c r="AD6" s="106" t="s">
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="108"/>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="AE6" s="106"/>
-      <c r="AF6" s="106"/>
-      <c r="AG6" s="106"/>
-      <c r="AH6" s="106"/>
-      <c r="AI6" s="106"/>
-      <c r="AJ6" s="107" t="s">
+      <c r="AE6" s="107"/>
+      <c r="AF6" s="107"/>
+      <c r="AG6" s="107"/>
+      <c r="AH6" s="107"/>
+      <c r="AI6" s="107"/>
+      <c r="AJ6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="AK6" s="107"/>
-      <c r="AL6" s="107"/>
-      <c r="AM6" s="107"/>
-      <c r="AN6" s="107"/>
-      <c r="AO6" s="107"/>
-      <c r="AP6" s="107"/>
-      <c r="AQ6" s="107"/>
-      <c r="AR6" s="107"/>
-      <c r="AS6" s="107"/>
-      <c r="AT6" s="107"/>
-      <c r="AU6" s="107"/>
-      <c r="AV6" s="107"/>
-      <c r="AW6" s="107"/>
-      <c r="AX6" s="107"/>
-      <c r="AY6" s="107"/>
-      <c r="AZ6" s="107"/>
-      <c r="BA6" s="107"/>
-      <c r="BB6" s="107"/>
-      <c r="BC6" s="107"/>
-      <c r="BD6" s="107"/>
-      <c r="BE6" s="107"/>
-      <c r="BF6" s="107"/>
-      <c r="BG6" s="107"/>
-      <c r="BH6" s="107"/>
-      <c r="BI6" s="107"/>
+      <c r="AK6" s="108"/>
+      <c r="AL6" s="108"/>
+      <c r="AM6" s="108"/>
+      <c r="AN6" s="108"/>
+      <c r="AO6" s="108"/>
+      <c r="AP6" s="108"/>
+      <c r="AQ6" s="108"/>
+      <c r="AR6" s="108"/>
+      <c r="AS6" s="108"/>
+      <c r="AT6" s="108"/>
+      <c r="AU6" s="108"/>
+      <c r="AV6" s="108"/>
+      <c r="AW6" s="108"/>
+      <c r="AX6" s="108"/>
+      <c r="AY6" s="108"/>
+      <c r="AZ6" s="108"/>
+      <c r="BA6" s="108"/>
+      <c r="BB6" s="108"/>
+      <c r="BC6" s="108"/>
+      <c r="BD6" s="108"/>
+      <c r="BE6" s="108"/>
+      <c r="BF6" s="108"/>
+      <c r="BG6" s="108"/>
+      <c r="BH6" s="108"/>
+      <c r="BI6" s="108"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="106" t="s">
+      <c r="A8" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106" t="s">
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="106"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="106"/>
-      <c r="O8" s="106"/>
-      <c r="P8" s="106"/>
-      <c r="Q8" s="106"/>
-      <c r="R8" s="106"/>
-      <c r="S8" s="106"/>
-      <c r="T8" s="106"/>
-      <c r="U8" s="106" t="s">
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="V8" s="106"/>
-      <c r="W8" s="106"/>
-      <c r="X8" s="106"/>
-      <c r="Y8" s="106"/>
-      <c r="Z8" s="106"/>
-      <c r="AA8" s="106"/>
-      <c r="AB8" s="106"/>
-      <c r="AC8" s="106"/>
-      <c r="AD8" s="106"/>
-      <c r="AE8" s="106" t="s">
+      <c r="V8" s="107"/>
+      <c r="W8" s="107"/>
+      <c r="X8" s="107"/>
+      <c r="Y8" s="107"/>
+      <c r="Z8" s="107"/>
+      <c r="AA8" s="107"/>
+      <c r="AB8" s="107"/>
+      <c r="AC8" s="107"/>
+      <c r="AD8" s="107"/>
+      <c r="AE8" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="AF8" s="106"/>
-      <c r="AG8" s="106"/>
-      <c r="AH8" s="106"/>
-      <c r="AI8" s="106"/>
-      <c r="AJ8" s="106"/>
-      <c r="AK8" s="106"/>
-      <c r="AL8" s="106"/>
-      <c r="AM8" s="106"/>
-      <c r="AN8" s="106"/>
-      <c r="AO8" s="106" t="s">
+      <c r="AF8" s="107"/>
+      <c r="AG8" s="107"/>
+      <c r="AH8" s="107"/>
+      <c r="AI8" s="107"/>
+      <c r="AJ8" s="107"/>
+      <c r="AK8" s="107"/>
+      <c r="AL8" s="107"/>
+      <c r="AM8" s="107"/>
+      <c r="AN8" s="107"/>
+      <c r="AO8" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="AP8" s="106"/>
-      <c r="AQ8" s="106"/>
-      <c r="AR8" s="106"/>
-      <c r="AS8" s="106"/>
-      <c r="AT8" s="106"/>
-      <c r="AU8" s="106"/>
-      <c r="AV8" s="106"/>
-      <c r="AW8" s="106"/>
-      <c r="AX8" s="106"/>
-      <c r="AY8" s="106"/>
-      <c r="AZ8" s="106"/>
-      <c r="BA8" s="106"/>
-      <c r="BB8" s="106"/>
-      <c r="BC8" s="106"/>
-      <c r="BD8" s="106"/>
-      <c r="BE8" s="106"/>
-      <c r="BF8" s="106"/>
-      <c r="BG8" s="106"/>
-      <c r="BH8" s="106"/>
-      <c r="BI8" s="106"/>
+      <c r="AP8" s="107"/>
+      <c r="AQ8" s="107"/>
+      <c r="AR8" s="107"/>
+      <c r="AS8" s="107"/>
+      <c r="AT8" s="107"/>
+      <c r="AU8" s="107"/>
+      <c r="AV8" s="107"/>
+      <c r="AW8" s="107"/>
+      <c r="AX8" s="107"/>
+      <c r="AY8" s="107"/>
+      <c r="AZ8" s="107"/>
+      <c r="BA8" s="107"/>
+      <c r="BB8" s="107"/>
+      <c r="BC8" s="107"/>
+      <c r="BD8" s="107"/>
+      <c r="BE8" s="107"/>
+      <c r="BF8" s="107"/>
+      <c r="BG8" s="107"/>
+      <c r="BH8" s="107"/>
+      <c r="BI8" s="107"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="110"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="110"/>
-      <c r="T9" s="110"/>
-      <c r="U9" s="110"/>
-      <c r="V9" s="110"/>
-      <c r="W9" s="110"/>
-      <c r="X9" s="110"/>
-      <c r="Y9" s="110"/>
-      <c r="Z9" s="110"/>
-      <c r="AA9" s="110"/>
-      <c r="AB9" s="110"/>
-      <c r="AC9" s="110"/>
-      <c r="AD9" s="110"/>
-      <c r="AE9" s="110"/>
-      <c r="AF9" s="110"/>
-      <c r="AG9" s="110"/>
-      <c r="AH9" s="110"/>
-      <c r="AI9" s="110"/>
-      <c r="AJ9" s="110"/>
-      <c r="AK9" s="110"/>
-      <c r="AL9" s="110"/>
-      <c r="AM9" s="110"/>
-      <c r="AN9" s="110"/>
-      <c r="AO9" s="110"/>
-      <c r="AP9" s="110"/>
-      <c r="AQ9" s="110"/>
-      <c r="AR9" s="110"/>
-      <c r="AS9" s="110"/>
-      <c r="AT9" s="110"/>
-      <c r="AU9" s="110"/>
-      <c r="AV9" s="110"/>
-      <c r="AW9" s="110"/>
-      <c r="AX9" s="110"/>
-      <c r="AY9" s="110"/>
-      <c r="AZ9" s="110"/>
-      <c r="BA9" s="110"/>
-      <c r="BB9" s="110"/>
-      <c r="BC9" s="110"/>
-      <c r="BD9" s="110"/>
-      <c r="BE9" s="110"/>
-      <c r="BF9" s="110"/>
-      <c r="BG9" s="110"/>
-      <c r="BH9" s="110"/>
-      <c r="BI9" s="110"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="111"/>
+      <c r="S9" s="111"/>
+      <c r="T9" s="111"/>
+      <c r="U9" s="111"/>
+      <c r="V9" s="111"/>
+      <c r="W9" s="111"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="111"/>
+      <c r="Z9" s="111"/>
+      <c r="AA9" s="111"/>
+      <c r="AB9" s="111"/>
+      <c r="AC9" s="111"/>
+      <c r="AD9" s="111"/>
+      <c r="AE9" s="111"/>
+      <c r="AF9" s="111"/>
+      <c r="AG9" s="111"/>
+      <c r="AH9" s="111"/>
+      <c r="AI9" s="111"/>
+      <c r="AJ9" s="111"/>
+      <c r="AK9" s="111"/>
+      <c r="AL9" s="111"/>
+      <c r="AM9" s="111"/>
+      <c r="AN9" s="111"/>
+      <c r="AO9" s="111"/>
+      <c r="AP9" s="111"/>
+      <c r="AQ9" s="111"/>
+      <c r="AR9" s="111"/>
+      <c r="AS9" s="111"/>
+      <c r="AT9" s="111"/>
+      <c r="AU9" s="111"/>
+      <c r="AV9" s="111"/>
+      <c r="AW9" s="111"/>
+      <c r="AX9" s="111"/>
+      <c r="AY9" s="111"/>
+      <c r="AZ9" s="111"/>
+      <c r="BA9" s="111"/>
+      <c r="BB9" s="111"/>
+      <c r="BC9" s="111"/>
+      <c r="BD9" s="111"/>
+      <c r="BE9" s="111"/>
+      <c r="BF9" s="111"/>
+      <c r="BG9" s="111"/>
+      <c r="BH9" s="111"/>
+      <c r="BI9" s="111"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="110"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="110"/>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110"/>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="110"/>
-      <c r="AB10" s="110"/>
-      <c r="AC10" s="110"/>
-      <c r="AD10" s="110"/>
-      <c r="AE10" s="110"/>
-      <c r="AF10" s="110"/>
-      <c r="AG10" s="110"/>
-      <c r="AH10" s="110"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="110"/>
-      <c r="AK10" s="110"/>
-      <c r="AL10" s="110"/>
-      <c r="AM10" s="110"/>
-      <c r="AN10" s="110"/>
-      <c r="AO10" s="110"/>
-      <c r="AP10" s="110"/>
-      <c r="AQ10" s="110"/>
-      <c r="AR10" s="110"/>
-      <c r="AS10" s="110"/>
-      <c r="AT10" s="110"/>
-      <c r="AU10" s="110"/>
-      <c r="AV10" s="110"/>
-      <c r="AW10" s="110"/>
-      <c r="AX10" s="110"/>
-      <c r="AY10" s="110"/>
-      <c r="AZ10" s="110"/>
-      <c r="BA10" s="110"/>
-      <c r="BB10" s="110"/>
-      <c r="BC10" s="110"/>
-      <c r="BD10" s="110"/>
-      <c r="BE10" s="110"/>
-      <c r="BF10" s="110"/>
-      <c r="BG10" s="110"/>
-      <c r="BH10" s="110"/>
-      <c r="BI10" s="110"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="111"/>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111"/>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="111"/>
+      <c r="AB10" s="111"/>
+      <c r="AC10" s="111"/>
+      <c r="AD10" s="111"/>
+      <c r="AE10" s="111"/>
+      <c r="AF10" s="111"/>
+      <c r="AG10" s="111"/>
+      <c r="AH10" s="111"/>
+      <c r="AI10" s="111"/>
+      <c r="AJ10" s="111"/>
+      <c r="AK10" s="111"/>
+      <c r="AL10" s="111"/>
+      <c r="AM10" s="111"/>
+      <c r="AN10" s="111"/>
+      <c r="AO10" s="111"/>
+      <c r="AP10" s="111"/>
+      <c r="AQ10" s="111"/>
+      <c r="AR10" s="111"/>
+      <c r="AS10" s="111"/>
+      <c r="AT10" s="111"/>
+      <c r="AU10" s="111"/>
+      <c r="AV10" s="111"/>
+      <c r="AW10" s="111"/>
+      <c r="AX10" s="111"/>
+      <c r="AY10" s="111"/>
+      <c r="AZ10" s="111"/>
+      <c r="BA10" s="111"/>
+      <c r="BB10" s="111"/>
+      <c r="BC10" s="111"/>
+      <c r="BD10" s="111"/>
+      <c r="BE10" s="111"/>
+      <c r="BF10" s="111"/>
+      <c r="BG10" s="111"/>
+      <c r="BH10" s="111"/>
+      <c r="BI10" s="111"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="110"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="110"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
-      <c r="AB11" s="110"/>
-      <c r="AC11" s="110"/>
-      <c r="AD11" s="110"/>
-      <c r="AE11" s="110"/>
-      <c r="AF11" s="110"/>
-      <c r="AG11" s="110"/>
-      <c r="AH11" s="110"/>
-      <c r="AI11" s="110"/>
-      <c r="AJ11" s="110"/>
-      <c r="AK11" s="110"/>
-      <c r="AL11" s="110"/>
-      <c r="AM11" s="110"/>
-      <c r="AN11" s="110"/>
-      <c r="AO11" s="110"/>
-      <c r="AP11" s="110"/>
-      <c r="AQ11" s="110"/>
-      <c r="AR11" s="110"/>
-      <c r="AS11" s="110"/>
-      <c r="AT11" s="110"/>
-      <c r="AU11" s="110"/>
-      <c r="AV11" s="110"/>
-      <c r="AW11" s="110"/>
-      <c r="AX11" s="110"/>
-      <c r="AY11" s="110"/>
-      <c r="AZ11" s="110"/>
-      <c r="BA11" s="110"/>
-      <c r="BB11" s="110"/>
-      <c r="BC11" s="110"/>
-      <c r="BD11" s="110"/>
-      <c r="BE11" s="110"/>
-      <c r="BF11" s="110"/>
-      <c r="BG11" s="110"/>
-      <c r="BH11" s="110"/>
-      <c r="BI11" s="110"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="111"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="111"/>
+      <c r="S11" s="111"/>
+      <c r="T11" s="111"/>
+      <c r="U11" s="111"/>
+      <c r="V11" s="111"/>
+      <c r="W11" s="111"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="111"/>
+      <c r="Z11" s="111"/>
+      <c r="AA11" s="111"/>
+      <c r="AB11" s="111"/>
+      <c r="AC11" s="111"/>
+      <c r="AD11" s="111"/>
+      <c r="AE11" s="111"/>
+      <c r="AF11" s="111"/>
+      <c r="AG11" s="111"/>
+      <c r="AH11" s="111"/>
+      <c r="AI11" s="111"/>
+      <c r="AJ11" s="111"/>
+      <c r="AK11" s="111"/>
+      <c r="AL11" s="111"/>
+      <c r="AM11" s="111"/>
+      <c r="AN11" s="111"/>
+      <c r="AO11" s="111"/>
+      <c r="AP11" s="111"/>
+      <c r="AQ11" s="111"/>
+      <c r="AR11" s="111"/>
+      <c r="AS11" s="111"/>
+      <c r="AT11" s="111"/>
+      <c r="AU11" s="111"/>
+      <c r="AV11" s="111"/>
+      <c r="AW11" s="111"/>
+      <c r="AX11" s="111"/>
+      <c r="AY11" s="111"/>
+      <c r="AZ11" s="111"/>
+      <c r="BA11" s="111"/>
+      <c r="BB11" s="111"/>
+      <c r="BC11" s="111"/>
+      <c r="BD11" s="111"/>
+      <c r="BE11" s="111"/>
+      <c r="BF11" s="111"/>
+      <c r="BG11" s="111"/>
+      <c r="BH11" s="111"/>
+      <c r="BI11" s="111"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="106"/>
-      <c r="S13" s="106"/>
-      <c r="T13" s="106"/>
-      <c r="U13" s="106"/>
-      <c r="V13" s="106"/>
-      <c r="W13" s="106"/>
-      <c r="X13" s="106"/>
-      <c r="Y13" s="106"/>
-      <c r="Z13" s="106"/>
-      <c r="AA13" s="106"/>
-      <c r="AB13" s="106"/>
-      <c r="AC13" s="106"/>
-      <c r="AD13" s="106"/>
-      <c r="AE13" s="106"/>
-      <c r="AF13" s="106"/>
-      <c r="AG13" s="106"/>
-      <c r="AH13" s="106"/>
-      <c r="AI13" s="106"/>
-      <c r="AJ13" s="106"/>
-      <c r="AK13" s="106"/>
-      <c r="AL13" s="106"/>
-      <c r="AM13" s="106"/>
-      <c r="AN13" s="106"/>
-      <c r="AO13" s="106"/>
-      <c r="AP13" s="106"/>
-      <c r="AQ13" s="106"/>
-      <c r="AR13" s="106"/>
-      <c r="AS13" s="106"/>
-      <c r="AT13" s="106"/>
-      <c r="AU13" s="106"/>
-      <c r="AV13" s="106"/>
-      <c r="AW13" s="106"/>
-      <c r="AX13" s="106"/>
-      <c r="AY13" s="106"/>
-      <c r="AZ13" s="106"/>
-      <c r="BA13" s="106"/>
-      <c r="BB13" s="106"/>
-      <c r="BC13" s="106"/>
-      <c r="BD13" s="106"/>
-      <c r="BE13" s="106"/>
-      <c r="BF13" s="106"/>
-      <c r="BG13" s="106"/>
-      <c r="BH13" s="106"/>
-      <c r="BI13" s="106"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="107"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="107"/>
+      <c r="S13" s="107"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="107"/>
+      <c r="V13" s="107"/>
+      <c r="W13" s="107"/>
+      <c r="X13" s="107"/>
+      <c r="Y13" s="107"/>
+      <c r="Z13" s="107"/>
+      <c r="AA13" s="107"/>
+      <c r="AB13" s="107"/>
+      <c r="AC13" s="107"/>
+      <c r="AD13" s="107"/>
+      <c r="AE13" s="107"/>
+      <c r="AF13" s="107"/>
+      <c r="AG13" s="107"/>
+      <c r="AH13" s="107"/>
+      <c r="AI13" s="107"/>
+      <c r="AJ13" s="107"/>
+      <c r="AK13" s="107"/>
+      <c r="AL13" s="107"/>
+      <c r="AM13" s="107"/>
+      <c r="AN13" s="107"/>
+      <c r="AO13" s="107"/>
+      <c r="AP13" s="107"/>
+      <c r="AQ13" s="107"/>
+      <c r="AR13" s="107"/>
+      <c r="AS13" s="107"/>
+      <c r="AT13" s="107"/>
+      <c r="AU13" s="107"/>
+      <c r="AV13" s="107"/>
+      <c r="AW13" s="107"/>
+      <c r="AX13" s="107"/>
+      <c r="AY13" s="107"/>
+      <c r="AZ13" s="107"/>
+      <c r="BA13" s="107"/>
+      <c r="BB13" s="107"/>
+      <c r="BC13" s="107"/>
+      <c r="BD13" s="107"/>
+      <c r="BE13" s="107"/>
+      <c r="BF13" s="107"/>
+      <c r="BG13" s="107"/>
+      <c r="BH13" s="107"/>
+      <c r="BI13" s="107"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="110" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="110"/>
-      <c r="AK14" s="110"/>
-      <c r="AL14" s="110"/>
-      <c r="AM14" s="110"/>
-      <c r="AN14" s="110"/>
-      <c r="AO14" s="110"/>
-      <c r="AP14" s="110"/>
-      <c r="AQ14" s="110"/>
-      <c r="AR14" s="110"/>
-      <c r="AS14" s="110"/>
-      <c r="AT14" s="110"/>
-      <c r="AU14" s="110"/>
-      <c r="AV14" s="110"/>
-      <c r="AW14" s="110"/>
-      <c r="AX14" s="110"/>
-      <c r="AY14" s="110"/>
-      <c r="AZ14" s="110"/>
-      <c r="BA14" s="110"/>
-      <c r="BB14" s="110"/>
-      <c r="BC14" s="110"/>
-      <c r="BD14" s="110"/>
-      <c r="BE14" s="110"/>
-      <c r="BF14" s="110"/>
-      <c r="BG14" s="110"/>
-      <c r="BH14" s="110"/>
-      <c r="BI14" s="110"/>
+      <c r="A14" s="111" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="111"/>
+      <c r="AC14" s="111"/>
+      <c r="AD14" s="111"/>
+      <c r="AE14" s="111"/>
+      <c r="AF14" s="111"/>
+      <c r="AG14" s="111"/>
+      <c r="AH14" s="111"/>
+      <c r="AI14" s="111"/>
+      <c r="AJ14" s="111"/>
+      <c r="AK14" s="111"/>
+      <c r="AL14" s="111"/>
+      <c r="AM14" s="111"/>
+      <c r="AN14" s="111"/>
+      <c r="AO14" s="111"/>
+      <c r="AP14" s="111"/>
+      <c r="AQ14" s="111"/>
+      <c r="AR14" s="111"/>
+      <c r="AS14" s="111"/>
+      <c r="AT14" s="111"/>
+      <c r="AU14" s="111"/>
+      <c r="AV14" s="111"/>
+      <c r="AW14" s="111"/>
+      <c r="AX14" s="111"/>
+      <c r="AY14" s="111"/>
+      <c r="AZ14" s="111"/>
+      <c r="BA14" s="111"/>
+      <c r="BB14" s="111"/>
+      <c r="BC14" s="111"/>
+      <c r="BD14" s="111"/>
+      <c r="BE14" s="111"/>
+      <c r="BF14" s="111"/>
+      <c r="BG14" s="111"/>
+      <c r="BH14" s="111"/>
+      <c r="BI14" s="111"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="110"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="110"/>
-      <c r="U15" s="110"/>
-      <c r="V15" s="110"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="110"/>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="110"/>
-      <c r="AB15" s="110"/>
-      <c r="AC15" s="110"/>
-      <c r="AD15" s="110"/>
-      <c r="AE15" s="110"/>
-      <c r="AF15" s="110"/>
-      <c r="AG15" s="110"/>
-      <c r="AH15" s="110"/>
-      <c r="AI15" s="110"/>
-      <c r="AJ15" s="110"/>
-      <c r="AK15" s="110"/>
-      <c r="AL15" s="110"/>
-      <c r="AM15" s="110"/>
-      <c r="AN15" s="110"/>
-      <c r="AO15" s="110"/>
-      <c r="AP15" s="110"/>
-      <c r="AQ15" s="110"/>
-      <c r="AR15" s="110"/>
-      <c r="AS15" s="110"/>
-      <c r="AT15" s="110"/>
-      <c r="AU15" s="110"/>
-      <c r="AV15" s="110"/>
-      <c r="AW15" s="110"/>
-      <c r="AX15" s="110"/>
-      <c r="AY15" s="110"/>
-      <c r="AZ15" s="110"/>
-      <c r="BA15" s="110"/>
-      <c r="BB15" s="110"/>
-      <c r="BC15" s="110"/>
-      <c r="BD15" s="110"/>
-      <c r="BE15" s="110"/>
-      <c r="BF15" s="110"/>
-      <c r="BG15" s="110"/>
-      <c r="BH15" s="110"/>
-      <c r="BI15" s="110"/>
+      <c r="A15" s="111"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="111"/>
+      <c r="AB15" s="111"/>
+      <c r="AC15" s="111"/>
+      <c r="AD15" s="111"/>
+      <c r="AE15" s="111"/>
+      <c r="AF15" s="111"/>
+      <c r="AG15" s="111"/>
+      <c r="AH15" s="111"/>
+      <c r="AI15" s="111"/>
+      <c r="AJ15" s="111"/>
+      <c r="AK15" s="111"/>
+      <c r="AL15" s="111"/>
+      <c r="AM15" s="111"/>
+      <c r="AN15" s="111"/>
+      <c r="AO15" s="111"/>
+      <c r="AP15" s="111"/>
+      <c r="AQ15" s="111"/>
+      <c r="AR15" s="111"/>
+      <c r="AS15" s="111"/>
+      <c r="AT15" s="111"/>
+      <c r="AU15" s="111"/>
+      <c r="AV15" s="111"/>
+      <c r="AW15" s="111"/>
+      <c r="AX15" s="111"/>
+      <c r="AY15" s="111"/>
+      <c r="AZ15" s="111"/>
+      <c r="BA15" s="111"/>
+      <c r="BB15" s="111"/>
+      <c r="BC15" s="111"/>
+      <c r="BD15" s="111"/>
+      <c r="BE15" s="111"/>
+      <c r="BF15" s="111"/>
+      <c r="BG15" s="111"/>
+      <c r="BH15" s="111"/>
+      <c r="BI15" s="111"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="110"/>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110"/>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="110"/>
-      <c r="AB16" s="110"/>
-      <c r="AC16" s="110"/>
-      <c r="AD16" s="110"/>
-      <c r="AE16" s="110"/>
-      <c r="AF16" s="110"/>
-      <c r="AG16" s="110"/>
-      <c r="AH16" s="110"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="110"/>
-      <c r="AK16" s="110"/>
-      <c r="AL16" s="110"/>
-      <c r="AM16" s="110"/>
-      <c r="AN16" s="110"/>
-      <c r="AO16" s="110"/>
-      <c r="AP16" s="110"/>
-      <c r="AQ16" s="110"/>
-      <c r="AR16" s="110"/>
-      <c r="AS16" s="110"/>
-      <c r="AT16" s="110"/>
-      <c r="AU16" s="110"/>
-      <c r="AV16" s="110"/>
-      <c r="AW16" s="110"/>
-      <c r="AX16" s="110"/>
-      <c r="AY16" s="110"/>
-      <c r="AZ16" s="110"/>
-      <c r="BA16" s="110"/>
-      <c r="BB16" s="110"/>
-      <c r="BC16" s="110"/>
-      <c r="BD16" s="110"/>
-      <c r="BE16" s="110"/>
-      <c r="BF16" s="110"/>
-      <c r="BG16" s="110"/>
-      <c r="BH16" s="110"/>
-      <c r="BI16" s="110"/>
+      <c r="A16" s="111"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="111"/>
+      <c r="AE16" s="111"/>
+      <c r="AF16" s="111"/>
+      <c r="AG16" s="111"/>
+      <c r="AH16" s="111"/>
+      <c r="AI16" s="111"/>
+      <c r="AJ16" s="111"/>
+      <c r="AK16" s="111"/>
+      <c r="AL16" s="111"/>
+      <c r="AM16" s="111"/>
+      <c r="AN16" s="111"/>
+      <c r="AO16" s="111"/>
+      <c r="AP16" s="111"/>
+      <c r="AQ16" s="111"/>
+      <c r="AR16" s="111"/>
+      <c r="AS16" s="111"/>
+      <c r="AT16" s="111"/>
+      <c r="AU16" s="111"/>
+      <c r="AV16" s="111"/>
+      <c r="AW16" s="111"/>
+      <c r="AX16" s="111"/>
+      <c r="AY16" s="111"/>
+      <c r="AZ16" s="111"/>
+      <c r="BA16" s="111"/>
+      <c r="BB16" s="111"/>
+      <c r="BC16" s="111"/>
+      <c r="BD16" s="111"/>
+      <c r="BE16" s="111"/>
+      <c r="BF16" s="111"/>
+      <c r="BG16" s="111"/>
+      <c r="BH16" s="111"/>
+      <c r="BI16" s="111"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="110"/>
-      <c r="B17" s="110"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
-      <c r="S17" s="110"/>
-      <c r="T17" s="110"/>
-      <c r="U17" s="110"/>
-      <c r="V17" s="110"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="110"/>
-      <c r="Y17" s="110"/>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="110"/>
-      <c r="AB17" s="110"/>
-      <c r="AC17" s="110"/>
-      <c r="AD17" s="110"/>
-      <c r="AE17" s="110"/>
-      <c r="AF17" s="110"/>
-      <c r="AG17" s="110"/>
-      <c r="AH17" s="110"/>
-      <c r="AI17" s="110"/>
-      <c r="AJ17" s="110"/>
-      <c r="AK17" s="110"/>
-      <c r="AL17" s="110"/>
-      <c r="AM17" s="110"/>
-      <c r="AN17" s="110"/>
-      <c r="AO17" s="110"/>
-      <c r="AP17" s="110"/>
-      <c r="AQ17" s="110"/>
-      <c r="AR17" s="110"/>
-      <c r="AS17" s="110"/>
-      <c r="AT17" s="110"/>
-      <c r="AU17" s="110"/>
-      <c r="AV17" s="110"/>
-      <c r="AW17" s="110"/>
-      <c r="AX17" s="110"/>
-      <c r="AY17" s="110"/>
-      <c r="AZ17" s="110"/>
-      <c r="BA17" s="110"/>
-      <c r="BB17" s="110"/>
-      <c r="BC17" s="110"/>
-      <c r="BD17" s="110"/>
-      <c r="BE17" s="110"/>
-      <c r="BF17" s="110"/>
-      <c r="BG17" s="110"/>
-      <c r="BH17" s="110"/>
-      <c r="BI17" s="110"/>
+      <c r="A17" s="111"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="111"/>
+      <c r="S17" s="111"/>
+      <c r="T17" s="111"/>
+      <c r="U17" s="111"/>
+      <c r="V17" s="111"/>
+      <c r="W17" s="111"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="111"/>
+      <c r="Z17" s="111"/>
+      <c r="AA17" s="111"/>
+      <c r="AB17" s="111"/>
+      <c r="AC17" s="111"/>
+      <c r="AD17" s="111"/>
+      <c r="AE17" s="111"/>
+      <c r="AF17" s="111"/>
+      <c r="AG17" s="111"/>
+      <c r="AH17" s="111"/>
+      <c r="AI17" s="111"/>
+      <c r="AJ17" s="111"/>
+      <c r="AK17" s="111"/>
+      <c r="AL17" s="111"/>
+      <c r="AM17" s="111"/>
+      <c r="AN17" s="111"/>
+      <c r="AO17" s="111"/>
+      <c r="AP17" s="111"/>
+      <c r="AQ17" s="111"/>
+      <c r="AR17" s="111"/>
+      <c r="AS17" s="111"/>
+      <c r="AT17" s="111"/>
+      <c r="AU17" s="111"/>
+      <c r="AV17" s="111"/>
+      <c r="AW17" s="111"/>
+      <c r="AX17" s="111"/>
+      <c r="AY17" s="111"/>
+      <c r="AZ17" s="111"/>
+      <c r="BA17" s="111"/>
+      <c r="BB17" s="111"/>
+      <c r="BC17" s="111"/>
+      <c r="BD17" s="111"/>
+      <c r="BE17" s="111"/>
+      <c r="BF17" s="111"/>
+      <c r="BG17" s="111"/>
+      <c r="BH17" s="111"/>
+      <c r="BI17" s="111"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="110"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="110"/>
-      <c r="U18" s="110"/>
-      <c r="V18" s="110"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="110"/>
-      <c r="AG18" s="110"/>
-      <c r="AH18" s="110"/>
-      <c r="AI18" s="110"/>
-      <c r="AJ18" s="110"/>
-      <c r="AK18" s="110"/>
-      <c r="AL18" s="110"/>
-      <c r="AM18" s="110"/>
-      <c r="AN18" s="110"/>
-      <c r="AO18" s="110"/>
-      <c r="AP18" s="110"/>
-      <c r="AQ18" s="110"/>
-      <c r="AR18" s="110"/>
-      <c r="AS18" s="110"/>
-      <c r="AT18" s="110"/>
-      <c r="AU18" s="110"/>
-      <c r="AV18" s="110"/>
-      <c r="AW18" s="110"/>
-      <c r="AX18" s="110"/>
-      <c r="AY18" s="110"/>
-      <c r="AZ18" s="110"/>
-      <c r="BA18" s="110"/>
-      <c r="BB18" s="110"/>
-      <c r="BC18" s="110"/>
-      <c r="BD18" s="110"/>
-      <c r="BE18" s="110"/>
-      <c r="BF18" s="110"/>
-      <c r="BG18" s="110"/>
-      <c r="BH18" s="110"/>
-      <c r="BI18" s="110"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="111"/>
+      <c r="S18" s="111"/>
+      <c r="T18" s="111"/>
+      <c r="U18" s="111"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="111"/>
+      <c r="Y18" s="111"/>
+      <c r="Z18" s="111"/>
+      <c r="AA18" s="111"/>
+      <c r="AB18" s="111"/>
+      <c r="AC18" s="111"/>
+      <c r="AD18" s="111"/>
+      <c r="AE18" s="111"/>
+      <c r="AF18" s="111"/>
+      <c r="AG18" s="111"/>
+      <c r="AH18" s="111"/>
+      <c r="AI18" s="111"/>
+      <c r="AJ18" s="111"/>
+      <c r="AK18" s="111"/>
+      <c r="AL18" s="111"/>
+      <c r="AM18" s="111"/>
+      <c r="AN18" s="111"/>
+      <c r="AO18" s="111"/>
+      <c r="AP18" s="111"/>
+      <c r="AQ18" s="111"/>
+      <c r="AR18" s="111"/>
+      <c r="AS18" s="111"/>
+      <c r="AT18" s="111"/>
+      <c r="AU18" s="111"/>
+      <c r="AV18" s="111"/>
+      <c r="AW18" s="111"/>
+      <c r="AX18" s="111"/>
+      <c r="AY18" s="111"/>
+      <c r="AZ18" s="111"/>
+      <c r="BA18" s="111"/>
+      <c r="BB18" s="111"/>
+      <c r="BC18" s="111"/>
+      <c r="BD18" s="111"/>
+      <c r="BE18" s="111"/>
+      <c r="BF18" s="111"/>
+      <c r="BG18" s="111"/>
+      <c r="BH18" s="111"/>
+      <c r="BI18" s="111"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="110"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
-      <c r="U19" s="110"/>
-      <c r="V19" s="110"/>
-      <c r="W19" s="110"/>
-      <c r="X19" s="110"/>
-      <c r="Y19" s="110"/>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="110"/>
-      <c r="AB19" s="110"/>
-      <c r="AC19" s="110"/>
-      <c r="AD19" s="110"/>
-      <c r="AE19" s="110"/>
-      <c r="AF19" s="110"/>
-      <c r="AG19" s="110"/>
-      <c r="AH19" s="110"/>
-      <c r="AI19" s="110"/>
-      <c r="AJ19" s="110"/>
-      <c r="AK19" s="110"/>
-      <c r="AL19" s="110"/>
-      <c r="AM19" s="110"/>
-      <c r="AN19" s="110"/>
-      <c r="AO19" s="110"/>
-      <c r="AP19" s="110"/>
-      <c r="AQ19" s="110"/>
-      <c r="AR19" s="110"/>
-      <c r="AS19" s="110"/>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
-      <c r="BA19" s="110"/>
-      <c r="BB19" s="110"/>
-      <c r="BC19" s="110"/>
-      <c r="BD19" s="110"/>
-      <c r="BE19" s="110"/>
-      <c r="BF19" s="110"/>
-      <c r="BG19" s="110"/>
-      <c r="BH19" s="110"/>
-      <c r="BI19" s="110"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="111"/>
+      <c r="S19" s="111"/>
+      <c r="T19" s="111"/>
+      <c r="U19" s="111"/>
+      <c r="V19" s="111"/>
+      <c r="W19" s="111"/>
+      <c r="X19" s="111"/>
+      <c r="Y19" s="111"/>
+      <c r="Z19" s="111"/>
+      <c r="AA19" s="111"/>
+      <c r="AB19" s="111"/>
+      <c r="AC19" s="111"/>
+      <c r="AD19" s="111"/>
+      <c r="AE19" s="111"/>
+      <c r="AF19" s="111"/>
+      <c r="AG19" s="111"/>
+      <c r="AH19" s="111"/>
+      <c r="AI19" s="111"/>
+      <c r="AJ19" s="111"/>
+      <c r="AK19" s="111"/>
+      <c r="AL19" s="111"/>
+      <c r="AM19" s="111"/>
+      <c r="AN19" s="111"/>
+      <c r="AO19" s="111"/>
+      <c r="AP19" s="111"/>
+      <c r="AQ19" s="111"/>
+      <c r="AR19" s="111"/>
+      <c r="AS19" s="111"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
+      <c r="BA19" s="111"/>
+      <c r="BB19" s="111"/>
+      <c r="BC19" s="111"/>
+      <c r="BD19" s="111"/>
+      <c r="BE19" s="111"/>
+      <c r="BF19" s="111"/>
+      <c r="BG19" s="111"/>
+      <c r="BH19" s="111"/>
+      <c r="BI19" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -4456,90 +4537,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX86"/>
+  <dimension ref="A1:IX91"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="103" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="104" t="s">
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
-      <c r="W1" s="104"/>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="103" t="s">
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="104"/>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="104"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="104"/>
-      <c r="AN1" s="104"/>
-      <c r="AO1" s="104"/>
-      <c r="AP1" s="104"/>
-      <c r="AQ1" s="103" t="s">
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="105"/>
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="103"/>
-      <c r="AS1" s="103"/>
-      <c r="AT1" s="104" t="s">
+      <c r="AR1" s="104"/>
+      <c r="AS1" s="104"/>
+      <c r="AT1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="AU1" s="104"/>
-      <c r="AV1" s="104"/>
-      <c r="AW1" s="104"/>
-      <c r="AX1" s="104"/>
-      <c r="AY1" s="104"/>
-      <c r="AZ1" s="104"/>
-      <c r="BA1" s="103" t="s">
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="103"/>
-      <c r="BC1" s="103"/>
-      <c r="BD1" s="105">
+      <c r="BB1" s="104"/>
+      <c r="BC1" s="104"/>
+      <c r="BD1" s="106">
         <v>45554</v>
       </c>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="105"/>
-      <c r="BI1" s="105"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -4739,77 +4820,77 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="103" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="109"/>
-      <c r="V2" s="109"/>
-      <c r="W2" s="109"/>
-      <c r="X2" s="109"/>
-      <c r="Y2" s="109"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="109"/>
-      <c r="AB2" s="103" t="s">
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="103"/>
-      <c r="AD2" s="103"/>
-      <c r="AE2" s="104" t="s">
+      <c r="AC2" s="104"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="104"/>
-      <c r="AG2" s="104"/>
-      <c r="AH2" s="104"/>
-      <c r="AI2" s="104"/>
-      <c r="AJ2" s="104"/>
-      <c r="AK2" s="104"/>
-      <c r="AL2" s="104"/>
-      <c r="AM2" s="104"/>
-      <c r="AN2" s="104"/>
-      <c r="AO2" s="104"/>
-      <c r="AP2" s="104"/>
-      <c r="AQ2" s="103" t="s">
+      <c r="AF2" s="105"/>
+      <c r="AG2" s="105"/>
+      <c r="AH2" s="105"/>
+      <c r="AI2" s="105"/>
+      <c r="AJ2" s="105"/>
+      <c r="AK2" s="105"/>
+      <c r="AL2" s="105"/>
+      <c r="AM2" s="105"/>
+      <c r="AN2" s="105"/>
+      <c r="AO2" s="105"/>
+      <c r="AP2" s="105"/>
+      <c r="AQ2" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="103"/>
-      <c r="AS2" s="103"/>
-      <c r="AT2" s="104"/>
-      <c r="AU2" s="104"/>
-      <c r="AV2" s="104"/>
-      <c r="AW2" s="104"/>
-      <c r="AX2" s="104"/>
-      <c r="AY2" s="104"/>
-      <c r="AZ2" s="104"/>
-      <c r="BA2" s="103" t="s">
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="104"/>
+      <c r="AT2" s="105"/>
+      <c r="AU2" s="105"/>
+      <c r="AV2" s="105"/>
+      <c r="AW2" s="105"/>
+      <c r="AX2" s="105"/>
+      <c r="AY2" s="105"/>
+      <c r="AZ2" s="105"/>
+      <c r="BA2" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="103"/>
-      <c r="BC2" s="103"/>
-      <c r="BD2" s="105"/>
-      <c r="BE2" s="105"/>
-      <c r="BF2" s="105"/>
-      <c r="BG2" s="105"/>
-      <c r="BH2" s="105"/>
-      <c r="BI2" s="105"/>
+      <c r="BB2" s="104"/>
+      <c r="BC2" s="104"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -5072,71 +5153,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="106" t="s">
+      <c r="A4" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="107" t="s">
-        <v>95</v>
-      </c>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="107"/>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
-      <c r="AB4" s="107"/>
-      <c r="AC4" s="107"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
-      <c r="AQ4" s="107"/>
-      <c r="AR4" s="107"/>
-      <c r="AS4" s="107"/>
-      <c r="AT4" s="107"/>
-      <c r="AU4" s="107"/>
-      <c r="AV4" s="107"/>
-      <c r="AW4" s="107"/>
-      <c r="AX4" s="107"/>
-      <c r="AY4" s="107"/>
-      <c r="AZ4" s="107"/>
-      <c r="BA4" s="107"/>
-      <c r="BB4" s="107"/>
-      <c r="BC4" s="107"/>
-      <c r="BD4" s="107"/>
-      <c r="BE4" s="107"/>
-      <c r="BF4" s="107"/>
-      <c r="BG4" s="107"/>
-      <c r="BH4" s="107"/>
-      <c r="BI4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="108" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
+      <c r="X4" s="108"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="108"/>
+      <c r="AA4" s="108"/>
+      <c r="AB4" s="108"/>
+      <c r="AC4" s="108"/>
+      <c r="AD4" s="108"/>
+      <c r="AE4" s="108"/>
+      <c r="AF4" s="108"/>
+      <c r="AG4" s="108"/>
+      <c r="AH4" s="108"/>
+      <c r="AI4" s="108"/>
+      <c r="AJ4" s="108"/>
+      <c r="AK4" s="108"/>
+      <c r="AL4" s="108"/>
+      <c r="AM4" s="108"/>
+      <c r="AN4" s="108"/>
+      <c r="AO4" s="108"/>
+      <c r="AP4" s="108"/>
+      <c r="AQ4" s="108"/>
+      <c r="AR4" s="108"/>
+      <c r="AS4" s="108"/>
+      <c r="AT4" s="108"/>
+      <c r="AU4" s="108"/>
+      <c r="AV4" s="108"/>
+      <c r="AW4" s="108"/>
+      <c r="AX4" s="108"/>
+      <c r="AY4" s="108"/>
+      <c r="AZ4" s="108"/>
+      <c r="BA4" s="108"/>
+      <c r="BB4" s="108"/>
+      <c r="BC4" s="108"/>
+      <c r="BD4" s="108"/>
+      <c r="BE4" s="108"/>
+      <c r="BF4" s="108"/>
+      <c r="BG4" s="108"/>
+      <c r="BH4" s="108"/>
+      <c r="BI4" s="108"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -5336,71 +5417,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="107" t="s">
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="107"/>
-      <c r="V5" s="107"/>
-      <c r="W5" s="107"/>
-      <c r="X5" s="107"/>
-      <c r="Y5" s="107"/>
-      <c r="Z5" s="107"/>
-      <c r="AA5" s="107"/>
-      <c r="AB5" s="107"/>
-      <c r="AC5" s="107"/>
-      <c r="AD5" s="107"/>
-      <c r="AE5" s="107"/>
-      <c r="AF5" s="107"/>
-      <c r="AG5" s="107"/>
-      <c r="AH5" s="107"/>
-      <c r="AI5" s="107"/>
-      <c r="AJ5" s="107"/>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="107"/>
-      <c r="AM5" s="107"/>
-      <c r="AN5" s="107"/>
-      <c r="AO5" s="107"/>
-      <c r="AP5" s="107"/>
-      <c r="AQ5" s="107"/>
-      <c r="AR5" s="107"/>
-      <c r="AS5" s="107"/>
-      <c r="AT5" s="107"/>
-      <c r="AU5" s="107"/>
-      <c r="AV5" s="107"/>
-      <c r="AW5" s="107"/>
-      <c r="AX5" s="107"/>
-      <c r="AY5" s="107"/>
-      <c r="AZ5" s="107"/>
-      <c r="BA5" s="107"/>
-      <c r="BB5" s="107"/>
-      <c r="BC5" s="107"/>
-      <c r="BD5" s="107"/>
-      <c r="BE5" s="107"/>
-      <c r="BF5" s="107"/>
-      <c r="BG5" s="107"/>
-      <c r="BH5" s="107"/>
-      <c r="BI5" s="107"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="108"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="108"/>
+      <c r="AF5" s="108"/>
+      <c r="AG5" s="108"/>
+      <c r="AH5" s="108"/>
+      <c r="AI5" s="108"/>
+      <c r="AJ5" s="108"/>
+      <c r="AK5" s="108"/>
+      <c r="AL5" s="108"/>
+      <c r="AM5" s="108"/>
+      <c r="AN5" s="108"/>
+      <c r="AO5" s="108"/>
+      <c r="AP5" s="108"/>
+      <c r="AQ5" s="108"/>
+      <c r="AR5" s="108"/>
+      <c r="AS5" s="108"/>
+      <c r="AT5" s="108"/>
+      <c r="AU5" s="108"/>
+      <c r="AV5" s="108"/>
+      <c r="AW5" s="108"/>
+      <c r="AX5" s="108"/>
+      <c r="AY5" s="108"/>
+      <c r="AZ5" s="108"/>
+      <c r="BA5" s="108"/>
+      <c r="BB5" s="108"/>
+      <c r="BC5" s="108"/>
+      <c r="BD5" s="108"/>
+      <c r="BE5" s="108"/>
+      <c r="BF5" s="108"/>
+      <c r="BG5" s="108"/>
+      <c r="BH5" s="108"/>
+      <c r="BI5" s="108"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -5860,75 +5941,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118" t="s">
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="118"/>
-      <c r="P7" s="118" t="s">
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="118"/>
-      <c r="Y7" s="118"/>
-      <c r="Z7" s="118"/>
-      <c r="AA7" s="118"/>
-      <c r="AB7" s="118"/>
-      <c r="AC7" s="118"/>
-      <c r="AD7" s="118"/>
-      <c r="AE7" s="118" t="s">
+      <c r="Q7" s="119"/>
+      <c r="R7" s="119"/>
+      <c r="S7" s="119"/>
+      <c r="T7" s="119"/>
+      <c r="U7" s="119"/>
+      <c r="V7" s="119"/>
+      <c r="W7" s="119"/>
+      <c r="X7" s="119"/>
+      <c r="Y7" s="119"/>
+      <c r="Z7" s="119"/>
+      <c r="AA7" s="119"/>
+      <c r="AB7" s="119"/>
+      <c r="AC7" s="119"/>
+      <c r="AD7" s="119"/>
+      <c r="AE7" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="AF7" s="118"/>
-      <c r="AG7" s="118"/>
-      <c r="AH7" s="118"/>
-      <c r="AI7" s="118"/>
-      <c r="AJ7" s="118"/>
-      <c r="AK7" s="118"/>
-      <c r="AL7" s="118"/>
-      <c r="AM7" s="118"/>
-      <c r="AN7" s="118"/>
-      <c r="AO7" s="118"/>
-      <c r="AP7" s="118"/>
-      <c r="AQ7" s="118"/>
-      <c r="AR7" s="118"/>
-      <c r="AS7" s="118"/>
-      <c r="AT7" s="118"/>
-      <c r="AU7" s="118"/>
-      <c r="AV7" s="118"/>
-      <c r="AW7" s="118"/>
-      <c r="AX7" s="118"/>
-      <c r="AY7" s="118"/>
-      <c r="AZ7" s="118"/>
-      <c r="BA7" s="118"/>
-      <c r="BB7" s="118"/>
-      <c r="BC7" s="118"/>
-      <c r="BD7" s="118"/>
-      <c r="BE7" s="118"/>
-      <c r="BF7" s="118"/>
-      <c r="BG7" s="118"/>
-      <c r="BH7" s="118"/>
-      <c r="BI7" s="118"/>
+      <c r="AF7" s="119"/>
+      <c r="AG7" s="119"/>
+      <c r="AH7" s="119"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
+      <c r="AK7" s="119"/>
+      <c r="AL7" s="119"/>
+      <c r="AM7" s="119"/>
+      <c r="AN7" s="119"/>
+      <c r="AO7" s="119"/>
+      <c r="AP7" s="119"/>
+      <c r="AQ7" s="119"/>
+      <c r="AR7" s="119"/>
+      <c r="AS7" s="119"/>
+      <c r="AT7" s="119"/>
+      <c r="AU7" s="119"/>
+      <c r="AV7" s="119"/>
+      <c r="AW7" s="119"/>
+      <c r="AX7" s="119"/>
+      <c r="AY7" s="119"/>
+      <c r="AZ7" s="119"/>
+      <c r="BA7" s="119"/>
+      <c r="BB7" s="119"/>
+      <c r="BC7" s="119"/>
+      <c r="BD7" s="119"/>
+      <c r="BE7" s="119"/>
+      <c r="BF7" s="119"/>
+      <c r="BG7" s="119"/>
+      <c r="BH7" s="119"/>
+      <c r="BI7" s="119"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -6128,75 +6209,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="115" t="s">
+      <c r="B8" s="117"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="117"/>
-      <c r="P8" s="115" t="s">
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="116"/>
-      <c r="S8" s="116"/>
-      <c r="T8" s="116"/>
-      <c r="U8" s="116"/>
-      <c r="V8" s="116"/>
-      <c r="W8" s="116"/>
-      <c r="X8" s="116"/>
-      <c r="Y8" s="116"/>
-      <c r="Z8" s="116"/>
-      <c r="AA8" s="116"/>
-      <c r="AB8" s="116"/>
-      <c r="AC8" s="116"/>
-      <c r="AD8" s="117"/>
-      <c r="AE8" s="115" t="s">
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="117"/>
+      <c r="X8" s="117"/>
+      <c r="Y8" s="117"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="117"/>
+      <c r="AB8" s="117"/>
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="118"/>
+      <c r="AE8" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="AF8" s="116"/>
-      <c r="AG8" s="116"/>
-      <c r="AH8" s="116"/>
-      <c r="AI8" s="116"/>
-      <c r="AJ8" s="116"/>
-      <c r="AK8" s="116"/>
-      <c r="AL8" s="116"/>
-      <c r="AM8" s="116"/>
-      <c r="AN8" s="116"/>
-      <c r="AO8" s="116"/>
-      <c r="AP8" s="116"/>
-      <c r="AQ8" s="116"/>
-      <c r="AR8" s="116"/>
-      <c r="AS8" s="116"/>
-      <c r="AT8" s="116"/>
-      <c r="AU8" s="116"/>
-      <c r="AV8" s="116"/>
-      <c r="AW8" s="116"/>
-      <c r="AX8" s="116"/>
-      <c r="AY8" s="116"/>
-      <c r="AZ8" s="116"/>
-      <c r="BA8" s="116"/>
-      <c r="BB8" s="116"/>
-      <c r="BC8" s="116"/>
-      <c r="BD8" s="116"/>
-      <c r="BE8" s="116"/>
-      <c r="BF8" s="116"/>
-      <c r="BG8" s="116"/>
-      <c r="BH8" s="116"/>
-      <c r="BI8" s="117"/>
+      <c r="AF8" s="117"/>
+      <c r="AG8" s="117"/>
+      <c r="AH8" s="117"/>
+      <c r="AI8" s="117"/>
+      <c r="AJ8" s="117"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
+      <c r="AM8" s="117"/>
+      <c r="AN8" s="117"/>
+      <c r="AO8" s="117"/>
+      <c r="AP8" s="117"/>
+      <c r="AQ8" s="117"/>
+      <c r="AR8" s="117"/>
+      <c r="AS8" s="117"/>
+      <c r="AT8" s="117"/>
+      <c r="AU8" s="117"/>
+      <c r="AV8" s="117"/>
+      <c r="AW8" s="117"/>
+      <c r="AX8" s="117"/>
+      <c r="AY8" s="117"/>
+      <c r="AZ8" s="117"/>
+      <c r="BA8" s="117"/>
+      <c r="BB8" s="117"/>
+      <c r="BC8" s="117"/>
+      <c r="BD8" s="117"/>
+      <c r="BE8" s="117"/>
+      <c r="BF8" s="117"/>
+      <c r="BG8" s="117"/>
+      <c r="BH8" s="117"/>
+      <c r="BI8" s="118"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -6396,75 +6477,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="119" t="s">
+      <c r="A9" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="114" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="114"/>
-      <c r="T9" s="114"/>
-      <c r="U9" s="114"/>
-      <c r="V9" s="114"/>
-      <c r="W9" s="114"/>
-      <c r="X9" s="114"/>
-      <c r="Y9" s="114"/>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="114"/>
-      <c r="AB9" s="114"/>
-      <c r="AC9" s="114"/>
-      <c r="AD9" s="114"/>
-      <c r="AE9" s="114" t="s">
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q9" s="112"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="112"/>
+      <c r="T9" s="112"/>
+      <c r="U9" s="112"/>
+      <c r="V9" s="112"/>
+      <c r="W9" s="112"/>
+      <c r="X9" s="112"/>
+      <c r="Y9" s="112"/>
+      <c r="Z9" s="112"/>
+      <c r="AA9" s="112"/>
+      <c r="AB9" s="112"/>
+      <c r="AC9" s="112"/>
+      <c r="AD9" s="112"/>
+      <c r="AE9" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
-      <c r="AJ9" s="114"/>
-      <c r="AK9" s="114"/>
-      <c r="AL9" s="114"/>
-      <c r="AM9" s="114"/>
-      <c r="AN9" s="114"/>
-      <c r="AO9" s="114"/>
-      <c r="AP9" s="114"/>
-      <c r="AQ9" s="114"/>
-      <c r="AR9" s="114"/>
-      <c r="AS9" s="114"/>
-      <c r="AT9" s="114"/>
-      <c r="AU9" s="114"/>
-      <c r="AV9" s="114"/>
-      <c r="AW9" s="114"/>
-      <c r="AX9" s="114"/>
-      <c r="AY9" s="114"/>
-      <c r="AZ9" s="114"/>
-      <c r="BA9" s="114"/>
-      <c r="BB9" s="114"/>
-      <c r="BC9" s="114"/>
-      <c r="BD9" s="114"/>
-      <c r="BE9" s="114"/>
-      <c r="BF9" s="114"/>
-      <c r="BG9" s="114"/>
-      <c r="BH9" s="114"/>
-      <c r="BI9" s="114"/>
+      <c r="AF9" s="112"/>
+      <c r="AG9" s="112"/>
+      <c r="AH9" s="112"/>
+      <c r="AI9" s="112"/>
+      <c r="AJ9" s="112"/>
+      <c r="AK9" s="112"/>
+      <c r="AL9" s="112"/>
+      <c r="AM9" s="112"/>
+      <c r="AN9" s="112"/>
+      <c r="AO9" s="112"/>
+      <c r="AP9" s="112"/>
+      <c r="AQ9" s="112"/>
+      <c r="AR9" s="112"/>
+      <c r="AS9" s="112"/>
+      <c r="AT9" s="112"/>
+      <c r="AU9" s="112"/>
+      <c r="AV9" s="112"/>
+      <c r="AW9" s="112"/>
+      <c r="AX9" s="112"/>
+      <c r="AY9" s="112"/>
+      <c r="AZ9" s="112"/>
+      <c r="BA9" s="112"/>
+      <c r="BB9" s="112"/>
+      <c r="BC9" s="112"/>
+      <c r="BD9" s="112"/>
+      <c r="BE9" s="112"/>
+      <c r="BF9" s="112"/>
+      <c r="BG9" s="112"/>
+      <c r="BH9" s="112"/>
+      <c r="BI9" s="112"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -6664,75 +6745,75 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110" t="s">
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="110" t="s">
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="110"/>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110"/>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="110"/>
-      <c r="AB10" s="110"/>
-      <c r="AC10" s="110"/>
-      <c r="AD10" s="110"/>
-      <c r="AE10" s="107" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF10" s="110"/>
-      <c r="AG10" s="110"/>
-      <c r="AH10" s="110"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="110"/>
-      <c r="AK10" s="110"/>
-      <c r="AL10" s="110"/>
-      <c r="AM10" s="110"/>
-      <c r="AN10" s="110"/>
-      <c r="AO10" s="110"/>
-      <c r="AP10" s="110"/>
-      <c r="AQ10" s="110"/>
-      <c r="AR10" s="110"/>
-      <c r="AS10" s="110"/>
-      <c r="AT10" s="110"/>
-      <c r="AU10" s="110"/>
-      <c r="AV10" s="110"/>
-      <c r="AW10" s="110"/>
-      <c r="AX10" s="110"/>
-      <c r="AY10" s="110"/>
-      <c r="AZ10" s="110"/>
-      <c r="BA10" s="110"/>
-      <c r="BB10" s="110"/>
-      <c r="BC10" s="110"/>
-      <c r="BD10" s="110"/>
-      <c r="BE10" s="110"/>
-      <c r="BF10" s="110"/>
-      <c r="BG10" s="110"/>
-      <c r="BH10" s="110"/>
-      <c r="BI10" s="110"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="111"/>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111"/>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="111"/>
+      <c r="AB10" s="111"/>
+      <c r="AC10" s="111"/>
+      <c r="AD10" s="111"/>
+      <c r="AE10" s="108" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF10" s="111"/>
+      <c r="AG10" s="111"/>
+      <c r="AH10" s="111"/>
+      <c r="AI10" s="111"/>
+      <c r="AJ10" s="111"/>
+      <c r="AK10" s="111"/>
+      <c r="AL10" s="111"/>
+      <c r="AM10" s="111"/>
+      <c r="AN10" s="111"/>
+      <c r="AO10" s="111"/>
+      <c r="AP10" s="111"/>
+      <c r="AQ10" s="111"/>
+      <c r="AR10" s="111"/>
+      <c r="AS10" s="111"/>
+      <c r="AT10" s="111"/>
+      <c r="AU10" s="111"/>
+      <c r="AV10" s="111"/>
+      <c r="AW10" s="111"/>
+      <c r="AX10" s="111"/>
+      <c r="AY10" s="111"/>
+      <c r="AZ10" s="111"/>
+      <c r="BA10" s="111"/>
+      <c r="BB10" s="111"/>
+      <c r="BC10" s="111"/>
+      <c r="BD10" s="111"/>
+      <c r="BE10" s="111"/>
+      <c r="BF10" s="111"/>
+      <c r="BG10" s="111"/>
+      <c r="BH10" s="111"/>
+      <c r="BI10" s="111"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -6932,75 +7013,75 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="114" t="s">
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="112" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="114" t="s">
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q11" s="112"/>
+      <c r="R11" s="112"/>
+      <c r="S11" s="112"/>
+      <c r="T11" s="112"/>
+      <c r="U11" s="112"/>
+      <c r="V11" s="112"/>
+      <c r="W11" s="112"/>
+      <c r="X11" s="112"/>
+      <c r="Y11" s="112"/>
+      <c r="Z11" s="112"/>
+      <c r="AA11" s="112"/>
+      <c r="AB11" s="112"/>
+      <c r="AC11" s="112"/>
+      <c r="AD11" s="112"/>
+      <c r="AE11" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="114"/>
-      <c r="S11" s="114"/>
-      <c r="T11" s="114"/>
-      <c r="U11" s="114"/>
-      <c r="V11" s="114"/>
-      <c r="W11" s="114"/>
-      <c r="X11" s="114"/>
-      <c r="Y11" s="114"/>
-      <c r="Z11" s="114"/>
-      <c r="AA11" s="114"/>
-      <c r="AB11" s="114"/>
-      <c r="AC11" s="114"/>
-      <c r="AD11" s="114"/>
-      <c r="AE11" s="114" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF11" s="114"/>
-      <c r="AG11" s="114"/>
-      <c r="AH11" s="114"/>
-      <c r="AI11" s="114"/>
-      <c r="AJ11" s="114"/>
-      <c r="AK11" s="114"/>
-      <c r="AL11" s="114"/>
-      <c r="AM11" s="114"/>
-      <c r="AN11" s="114"/>
-      <c r="AO11" s="114"/>
-      <c r="AP11" s="114"/>
-      <c r="AQ11" s="114"/>
-      <c r="AR11" s="114"/>
-      <c r="AS11" s="114"/>
-      <c r="AT11" s="114"/>
-      <c r="AU11" s="114"/>
-      <c r="AV11" s="114"/>
-      <c r="AW11" s="114"/>
-      <c r="AX11" s="114"/>
-      <c r="AY11" s="114"/>
-      <c r="AZ11" s="114"/>
-      <c r="BA11" s="114"/>
-      <c r="BB11" s="114"/>
-      <c r="BC11" s="114"/>
-      <c r="BD11" s="114"/>
-      <c r="BE11" s="114"/>
-      <c r="BF11" s="114"/>
-      <c r="BG11" s="114"/>
-      <c r="BH11" s="114"/>
-      <c r="BI11" s="114"/>
+      <c r="AF11" s="112"/>
+      <c r="AG11" s="112"/>
+      <c r="AH11" s="112"/>
+      <c r="AI11" s="112"/>
+      <c r="AJ11" s="112"/>
+      <c r="AK11" s="112"/>
+      <c r="AL11" s="112"/>
+      <c r="AM11" s="112"/>
+      <c r="AN11" s="112"/>
+      <c r="AO11" s="112"/>
+      <c r="AP11" s="112"/>
+      <c r="AQ11" s="112"/>
+      <c r="AR11" s="112"/>
+      <c r="AS11" s="112"/>
+      <c r="AT11" s="112"/>
+      <c r="AU11" s="112"/>
+      <c r="AV11" s="112"/>
+      <c r="AW11" s="112"/>
+      <c r="AX11" s="112"/>
+      <c r="AY11" s="112"/>
+      <c r="AZ11" s="112"/>
+      <c r="BA11" s="112"/>
+      <c r="BB11" s="112"/>
+      <c r="BC11" s="112"/>
+      <c r="BD11" s="112"/>
+      <c r="BE11" s="112"/>
+      <c r="BF11" s="112"/>
+      <c r="BG11" s="112"/>
+      <c r="BH11" s="112"/>
+      <c r="BI11" s="112"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -7200,75 +7281,75 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="114" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-      <c r="M12" s="114"/>
-      <c r="N12" s="114"/>
-      <c r="O12" s="114"/>
-      <c r="P12" s="114" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12" s="114"/>
-      <c r="R12" s="114"/>
-      <c r="S12" s="114"/>
-      <c r="T12" s="114"/>
-      <c r="U12" s="114"/>
-      <c r="V12" s="114"/>
-      <c r="W12" s="114"/>
-      <c r="X12" s="114"/>
-      <c r="Y12" s="114"/>
-      <c r="Z12" s="114"/>
-      <c r="AA12" s="114"/>
-      <c r="AB12" s="114"/>
-      <c r="AC12" s="114"/>
-      <c r="AD12" s="114"/>
-      <c r="AE12" s="114" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF12" s="114"/>
-      <c r="AG12" s="114"/>
-      <c r="AH12" s="114"/>
-      <c r="AI12" s="114"/>
-      <c r="AJ12" s="114"/>
-      <c r="AK12" s="114"/>
-      <c r="AL12" s="114"/>
-      <c r="AM12" s="114"/>
-      <c r="AN12" s="114"/>
-      <c r="AO12" s="114"/>
-      <c r="AP12" s="114"/>
-      <c r="AQ12" s="114"/>
-      <c r="AR12" s="114"/>
-      <c r="AS12" s="114"/>
-      <c r="AT12" s="114"/>
-      <c r="AU12" s="114"/>
-      <c r="AV12" s="114"/>
-      <c r="AW12" s="114"/>
-      <c r="AX12" s="114"/>
-      <c r="AY12" s="114"/>
-      <c r="AZ12" s="114"/>
-      <c r="BA12" s="114"/>
-      <c r="BB12" s="114"/>
-      <c r="BC12" s="114"/>
-      <c r="BD12" s="114"/>
-      <c r="BE12" s="114"/>
-      <c r="BF12" s="114"/>
-      <c r="BG12" s="114"/>
-      <c r="BH12" s="114"/>
-      <c r="BI12" s="114"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q12" s="112"/>
+      <c r="R12" s="112"/>
+      <c r="S12" s="112"/>
+      <c r="T12" s="112"/>
+      <c r="U12" s="112"/>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="112"/>
+      <c r="Y12" s="112"/>
+      <c r="Z12" s="112"/>
+      <c r="AA12" s="112"/>
+      <c r="AB12" s="112"/>
+      <c r="AC12" s="112"/>
+      <c r="AD12" s="112"/>
+      <c r="AE12" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF12" s="112"/>
+      <c r="AG12" s="112"/>
+      <c r="AH12" s="112"/>
+      <c r="AI12" s="112"/>
+      <c r="AJ12" s="112"/>
+      <c r="AK12" s="112"/>
+      <c r="AL12" s="112"/>
+      <c r="AM12" s="112"/>
+      <c r="AN12" s="112"/>
+      <c r="AO12" s="112"/>
+      <c r="AP12" s="112"/>
+      <c r="AQ12" s="112"/>
+      <c r="AR12" s="112"/>
+      <c r="AS12" s="112"/>
+      <c r="AT12" s="112"/>
+      <c r="AU12" s="112"/>
+      <c r="AV12" s="112"/>
+      <c r="AW12" s="112"/>
+      <c r="AX12" s="112"/>
+      <c r="AY12" s="112"/>
+      <c r="AZ12" s="112"/>
+      <c r="BA12" s="112"/>
+      <c r="BB12" s="112"/>
+      <c r="BC12" s="112"/>
+      <c r="BD12" s="112"/>
+      <c r="BE12" s="112"/>
+      <c r="BF12" s="112"/>
+      <c r="BG12" s="112"/>
+      <c r="BH12" s="112"/>
+      <c r="BI12" s="112"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -7468,75 +7549,75 @@
       <c r="IX12" s="1"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="110" t="s">
+      <c r="A13" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="114" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="114"/>
-      <c r="I13" s="114"/>
-      <c r="J13" s="114"/>
-      <c r="K13" s="114"/>
-      <c r="L13" s="114"/>
-      <c r="M13" s="114"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="114"/>
-      <c r="P13" s="114" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q13" s="114"/>
-      <c r="R13" s="114"/>
-      <c r="S13" s="114"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="114"/>
-      <c r="V13" s="114"/>
-      <c r="W13" s="114"/>
-      <c r="X13" s="114"/>
-      <c r="Y13" s="114"/>
-      <c r="Z13" s="114"/>
-      <c r="AA13" s="114"/>
-      <c r="AB13" s="114"/>
-      <c r="AC13" s="114"/>
-      <c r="AD13" s="114"/>
-      <c r="AE13" s="114" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF13" s="114"/>
-      <c r="AG13" s="114"/>
-      <c r="AH13" s="114"/>
-      <c r="AI13" s="114"/>
-      <c r="AJ13" s="114"/>
-      <c r="AK13" s="114"/>
-      <c r="AL13" s="114"/>
-      <c r="AM13" s="114"/>
-      <c r="AN13" s="114"/>
-      <c r="AO13" s="114"/>
-      <c r="AP13" s="114"/>
-      <c r="AQ13" s="114"/>
-      <c r="AR13" s="114"/>
-      <c r="AS13" s="114"/>
-      <c r="AT13" s="114"/>
-      <c r="AU13" s="114"/>
-      <c r="AV13" s="114"/>
-      <c r="AW13" s="114"/>
-      <c r="AX13" s="114"/>
-      <c r="AY13" s="114"/>
-      <c r="AZ13" s="114"/>
-      <c r="BA13" s="114"/>
-      <c r="BB13" s="114"/>
-      <c r="BC13" s="114"/>
-      <c r="BD13" s="114"/>
-      <c r="BE13" s="114"/>
-      <c r="BF13" s="114"/>
-      <c r="BG13" s="114"/>
-      <c r="BH13" s="114"/>
-      <c r="BI13" s="114"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="112" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" s="112"/>
+      <c r="R13" s="112"/>
+      <c r="S13" s="112"/>
+      <c r="T13" s="112"/>
+      <c r="U13" s="112"/>
+      <c r="V13" s="112"/>
+      <c r="W13" s="112"/>
+      <c r="X13" s="112"/>
+      <c r="Y13" s="112"/>
+      <c r="Z13" s="112"/>
+      <c r="AA13" s="112"/>
+      <c r="AB13" s="112"/>
+      <c r="AC13" s="112"/>
+      <c r="AD13" s="112"/>
+      <c r="AE13" s="112" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF13" s="112"/>
+      <c r="AG13" s="112"/>
+      <c r="AH13" s="112"/>
+      <c r="AI13" s="112"/>
+      <c r="AJ13" s="112"/>
+      <c r="AK13" s="112"/>
+      <c r="AL13" s="112"/>
+      <c r="AM13" s="112"/>
+      <c r="AN13" s="112"/>
+      <c r="AO13" s="112"/>
+      <c r="AP13" s="112"/>
+      <c r="AQ13" s="112"/>
+      <c r="AR13" s="112"/>
+      <c r="AS13" s="112"/>
+      <c r="AT13" s="112"/>
+      <c r="AU13" s="112"/>
+      <c r="AV13" s="112"/>
+      <c r="AW13" s="112"/>
+      <c r="AX13" s="112"/>
+      <c r="AY13" s="112"/>
+      <c r="AZ13" s="112"/>
+      <c r="BA13" s="112"/>
+      <c r="BB13" s="112"/>
+      <c r="BC13" s="112"/>
+      <c r="BD13" s="112"/>
+      <c r="BE13" s="112"/>
+      <c r="BF13" s="112"/>
+      <c r="BG13" s="112"/>
+      <c r="BH13" s="112"/>
+      <c r="BI13" s="112"/>
       <c r="BJ13" s="1"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
@@ -7736,75 +7817,75 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="114" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
-      <c r="V14" s="114"/>
-      <c r="W14" s="114"/>
-      <c r="X14" s="114"/>
-      <c r="Y14" s="114"/>
-      <c r="Z14" s="114"/>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="114"/>
-      <c r="AE14" s="114" t="s">
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="112" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="112"/>
+      <c r="S14" s="112"/>
+      <c r="T14" s="112"/>
+      <c r="U14" s="112"/>
+      <c r="V14" s="112"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="112"/>
+      <c r="Y14" s="112"/>
+      <c r="Z14" s="112"/>
+      <c r="AA14" s="112"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="112"/>
+      <c r="AD14" s="112"/>
+      <c r="AE14" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="AF14" s="114"/>
-      <c r="AG14" s="114"/>
-      <c r="AH14" s="114"/>
-      <c r="AI14" s="114"/>
-      <c r="AJ14" s="114"/>
-      <c r="AK14" s="114"/>
-      <c r="AL14" s="114"/>
-      <c r="AM14" s="114"/>
-      <c r="AN14" s="114"/>
-      <c r="AO14" s="114"/>
-      <c r="AP14" s="114"/>
-      <c r="AQ14" s="114"/>
-      <c r="AR14" s="114"/>
-      <c r="AS14" s="114"/>
-      <c r="AT14" s="114"/>
-      <c r="AU14" s="114"/>
-      <c r="AV14" s="114"/>
-      <c r="AW14" s="114"/>
-      <c r="AX14" s="114"/>
-      <c r="AY14" s="114"/>
-      <c r="AZ14" s="114"/>
-      <c r="BA14" s="114"/>
-      <c r="BB14" s="114"/>
-      <c r="BC14" s="114"/>
-      <c r="BD14" s="114"/>
-      <c r="BE14" s="114"/>
-      <c r="BF14" s="114"/>
-      <c r="BG14" s="114"/>
-      <c r="BH14" s="114"/>
-      <c r="BI14" s="114"/>
+      <c r="AF14" s="112"/>
+      <c r="AG14" s="112"/>
+      <c r="AH14" s="112"/>
+      <c r="AI14" s="112"/>
+      <c r="AJ14" s="112"/>
+      <c r="AK14" s="112"/>
+      <c r="AL14" s="112"/>
+      <c r="AM14" s="112"/>
+      <c r="AN14" s="112"/>
+      <c r="AO14" s="112"/>
+      <c r="AP14" s="112"/>
+      <c r="AQ14" s="112"/>
+      <c r="AR14" s="112"/>
+      <c r="AS14" s="112"/>
+      <c r="AT14" s="112"/>
+      <c r="AU14" s="112"/>
+      <c r="AV14" s="112"/>
+      <c r="AW14" s="112"/>
+      <c r="AX14" s="112"/>
+      <c r="AY14" s="112"/>
+      <c r="AZ14" s="112"/>
+      <c r="BA14" s="112"/>
+      <c r="BB14" s="112"/>
+      <c r="BC14" s="112"/>
+      <c r="BD14" s="112"/>
+      <c r="BE14" s="112"/>
+      <c r="BF14" s="112"/>
+      <c r="BG14" s="112"/>
+      <c r="BH14" s="112"/>
+      <c r="BI14" s="112"/>
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
@@ -8004,75 +8085,75 @@
       <c r="IX14" s="1"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="110" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="114" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
-      <c r="V15" s="114"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="114"/>
-      <c r="Y15" s="114"/>
-      <c r="Z15" s="114"/>
-      <c r="AA15" s="114"/>
-      <c r="AB15" s="114"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="114"/>
-      <c r="AE15" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF15" s="114"/>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="114"/>
-      <c r="AJ15" s="114"/>
-      <c r="AK15" s="114"/>
-      <c r="AL15" s="114"/>
-      <c r="AM15" s="114"/>
-      <c r="AN15" s="114"/>
-      <c r="AO15" s="114"/>
-      <c r="AP15" s="114"/>
-      <c r="AQ15" s="114"/>
-      <c r="AR15" s="114"/>
-      <c r="AS15" s="114"/>
-      <c r="AT15" s="114"/>
-      <c r="AU15" s="114"/>
-      <c r="AV15" s="114"/>
-      <c r="AW15" s="114"/>
-      <c r="AX15" s="114"/>
-      <c r="AY15" s="114"/>
-      <c r="AZ15" s="114"/>
-      <c r="BA15" s="114"/>
-      <c r="BB15" s="114"/>
-      <c r="BC15" s="114"/>
-      <c r="BD15" s="114"/>
-      <c r="BE15" s="114"/>
-      <c r="BF15" s="114"/>
-      <c r="BG15" s="114"/>
-      <c r="BH15" s="114"/>
-      <c r="BI15" s="114"/>
+      <c r="A15" s="111" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="112"/>
+      <c r="T15" s="112"/>
+      <c r="U15" s="112"/>
+      <c r="V15" s="112"/>
+      <c r="W15" s="112"/>
+      <c r="X15" s="112"/>
+      <c r="Y15" s="112"/>
+      <c r="Z15" s="112"/>
+      <c r="AA15" s="112"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="112"/>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF15" s="112"/>
+      <c r="AG15" s="112"/>
+      <c r="AH15" s="112"/>
+      <c r="AI15" s="112"/>
+      <c r="AJ15" s="112"/>
+      <c r="AK15" s="112"/>
+      <c r="AL15" s="112"/>
+      <c r="AM15" s="112"/>
+      <c r="AN15" s="112"/>
+      <c r="AO15" s="112"/>
+      <c r="AP15" s="112"/>
+      <c r="AQ15" s="112"/>
+      <c r="AR15" s="112"/>
+      <c r="AS15" s="112"/>
+      <c r="AT15" s="112"/>
+      <c r="AU15" s="112"/>
+      <c r="AV15" s="112"/>
+      <c r="AW15" s="112"/>
+      <c r="AX15" s="112"/>
+      <c r="AY15" s="112"/>
+      <c r="AZ15" s="112"/>
+      <c r="BA15" s="112"/>
+      <c r="BB15" s="112"/>
+      <c r="BC15" s="112"/>
+      <c r="BD15" s="112"/>
+      <c r="BE15" s="112"/>
+      <c r="BF15" s="112"/>
+      <c r="BG15" s="112"/>
+      <c r="BH15" s="112"/>
+      <c r="BI15" s="112"/>
       <c r="BJ15" s="1"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
@@ -8272,75 +8353,75 @@
       <c r="IX15" s="1"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="114" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="114"/>
-      <c r="T16" s="114"/>
-      <c r="U16" s="114"/>
-      <c r="V16" s="114"/>
-      <c r="W16" s="114"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="114"/>
-      <c r="AB16" s="114"/>
-      <c r="AC16" s="114"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="114" t="s">
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="112"/>
+      <c r="S16" s="112"/>
+      <c r="T16" s="112"/>
+      <c r="U16" s="112"/>
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+      <c r="Y16" s="112"/>
+      <c r="Z16" s="112"/>
+      <c r="AA16" s="112"/>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="112"/>
+      <c r="AD16" s="112"/>
+      <c r="AE16" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="AF16" s="114"/>
-      <c r="AG16" s="114"/>
-      <c r="AH16" s="114"/>
-      <c r="AI16" s="114"/>
-      <c r="AJ16" s="114"/>
-      <c r="AK16" s="114"/>
-      <c r="AL16" s="114"/>
-      <c r="AM16" s="114"/>
-      <c r="AN16" s="114"/>
-      <c r="AO16" s="114"/>
-      <c r="AP16" s="114"/>
-      <c r="AQ16" s="114"/>
-      <c r="AR16" s="114"/>
-      <c r="AS16" s="114"/>
-      <c r="AT16" s="114"/>
-      <c r="AU16" s="114"/>
-      <c r="AV16" s="114"/>
-      <c r="AW16" s="114"/>
-      <c r="AX16" s="114"/>
-      <c r="AY16" s="114"/>
-      <c r="AZ16" s="114"/>
-      <c r="BA16" s="114"/>
-      <c r="BB16" s="114"/>
-      <c r="BC16" s="114"/>
-      <c r="BD16" s="114"/>
-      <c r="BE16" s="114"/>
-      <c r="BF16" s="114"/>
-      <c r="BG16" s="114"/>
-      <c r="BH16" s="114"/>
-      <c r="BI16" s="114"/>
+      <c r="AF16" s="112"/>
+      <c r="AG16" s="112"/>
+      <c r="AH16" s="112"/>
+      <c r="AI16" s="112"/>
+      <c r="AJ16" s="112"/>
+      <c r="AK16" s="112"/>
+      <c r="AL16" s="112"/>
+      <c r="AM16" s="112"/>
+      <c r="AN16" s="112"/>
+      <c r="AO16" s="112"/>
+      <c r="AP16" s="112"/>
+      <c r="AQ16" s="112"/>
+      <c r="AR16" s="112"/>
+      <c r="AS16" s="112"/>
+      <c r="AT16" s="112"/>
+      <c r="AU16" s="112"/>
+      <c r="AV16" s="112"/>
+      <c r="AW16" s="112"/>
+      <c r="AX16" s="112"/>
+      <c r="AY16" s="112"/>
+      <c r="AZ16" s="112"/>
+      <c r="BA16" s="112"/>
+      <c r="BB16" s="112"/>
+      <c r="BC16" s="112"/>
+      <c r="BD16" s="112"/>
+      <c r="BE16" s="112"/>
+      <c r="BF16" s="112"/>
+      <c r="BG16" s="112"/>
+      <c r="BH16" s="112"/>
+      <c r="BI16" s="112"/>
       <c r="BJ16" s="1"/>
       <c r="BK16" s="1"/>
       <c r="BL16" s="1"/>
@@ -8540,67 +8621,75 @@
       <c r="IX16" s="1"/>
     </row>
     <row r="17" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
-      <c r="AJ17" s="32"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
-      <c r="AN17" s="32"/>
-      <c r="AO17" s="32"/>
-      <c r="AP17" s="32"/>
-      <c r="AQ17" s="32"/>
-      <c r="AR17" s="32"/>
-      <c r="AS17" s="32"/>
-      <c r="AT17" s="32"/>
-      <c r="AU17" s="32"/>
-      <c r="AV17" s="32"/>
-      <c r="AW17" s="32"/>
-      <c r="AX17" s="32"/>
-      <c r="AY17" s="32"/>
-      <c r="AZ17" s="32"/>
-      <c r="BA17" s="32"/>
-      <c r="BB17" s="32"/>
-      <c r="BC17" s="32"/>
-      <c r="BD17" s="32"/>
-      <c r="BE17" s="32"/>
-      <c r="BF17" s="32"/>
-      <c r="BG17" s="32"/>
-      <c r="BH17" s="32"/>
-      <c r="BI17" s="32"/>
+      <c r="A17" s="111" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="112"/>
+      <c r="S17" s="112"/>
+      <c r="T17" s="112"/>
+      <c r="U17" s="112"/>
+      <c r="V17" s="112"/>
+      <c r="W17" s="112"/>
+      <c r="X17" s="112"/>
+      <c r="Y17" s="112"/>
+      <c r="Z17" s="112"/>
+      <c r="AA17" s="112"/>
+      <c r="AB17" s="112"/>
+      <c r="AC17" s="112"/>
+      <c r="AD17" s="112"/>
+      <c r="AE17" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="112"/>
+      <c r="AG17" s="112"/>
+      <c r="AH17" s="112"/>
+      <c r="AI17" s="112"/>
+      <c r="AJ17" s="112"/>
+      <c r="AK17" s="112"/>
+      <c r="AL17" s="112"/>
+      <c r="AM17" s="112"/>
+      <c r="AN17" s="112"/>
+      <c r="AO17" s="112"/>
+      <c r="AP17" s="112"/>
+      <c r="AQ17" s="112"/>
+      <c r="AR17" s="112"/>
+      <c r="AS17" s="112"/>
+      <c r="AT17" s="112"/>
+      <c r="AU17" s="112"/>
+      <c r="AV17" s="112"/>
+      <c r="AW17" s="112"/>
+      <c r="AX17" s="112"/>
+      <c r="AY17" s="112"/>
+      <c r="AZ17" s="112"/>
+      <c r="BA17" s="112"/>
+      <c r="BB17" s="112"/>
+      <c r="BC17" s="112"/>
+      <c r="BD17" s="112"/>
+      <c r="BE17" s="112"/>
+      <c r="BF17" s="112"/>
+      <c r="BG17" s="112"/>
+      <c r="BH17" s="112"/>
+      <c r="BI17" s="112"/>
       <c r="BJ17" s="1"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
@@ -9060,67 +9149,67 @@
       <c r="IX18" s="1"/>
     </row>
     <row r="19" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
-      <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
-      <c r="AR19" s="4"/>
-      <c r="AS19" s="4"/>
-      <c r="AT19" s="4"/>
-      <c r="AU19" s="4"/>
-      <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="4"/>
-      <c r="AY19" s="4"/>
-      <c r="AZ19" s="4"/>
-      <c r="BA19" s="4"/>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
-      <c r="BH19" s="4"/>
-      <c r="BI19" s="4"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32"/>
+      <c r="AJ19" s="32"/>
+      <c r="AK19" s="32"/>
+      <c r="AL19" s="32"/>
+      <c r="AM19" s="32"/>
+      <c r="AN19" s="32"/>
+      <c r="AO19" s="32"/>
+      <c r="AP19" s="32"/>
+      <c r="AQ19" s="32"/>
+      <c r="AR19" s="32"/>
+      <c r="AS19" s="32"/>
+      <c r="AT19" s="32"/>
+      <c r="AU19" s="32"/>
+      <c r="AV19" s="32"/>
+      <c r="AW19" s="32"/>
+      <c r="AX19" s="32"/>
+      <c r="AY19" s="32"/>
+      <c r="AZ19" s="32"/>
+      <c r="BA19" s="32"/>
+      <c r="BB19" s="32"/>
+      <c r="BC19" s="32"/>
+      <c r="BD19" s="32"/>
+      <c r="BE19" s="32"/>
+      <c r="BF19" s="32"/>
+      <c r="BG19" s="32"/>
+      <c r="BH19" s="32"/>
+      <c r="BI19" s="32"/>
       <c r="BJ19" s="1"/>
       <c r="BK19" s="1"/>
       <c r="BL19" s="1"/>
@@ -9320,75 +9409,67 @@
       <c r="IX19" s="1"/>
     </row>
     <row r="20" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="111" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="112"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="124" t="s">
-        <v>45</v>
-      </c>
-      <c r="P20" s="122"/>
-      <c r="Q20" s="122"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="T20" s="122"/>
-      <c r="U20" s="122"/>
-      <c r="V20" s="122"/>
-      <c r="W20" s="122"/>
-      <c r="X20" s="122"/>
-      <c r="Y20" s="122"/>
-      <c r="Z20" s="122"/>
-      <c r="AA20" s="122"/>
-      <c r="AB20" s="122"/>
-      <c r="AC20" s="122"/>
-      <c r="AD20" s="122"/>
-      <c r="AE20" s="122"/>
-      <c r="AF20" s="122"/>
-      <c r="AG20" s="122"/>
-      <c r="AH20" s="122"/>
-      <c r="AI20" s="122"/>
-      <c r="AJ20" s="122"/>
-      <c r="AK20" s="122"/>
-      <c r="AL20" s="122"/>
-      <c r="AM20" s="122"/>
-      <c r="AN20" s="122"/>
-      <c r="AO20" s="122"/>
-      <c r="AP20" s="122"/>
-      <c r="AQ20" s="122"/>
-      <c r="AR20" s="122"/>
-      <c r="AS20" s="123"/>
-      <c r="AT20" s="120" t="s">
-        <v>25</v>
-      </c>
-      <c r="AU20" s="120"/>
-      <c r="AV20" s="120"/>
-      <c r="AW20" s="120"/>
-      <c r="AX20" s="120"/>
-      <c r="AY20" s="120"/>
-      <c r="AZ20" s="120"/>
-      <c r="BA20" s="120"/>
-      <c r="BB20" s="120"/>
-      <c r="BC20" s="120"/>
-      <c r="BD20" s="120"/>
-      <c r="BE20" s="120"/>
-      <c r="BF20" s="120"/>
-      <c r="BG20" s="120"/>
-      <c r="BH20" s="120"/>
-      <c r="BI20" s="121"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="4"/>
+      <c r="AG20" s="4"/>
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="4"/>
+      <c r="AJ20" s="4"/>
+      <c r="AK20" s="4"/>
+      <c r="AL20" s="4"/>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="4"/>
+      <c r="AQ20" s="4"/>
+      <c r="AR20" s="4"/>
+      <c r="AS20" s="4"/>
+      <c r="AT20" s="4"/>
+      <c r="AU20" s="4"/>
+      <c r="AV20" s="4"/>
+      <c r="AW20" s="4"/>
+      <c r="AX20" s="4"/>
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="4"/>
+      <c r="BG20" s="4"/>
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
       <c r="BJ20" s="1"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="1"/>
@@ -9588,43 +9669,75 @@
       <c r="IX20" s="1"/>
     </row>
     <row r="21" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="34">
-        <v>1</v>
-      </c>
-      <c r="R21" s="25"/>
-      <c r="S21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT21" s="5"/>
-      <c r="AU21" s="9"/>
-      <c r="AV21" s="9"/>
-      <c r="AW21" s="6"/>
-      <c r="AX21" s="6"/>
-      <c r="AY21" s="6"/>
-      <c r="AZ21" s="6"/>
-      <c r="BA21" s="6"/>
-      <c r="BB21" s="6"/>
-      <c r="BC21" s="6"/>
-      <c r="BD21" s="6"/>
-      <c r="BE21" s="6"/>
-      <c r="BF21" s="6"/>
-      <c r="BG21" s="6"/>
-      <c r="BH21" s="6"/>
-      <c r="BI21" s="7"/>
+      <c r="A21" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="124" t="s">
+        <v>45</v>
+      </c>
+      <c r="P21" s="122"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="122"/>
+      <c r="U21" s="122"/>
+      <c r="V21" s="122"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="122"/>
+      <c r="Y21" s="122"/>
+      <c r="Z21" s="122"/>
+      <c r="AA21" s="122"/>
+      <c r="AB21" s="122"/>
+      <c r="AC21" s="122"/>
+      <c r="AD21" s="122"/>
+      <c r="AE21" s="122"/>
+      <c r="AF21" s="122"/>
+      <c r="AG21" s="122"/>
+      <c r="AH21" s="122"/>
+      <c r="AI21" s="122"/>
+      <c r="AJ21" s="122"/>
+      <c r="AK21" s="122"/>
+      <c r="AL21" s="122"/>
+      <c r="AM21" s="122"/>
+      <c r="AN21" s="122"/>
+      <c r="AO21" s="122"/>
+      <c r="AP21" s="122"/>
+      <c r="AQ21" s="122"/>
+      <c r="AR21" s="122"/>
+      <c r="AS21" s="123"/>
+      <c r="AT21" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU21" s="120"/>
+      <c r="AV21" s="120"/>
+      <c r="AW21" s="120"/>
+      <c r="AX21" s="120"/>
+      <c r="AY21" s="120"/>
+      <c r="AZ21" s="120"/>
+      <c r="BA21" s="120"/>
+      <c r="BB21" s="120"/>
+      <c r="BC21" s="120"/>
+      <c r="BD21" s="120"/>
+      <c r="BE21" s="120"/>
+      <c r="BF21" s="120"/>
+      <c r="BG21" s="120"/>
+      <c r="BH21" s="120"/>
+      <c r="BI21" s="121"/>
       <c r="BJ21" s="1"/>
       <c r="BK21" s="1"/>
       <c r="BL21" s="1"/>
@@ -9824,67 +9937,43 @@
       <c r="IX21" s="1"/>
     </row>
     <row r="22" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="10"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="22"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="22"/>
-      <c r="AN22" s="22"/>
-      <c r="AO22" s="22"/>
-      <c r="AP22" s="22"/>
-      <c r="AQ22" s="22"/>
-      <c r="AR22" s="22"/>
-      <c r="AS22" s="50"/>
-      <c r="AT22" s="8"/>
-      <c r="AW22" s="10"/>
-      <c r="AX22" s="11"/>
-      <c r="AY22" s="11"/>
-      <c r="AZ22" s="11"/>
-      <c r="BA22" s="11"/>
-      <c r="BB22" s="11"/>
-      <c r="BC22" s="11"/>
-      <c r="BD22" s="11"/>
-      <c r="BE22" s="11"/>
-      <c r="BF22" s="11"/>
-      <c r="BG22" s="11"/>
-      <c r="BH22" s="11"/>
-      <c r="BI22" s="12"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="34">
+        <v>1</v>
+      </c>
+      <c r="R22" s="25"/>
+      <c r="S22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="9"/>
+      <c r="AV22" s="9"/>
+      <c r="AW22" s="6"/>
+      <c r="AX22" s="6"/>
+      <c r="AY22" s="6"/>
+      <c r="AZ22" s="6"/>
+      <c r="BA22" s="6"/>
+      <c r="BB22" s="6"/>
+      <c r="BC22" s="6"/>
+      <c r="BD22" s="6"/>
+      <c r="BE22" s="6"/>
+      <c r="BF22" s="6"/>
+      <c r="BG22" s="6"/>
+      <c r="BH22" s="6"/>
+      <c r="BI22" s="7"/>
       <c r="BJ22" s="1"/>
       <c r="BK22" s="1"/>
       <c r="BL22" s="1"/>
@@ -10084,9 +10173,6 @@
       <c r="IX22" s="1"/>
     </row>
     <row r="23" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
-        <v>114</v>
-      </c>
       <c r="B23" s="10"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -10098,42 +10184,42 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="27">
-        <v>2</v>
-      </c>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="33"/>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AG23" s="33"/>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
-      <c r="AK23" s="33"/>
-      <c r="AL23" s="33"/>
-      <c r="AM23" s="33"/>
-      <c r="AN23" s="33"/>
-      <c r="AO23" s="33"/>
-      <c r="AP23" s="33"/>
-      <c r="AQ23" s="33"/>
-      <c r="AR23" s="33"/>
-      <c r="AS23" s="33"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
+      <c r="AE23" s="22"/>
+      <c r="AF23" s="22"/>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="22"/>
+      <c r="AL23" s="22"/>
+      <c r="AM23" s="22"/>
+      <c r="AN23" s="22"/>
+      <c r="AO23" s="22"/>
+      <c r="AP23" s="22"/>
+      <c r="AQ23" s="22"/>
+      <c r="AR23" s="22"/>
+      <c r="AS23" s="50"/>
       <c r="AT23" s="8"/>
       <c r="AW23" s="10"/>
       <c r="AX23" s="11"/>
@@ -10347,6 +10433,9 @@
       <c r="IX23" s="1"/>
     </row>
     <row r="24" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="28" t="s">
+        <v>112</v>
+      </c>
       <c r="B24" s="10"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
@@ -10359,39 +10448,41 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="51"/>
-      <c r="O24" s="48" t="s">
+      <c r="O24" s="27">
+        <v>2</v>
+      </c>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="22"/>
-      <c r="AC24" s="22"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="22"/>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="22"/>
-      <c r="AH24" s="22"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="22"/>
-      <c r="AK24" s="22"/>
-      <c r="AL24" s="22"/>
-      <c r="AM24" s="22"/>
-      <c r="AN24" s="22"/>
-      <c r="AO24" s="22"/>
-      <c r="AP24" s="22"/>
-      <c r="AQ24" s="22"/>
-      <c r="AR24" s="22"/>
-      <c r="AS24" s="50"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="33"/>
+      <c r="AH24" s="33"/>
+      <c r="AI24" s="33"/>
+      <c r="AJ24" s="33"/>
+      <c r="AK24" s="33"/>
+      <c r="AL24" s="33"/>
+      <c r="AM24" s="33"/>
+      <c r="AN24" s="33"/>
+      <c r="AO24" s="33"/>
+      <c r="AP24" s="33"/>
+      <c r="AQ24" s="33"/>
+      <c r="AR24" s="33"/>
+      <c r="AS24" s="33"/>
       <c r="AT24" s="8"/>
       <c r="AW24" s="10"/>
       <c r="AX24" s="11"/>
@@ -10616,42 +10707,40 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="27">
-        <v>3</v>
-      </c>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="13"/>
-      <c r="AB25" s="13"/>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="13"/>
-      <c r="AE25" s="13"/>
-      <c r="AF25" s="13"/>
-      <c r="AG25" s="13"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="13"/>
-      <c r="AJ25" s="15"/>
-      <c r="AK25" s="15"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="15"/>
-      <c r="AN25" s="15"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
-      <c r="AS25" s="15"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="22"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
+      <c r="AE25" s="22"/>
+      <c r="AF25" s="22"/>
+      <c r="AG25" s="22"/>
+      <c r="AH25" s="22"/>
+      <c r="AI25" s="22"/>
+      <c r="AJ25" s="22"/>
+      <c r="AK25" s="22"/>
+      <c r="AL25" s="22"/>
+      <c r="AM25" s="22"/>
+      <c r="AN25" s="22"/>
+      <c r="AO25" s="22"/>
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="22"/>
+      <c r="AR25" s="22"/>
+      <c r="AS25" s="50"/>
       <c r="AT25" s="8"/>
       <c r="AW25" s="10"/>
       <c r="AX25" s="11"/>
@@ -10865,7 +10954,6 @@
       <c r="IX25" s="1"/>
     </row>
     <row r="26" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
       <c r="B26" s="10"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -10878,11 +10966,14 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="S26" s="29" t="s">
-        <v>83</v>
+      <c r="O26" s="27">
+        <v>3</v>
+      </c>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="T26" s="13"/>
       <c r="U26" s="13"/>
@@ -11137,12 +11228,37 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
       <c r="O27" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="S27" s="28"/>
-      <c r="T27" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="S27" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="13"/>
+      <c r="AH27" s="13"/>
+      <c r="AI27" s="13"/>
+      <c r="AJ27" s="15"/>
+      <c r="AK27" s="15"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+      <c r="AS27" s="15"/>
       <c r="AT27" s="8"/>
       <c r="AW27" s="10"/>
       <c r="AX27" s="11"/>
@@ -11369,39 +11485,13 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="16"/>
-      <c r="AI28" s="16"/>
-      <c r="AJ28" s="17"/>
-      <c r="AK28" s="17"/>
-      <c r="AL28" s="17"/>
-      <c r="AM28" s="17"/>
-      <c r="AN28" s="17"/>
-      <c r="AO28" s="17"/>
-      <c r="AP28" s="17"/>
-      <c r="AQ28" s="17"/>
-      <c r="AR28" s="17"/>
-      <c r="AS28" s="18"/>
+      <c r="O28" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="S28" s="28"/>
+      <c r="T28" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="AT28" s="8"/>
       <c r="AW28" s="10"/>
       <c r="AX28" s="11"/>
@@ -11615,6 +11705,7 @@
       <c r="IX28" s="1"/>
     </row>
     <row r="29" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39"/>
       <c r="B29" s="10"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -11627,43 +11718,69 @@
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
-      <c r="O29" s="27">
-        <v>4</v>
-      </c>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
-      <c r="AH29" s="20"/>
-      <c r="AI29" s="20"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="21"/>
-      <c r="AL29" s="21"/>
-      <c r="AM29" s="21"/>
-      <c r="AN29" s="21"/>
-      <c r="AO29" s="21"/>
-      <c r="AP29" s="21"/>
-      <c r="AQ29" s="21"/>
-      <c r="AR29" s="21"/>
-      <c r="AS29" s="21"/>
+      <c r="O29" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="16"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17"/>
+      <c r="AM29" s="17"/>
+      <c r="AN29" s="17"/>
+      <c r="AO29" s="17"/>
+      <c r="AP29" s="17"/>
+      <c r="AQ29" s="17"/>
+      <c r="AR29" s="17"/>
+      <c r="AS29" s="18"/>
       <c r="AT29" s="8"/>
-      <c r="BI29" s="44"/>
+      <c r="AW29" s="10"/>
+      <c r="AX29" s="11"/>
+      <c r="AY29" s="11"/>
+      <c r="AZ29" s="11"/>
+      <c r="BA29" s="11"/>
+      <c r="BB29" s="11"/>
+      <c r="BC29" s="11"/>
+      <c r="BD29" s="11"/>
+      <c r="BE29" s="11"/>
+      <c r="BF29" s="11"/>
+      <c r="BG29" s="11"/>
+      <c r="BH29" s="11"/>
+      <c r="BI29" s="12"/>
+      <c r="BJ29" s="1"/>
+      <c r="BK29" s="1"/>
+      <c r="BL29" s="1"/>
+      <c r="BM29" s="1"/>
+      <c r="BN29" s="1"/>
+      <c r="BO29" s="1"/>
+      <c r="BP29" s="1"/>
+      <c r="BQ29" s="1"/>
+      <c r="BR29" s="1"/>
+      <c r="BS29" s="1"/>
+      <c r="BT29" s="1"/>
+      <c r="BU29" s="1"/>
+      <c r="BV29" s="1"/>
+      <c r="BW29" s="1"/>
+      <c r="BX29" s="1"/>
+      <c r="BY29" s="1"/>
       <c r="BZ29" s="1"/>
       <c r="CA29" s="1"/>
       <c r="CB29" s="1"/>
@@ -11847,6 +11964,7 @@
       <c r="IX29" s="1"/>
     </row>
     <row r="30" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="51"/>
       <c r="B30" s="10"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -11859,16 +11977,14 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
-      <c r="O30" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="25"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20" t="s">
-        <v>126</v>
-      </c>
+      <c r="O30" s="27"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="T30" s="20"/>
       <c r="U30" s="20"/>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
@@ -11895,7 +12011,35 @@
       <c r="AR30" s="21"/>
       <c r="AS30" s="21"/>
       <c r="AT30" s="8"/>
-      <c r="BI30" s="44"/>
+      <c r="AW30" s="10"/>
+      <c r="AX30" s="11"/>
+      <c r="AY30" s="11"/>
+      <c r="AZ30" s="11"/>
+      <c r="BA30" s="11"/>
+      <c r="BB30" s="11"/>
+      <c r="BC30" s="11"/>
+      <c r="BD30" s="11"/>
+      <c r="BE30" s="11"/>
+      <c r="BF30" s="11"/>
+      <c r="BG30" s="11"/>
+      <c r="BH30" s="11"/>
+      <c r="BI30" s="51"/>
+      <c r="BJ30" s="1"/>
+      <c r="BK30" s="1"/>
+      <c r="BL30" s="1"/>
+      <c r="BM30" s="1"/>
+      <c r="BN30" s="1"/>
+      <c r="BO30" s="1"/>
+      <c r="BP30" s="1"/>
+      <c r="BQ30" s="1"/>
+      <c r="BR30" s="1"/>
+      <c r="BS30" s="1"/>
+      <c r="BT30" s="1"/>
+      <c r="BU30" s="1"/>
+      <c r="BV30" s="1"/>
+      <c r="BW30" s="1"/>
+      <c r="BX30" s="1"/>
+      <c r="BY30" s="1"/>
       <c r="BZ30" s="1"/>
       <c r="CA30" s="1"/>
       <c r="CB30" s="1"/>
@@ -12079,6 +12223,7 @@
       <c r="IX30" s="1"/>
     </row>
     <row r="31" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="51"/>
       <c r="B31" s="10"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
@@ -12091,16 +12236,14 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="25"/>
-      <c r="S31" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="T31" s="20"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20" t="s">
+        <v>123</v>
+      </c>
       <c r="U31" s="20"/>
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
@@ -12127,7 +12270,35 @@
       <c r="AR31" s="21"/>
       <c r="AS31" s="21"/>
       <c r="AT31" s="8"/>
-      <c r="BI31" s="44"/>
+      <c r="AW31" s="10"/>
+      <c r="AX31" s="11"/>
+      <c r="AY31" s="11"/>
+      <c r="AZ31" s="11"/>
+      <c r="BA31" s="11"/>
+      <c r="BB31" s="11"/>
+      <c r="BC31" s="11"/>
+      <c r="BD31" s="11"/>
+      <c r="BE31" s="11"/>
+      <c r="BF31" s="11"/>
+      <c r="BG31" s="11"/>
+      <c r="BH31" s="11"/>
+      <c r="BI31" s="51"/>
+      <c r="BJ31" s="1"/>
+      <c r="BK31" s="1"/>
+      <c r="BL31" s="1"/>
+      <c r="BM31" s="1"/>
+      <c r="BN31" s="1"/>
+      <c r="BO31" s="1"/>
+      <c r="BP31" s="1"/>
+      <c r="BQ31" s="1"/>
+      <c r="BR31" s="1"/>
+      <c r="BS31" s="1"/>
+      <c r="BT31" s="1"/>
+      <c r="BU31" s="1"/>
+      <c r="BV31" s="1"/>
+      <c r="BW31" s="1"/>
+      <c r="BX31" s="1"/>
+      <c r="BY31" s="1"/>
       <c r="BZ31" s="1"/>
       <c r="CA31" s="1"/>
       <c r="CB31" s="1"/>
@@ -12311,9 +12482,7 @@
       <c r="IX31" s="1"/>
     </row>
     <row r="32" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>133</v>
-      </c>
+      <c r="B32" s="10"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
@@ -12325,13 +12494,41 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="29" t="s">
-        <v>128</v>
-      </c>
+      <c r="O32" s="27">
+        <v>4</v>
+      </c>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
       <c r="R32" s="25"/>
-      <c r="T32" s="2" t="s">
-        <v>138</v>
-      </c>
+      <c r="S32" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
+      <c r="AE32" s="20"/>
+      <c r="AF32" s="20"/>
+      <c r="AG32" s="20"/>
+      <c r="AH32" s="20"/>
+      <c r="AI32" s="20"/>
+      <c r="AJ32" s="21"/>
+      <c r="AK32" s="21"/>
+      <c r="AL32" s="21"/>
+      <c r="AM32" s="21"/>
+      <c r="AN32" s="21"/>
+      <c r="AO32" s="21"/>
+      <c r="AP32" s="21"/>
+      <c r="AQ32" s="21"/>
+      <c r="AR32" s="21"/>
+      <c r="AS32" s="21"/>
       <c r="AT32" s="8"/>
       <c r="BI32" s="44"/>
       <c r="BZ32" s="1"/>
@@ -12517,6 +12714,7 @@
       <c r="IX32" s="1"/>
     </row>
     <row r="33" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="10"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
@@ -12528,14 +12726,16 @@
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
+      <c r="O33" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
       <c r="R33" s="25"/>
-      <c r="S33" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="U33" s="20"/>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
@@ -12560,9 +12760,9 @@
       <c r="AP33" s="21"/>
       <c r="AQ33" s="21"/>
       <c r="AR33" s="21"/>
-      <c r="AS33" s="53"/>
+      <c r="AS33" s="21"/>
       <c r="AT33" s="8"/>
-      <c r="BI33" s="33"/>
+      <c r="BI33" s="44"/>
       <c r="BZ33" s="1"/>
       <c r="CA33" s="1"/>
       <c r="CB33" s="1"/>
@@ -12746,6 +12946,7 @@
       <c r="IX33" s="1"/>
     </row>
     <row r="34" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="10"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
@@ -12757,41 +12958,41 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
-      <c r="AF34" s="16"/>
-      <c r="AG34" s="16"/>
-      <c r="AH34" s="16"/>
-      <c r="AI34" s="16"/>
-      <c r="AJ34" s="17"/>
-      <c r="AK34" s="17"/>
-      <c r="AL34" s="17"/>
-      <c r="AM34" s="17"/>
-      <c r="AN34" s="17"/>
-      <c r="AO34" s="17"/>
-      <c r="AP34" s="17"/>
-      <c r="AQ34" s="17"/>
-      <c r="AR34" s="17"/>
-      <c r="AS34" s="18"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+      <c r="AE34" s="20"/>
+      <c r="AF34" s="20"/>
+      <c r="AG34" s="20"/>
+      <c r="AH34" s="20"/>
+      <c r="AI34" s="20"/>
+      <c r="AJ34" s="21"/>
+      <c r="AK34" s="21"/>
+      <c r="AL34" s="21"/>
+      <c r="AM34" s="21"/>
+      <c r="AN34" s="21"/>
+      <c r="AO34" s="21"/>
+      <c r="AP34" s="21"/>
+      <c r="AQ34" s="21"/>
+      <c r="AR34" s="21"/>
+      <c r="AS34" s="21"/>
       <c r="AT34" s="8"/>
-      <c r="BI34" s="33"/>
+      <c r="BI34" s="44"/>
       <c r="BZ34" s="1"/>
       <c r="CA34" s="1"/>
       <c r="CB34" s="1"/>
@@ -12975,9 +13176,7 @@
       <c r="IX34" s="1"/>
     </row>
     <row r="35" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
+      <c r="B35" s="10"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
@@ -12989,71 +13188,41 @@
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
-      <c r="O35" s="52">
-        <v>5</v>
-      </c>
+      <c r="O35" s="27"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="25"/>
-      <c r="S35" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="T35" s="13"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="13"/>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
-      <c r="AH35" s="13"/>
-      <c r="AI35" s="13"/>
-      <c r="AJ35" s="15"/>
-      <c r="AK35" s="15"/>
-      <c r="AL35" s="15"/>
-      <c r="AM35" s="15"/>
-      <c r="AN35" s="15"/>
-      <c r="AO35" s="15"/>
-      <c r="AP35" s="15"/>
-      <c r="AQ35" s="15"/>
-      <c r="AR35" s="15"/>
-      <c r="AS35" s="53"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
+      <c r="AE35" s="20"/>
+      <c r="AF35" s="20"/>
+      <c r="AG35" s="20"/>
+      <c r="AH35" s="20"/>
+      <c r="AI35" s="20"/>
+      <c r="AJ35" s="21"/>
+      <c r="AK35" s="21"/>
+      <c r="AL35" s="21"/>
+      <c r="AM35" s="21"/>
+      <c r="AN35" s="21"/>
+      <c r="AO35" s="21"/>
+      <c r="AP35" s="21"/>
+      <c r="AQ35" s="21"/>
+      <c r="AR35" s="21"/>
+      <c r="AS35" s="21"/>
       <c r="AT35" s="8"/>
-      <c r="AW35" s="10"/>
-      <c r="AX35" s="11"/>
-      <c r="AY35" s="11"/>
-      <c r="AZ35" s="11"/>
-      <c r="BA35" s="11"/>
-      <c r="BB35" s="11"/>
-      <c r="BC35" s="11"/>
-      <c r="BD35" s="11"/>
-      <c r="BE35" s="11"/>
-      <c r="BF35" s="11"/>
-      <c r="BG35" s="11"/>
-      <c r="BH35" s="11"/>
-      <c r="BI35" s="12"/>
-      <c r="BJ35" s="1"/>
-      <c r="BK35" s="1"/>
-      <c r="BL35" s="1"/>
-      <c r="BM35" s="1"/>
-      <c r="BN35" s="1"/>
-      <c r="BO35" s="1"/>
-      <c r="BP35" s="1"/>
-      <c r="BQ35" s="1"/>
-      <c r="BR35" s="1"/>
-      <c r="BS35" s="1"/>
-      <c r="BT35" s="1"/>
-      <c r="BU35" s="1"/>
-      <c r="BV35" s="1"/>
-      <c r="BW35" s="1"/>
-      <c r="BX35" s="1"/>
-      <c r="BY35" s="1"/>
+      <c r="BI35" s="44"/>
       <c r="BZ35" s="1"/>
       <c r="CA35" s="1"/>
       <c r="CB35" s="1"/>
@@ -13237,9 +13406,7 @@
       <c r="IX35" s="1"/>
     </row>
     <row r="36" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
+      <c r="B36" s="10"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
@@ -13252,70 +13419,42 @@
       <c r="M36" s="11"/>
       <c r="N36" s="11"/>
       <c r="O36" s="29" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="25"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
-      <c r="AH36" s="13"/>
-      <c r="AI36" s="13"/>
-      <c r="AJ36" s="15"/>
-      <c r="AK36" s="15"/>
-      <c r="AL36" s="15"/>
-      <c r="AM36" s="15"/>
-      <c r="AN36" s="15"/>
-      <c r="AO36" s="15"/>
-      <c r="AP36" s="15"/>
-      <c r="AQ36" s="15"/>
-      <c r="AR36" s="15"/>
-      <c r="AS36" s="15"/>
+      <c r="S36" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="20"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
+      <c r="AG36" s="20"/>
+      <c r="AH36" s="20"/>
+      <c r="AI36" s="20"/>
+      <c r="AJ36" s="21"/>
+      <c r="AK36" s="21"/>
+      <c r="AL36" s="21"/>
+      <c r="AM36" s="21"/>
+      <c r="AN36" s="21"/>
+      <c r="AO36" s="21"/>
+      <c r="AP36" s="21"/>
+      <c r="AQ36" s="21"/>
+      <c r="AR36" s="21"/>
+      <c r="AS36" s="21"/>
       <c r="AT36" s="8"/>
-      <c r="AW36" s="10"/>
-      <c r="AX36" s="11"/>
-      <c r="AY36" s="11"/>
-      <c r="AZ36" s="11"/>
-      <c r="BA36" s="11"/>
-      <c r="BB36" s="11"/>
-      <c r="BC36" s="11"/>
-      <c r="BD36" s="11"/>
-      <c r="BE36" s="11"/>
-      <c r="BF36" s="11"/>
-      <c r="BG36" s="11"/>
-      <c r="BH36" s="11"/>
-      <c r="BI36" s="12"/>
-      <c r="BJ36" s="1"/>
-      <c r="BK36" s="1"/>
-      <c r="BL36" s="1"/>
-      <c r="BM36" s="1"/>
-      <c r="BN36" s="1"/>
-      <c r="BO36" s="1"/>
-      <c r="BP36" s="1"/>
-      <c r="BQ36" s="1"/>
-      <c r="BR36" s="1"/>
-      <c r="BS36" s="1"/>
-      <c r="BT36" s="1"/>
-      <c r="BU36" s="1"/>
-      <c r="BV36" s="1"/>
-      <c r="BW36" s="1"/>
-      <c r="BX36" s="1"/>
-      <c r="BY36" s="1"/>
+      <c r="BI36" s="44"/>
       <c r="BZ36" s="1"/>
       <c r="CA36" s="1"/>
       <c r="CB36" s="1"/>
@@ -13499,9 +13638,9 @@
       <c r="IX36" s="1"/>
     </row>
     <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
+      <c r="A37" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
@@ -13513,71 +13652,15 @@
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
-      <c r="O37" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
+      <c r="O37" s="29" t="s">
+        <v>125</v>
+      </c>
       <c r="R37" s="25"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="13"/>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="13"/>
-      <c r="AF37" s="13"/>
-      <c r="AG37" s="13"/>
-      <c r="AH37" s="13"/>
-      <c r="AI37" s="13"/>
-      <c r="AJ37" s="15"/>
-      <c r="AK37" s="15"/>
-      <c r="AL37" s="15"/>
-      <c r="AM37" s="15"/>
-      <c r="AN37" s="15"/>
-      <c r="AO37" s="15"/>
-      <c r="AP37" s="15"/>
-      <c r="AQ37" s="15"/>
-      <c r="AR37" s="15"/>
-      <c r="AS37" s="15"/>
+      <c r="T37" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="AT37" s="8"/>
-      <c r="AW37" s="10"/>
-      <c r="AX37" s="11"/>
-      <c r="AY37" s="11"/>
-      <c r="AZ37" s="11"/>
-      <c r="BA37" s="11"/>
-      <c r="BB37" s="11"/>
-      <c r="BC37" s="11"/>
-      <c r="BD37" s="11"/>
-      <c r="BE37" s="11"/>
-      <c r="BF37" s="11"/>
-      <c r="BG37" s="11"/>
-      <c r="BH37" s="11"/>
-      <c r="BI37" s="12"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="1"/>
-      <c r="BM37" s="1"/>
-      <c r="BN37" s="1"/>
-      <c r="BO37" s="1"/>
-      <c r="BP37" s="1"/>
-      <c r="BQ37" s="1"/>
-      <c r="BR37" s="1"/>
-      <c r="BS37" s="1"/>
-      <c r="BT37" s="1"/>
-      <c r="BU37" s="1"/>
-      <c r="BV37" s="1"/>
-      <c r="BW37" s="1"/>
-      <c r="BX37" s="1"/>
-      <c r="BY37" s="1"/>
+      <c r="BI37" s="44"/>
       <c r="BZ37" s="1"/>
       <c r="CA37" s="1"/>
       <c r="CB37" s="1"/>
@@ -13761,9 +13844,6 @@
       <c r="IX37" s="1"/>
     </row>
     <row r="38" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
@@ -13775,71 +13855,41 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
-      <c r="O38" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="51"/>
       <c r="R38" s="25"/>
-      <c r="S38" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13"/>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="13"/>
-      <c r="AG38" s="13"/>
-      <c r="AH38" s="13"/>
-      <c r="AI38" s="13"/>
-      <c r="AJ38" s="13"/>
-      <c r="AK38" s="13"/>
-      <c r="AL38" s="13"/>
-      <c r="AM38" s="13"/>
-      <c r="AN38" s="13"/>
-      <c r="AO38" s="13"/>
-      <c r="AP38" s="13"/>
-      <c r="AQ38" s="13"/>
-      <c r="AR38" s="13"/>
-      <c r="AS38" s="13"/>
+      <c r="S38" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="20"/>
+      <c r="AE38" s="20"/>
+      <c r="AF38" s="20"/>
+      <c r="AG38" s="20"/>
+      <c r="AH38" s="20"/>
+      <c r="AI38" s="20"/>
+      <c r="AJ38" s="21"/>
+      <c r="AK38" s="21"/>
+      <c r="AL38" s="21"/>
+      <c r="AM38" s="21"/>
+      <c r="AN38" s="21"/>
+      <c r="AO38" s="21"/>
+      <c r="AP38" s="21"/>
+      <c r="AQ38" s="21"/>
+      <c r="AR38" s="21"/>
+      <c r="AS38" s="53"/>
       <c r="AT38" s="8"/>
-      <c r="AW38" s="10"/>
-      <c r="AX38" s="11"/>
-      <c r="AY38" s="11"/>
-      <c r="AZ38" s="11"/>
-      <c r="BA38" s="11"/>
-      <c r="BB38" s="11"/>
-      <c r="BC38" s="11"/>
-      <c r="BD38" s="11"/>
-      <c r="BE38" s="11"/>
-      <c r="BF38" s="11"/>
-      <c r="BG38" s="11"/>
-      <c r="BH38" s="11"/>
-      <c r="BI38" s="12"/>
-      <c r="BJ38" s="1"/>
-      <c r="BK38" s="1"/>
-      <c r="BL38" s="1"/>
-      <c r="BM38" s="1"/>
-      <c r="BN38" s="1"/>
-      <c r="BO38" s="1"/>
-      <c r="BP38" s="1"/>
-      <c r="BQ38" s="1"/>
-      <c r="BR38" s="1"/>
-      <c r="BS38" s="1"/>
-      <c r="BT38" s="1"/>
-      <c r="BU38" s="1"/>
-      <c r="BV38" s="1"/>
-      <c r="BW38" s="1"/>
-      <c r="BX38" s="1"/>
-      <c r="BY38" s="1"/>
+      <c r="BI38" s="33"/>
       <c r="BZ38" s="1"/>
       <c r="CA38" s="1"/>
       <c r="CB38" s="1"/>
@@ -14023,9 +14073,6 @@
       <c r="IX38" s="1"/>
     </row>
     <row r="39" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
@@ -14037,69 +14084,41 @@
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="13"/>
-      <c r="AG39" s="13"/>
-      <c r="AH39" s="13"/>
-      <c r="AI39" s="13"/>
-      <c r="AJ39" s="13"/>
-      <c r="AK39" s="13"/>
-      <c r="AL39" s="13"/>
-      <c r="AM39" s="13"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39" s="13"/>
-      <c r="AQ39" s="13"/>
-      <c r="AR39" s="13"/>
-      <c r="AS39" s="13"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="37"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="16"/>
+      <c r="T39" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="U39" s="16"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="16"/>
+      <c r="Y39" s="16"/>
+      <c r="Z39" s="16"/>
+      <c r="AA39" s="16"/>
+      <c r="AB39" s="16"/>
+      <c r="AC39" s="16"/>
+      <c r="AD39" s="16"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="16"/>
+      <c r="AI39" s="16"/>
+      <c r="AJ39" s="17"/>
+      <c r="AK39" s="17"/>
+      <c r="AL39" s="17"/>
+      <c r="AM39" s="17"/>
+      <c r="AN39" s="17"/>
+      <c r="AO39" s="17"/>
+      <c r="AP39" s="17"/>
+      <c r="AQ39" s="17"/>
+      <c r="AR39" s="17"/>
+      <c r="AS39" s="18"/>
       <c r="AT39" s="8"/>
-      <c r="AW39" s="10"/>
-      <c r="AX39" s="11"/>
-      <c r="AY39" s="11"/>
-      <c r="AZ39" s="11"/>
-      <c r="BA39" s="11"/>
-      <c r="BB39" s="11"/>
-      <c r="BC39" s="11"/>
-      <c r="BD39" s="11"/>
-      <c r="BE39" s="11"/>
-      <c r="BF39" s="11"/>
-      <c r="BG39" s="11"/>
-      <c r="BH39" s="11"/>
-      <c r="BI39" s="12"/>
-      <c r="BJ39" s="1"/>
-      <c r="BK39" s="1"/>
-      <c r="BL39" s="1"/>
-      <c r="BM39" s="1"/>
-      <c r="BN39" s="1"/>
-      <c r="BO39" s="1"/>
-      <c r="BP39" s="1"/>
-      <c r="BQ39" s="1"/>
-      <c r="BR39" s="1"/>
-      <c r="BS39" s="1"/>
-      <c r="BT39" s="1"/>
-      <c r="BU39" s="1"/>
-      <c r="BV39" s="1"/>
-      <c r="BW39" s="1"/>
-      <c r="BX39" s="1"/>
-      <c r="BY39" s="1"/>
+      <c r="BI39" s="33"/>
       <c r="BZ39" s="1"/>
       <c r="CA39" s="1"/>
       <c r="CB39" s="1"/>
@@ -14297,14 +14316,16 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
+      <c r="O40" s="52">
+        <v>5</v>
+      </c>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
       <c r="R40" s="25"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="13" t="s">
-        <v>52</v>
-      </c>
+      <c r="S40" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="T40" s="13"/>
       <c r="U40" s="13"/>
       <c r="V40" s="13"/>
       <c r="W40" s="13"/>
@@ -14320,16 +14341,16 @@
       <c r="AG40" s="13"/>
       <c r="AH40" s="13"/>
       <c r="AI40" s="13"/>
-      <c r="AJ40" s="13"/>
-      <c r="AK40" s="13"/>
-      <c r="AL40" s="13"/>
-      <c r="AM40" s="13"/>
-      <c r="AN40" s="13"/>
-      <c r="AO40" s="13"/>
-      <c r="AP40" s="13"/>
-      <c r="AQ40" s="13"/>
-      <c r="AR40" s="13"/>
-      <c r="AS40" s="13"/>
+      <c r="AJ40" s="15"/>
+      <c r="AK40" s="15"/>
+      <c r="AL40" s="15"/>
+      <c r="AM40" s="15"/>
+      <c r="AN40" s="15"/>
+      <c r="AO40" s="15"/>
+      <c r="AP40" s="15"/>
+      <c r="AQ40" s="15"/>
+      <c r="AR40" s="15"/>
+      <c r="AS40" s="53"/>
       <c r="AT40" s="8"/>
       <c r="AW40" s="10"/>
       <c r="AX40" s="11"/>
@@ -14557,39 +14578,41 @@
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
-      <c r="O41" s="36"/>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13"/>
+      <c r="O41" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
       <c r="R41" s="25"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="20"/>
-      <c r="AA41" s="20"/>
-      <c r="AB41" s="20"/>
-      <c r="AC41" s="20"/>
-      <c r="AD41" s="20"/>
-      <c r="AE41" s="20"/>
-      <c r="AF41" s="20"/>
-      <c r="AG41" s="20"/>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="20"/>
-      <c r="AJ41" s="20"/>
-      <c r="AK41" s="20"/>
-      <c r="AL41" s="20"/>
-      <c r="AM41" s="20"/>
-      <c r="AN41" s="20"/>
-      <c r="AO41" s="20"/>
-      <c r="AP41" s="20"/>
-      <c r="AQ41" s="20"/>
-      <c r="AR41" s="20"/>
-      <c r="AS41" s="38"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="U41" s="13"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="47"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="13"/>
+      <c r="AC41" s="13"/>
+      <c r="AD41" s="13"/>
+      <c r="AE41" s="13"/>
+      <c r="AF41" s="13"/>
+      <c r="AG41" s="13"/>
+      <c r="AH41" s="13"/>
+      <c r="AI41" s="13"/>
+      <c r="AJ41" s="15"/>
+      <c r="AK41" s="15"/>
+      <c r="AL41" s="15"/>
+      <c r="AM41" s="15"/>
+      <c r="AN41" s="15"/>
+      <c r="AO41" s="15"/>
+      <c r="AP41" s="15"/>
+      <c r="AQ41" s="15"/>
+      <c r="AR41" s="15"/>
+      <c r="AS41" s="15"/>
       <c r="AT41" s="8"/>
       <c r="AW41" s="10"/>
       <c r="AX41" s="11"/>
@@ -14803,6 +14826,7 @@
       <c r="IX41" s="1"/>
     </row>
     <row r="42" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="28"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -14816,14 +14840,16 @@
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
-      <c r="O42" s="36"/>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="13"/>
+      <c r="O42" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
       <c r="R42" s="25"/>
-      <c r="S42" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="T42" s="13"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="U42" s="13"/>
       <c r="V42" s="13"/>
       <c r="W42" s="13"/>
@@ -14839,16 +14865,16 @@
       <c r="AG42" s="13"/>
       <c r="AH42" s="13"/>
       <c r="AI42" s="13"/>
-      <c r="AJ42" s="13"/>
-      <c r="AK42" s="13"/>
-      <c r="AL42" s="13"/>
-      <c r="AM42" s="13"/>
-      <c r="AN42" s="13"/>
-      <c r="AO42" s="13"/>
-      <c r="AP42" s="13"/>
-      <c r="AQ42" s="13"/>
-      <c r="AR42" s="13"/>
-      <c r="AS42" s="38"/>
+      <c r="AJ42" s="15"/>
+      <c r="AK42" s="15"/>
+      <c r="AL42" s="15"/>
+      <c r="AM42" s="15"/>
+      <c r="AN42" s="15"/>
+      <c r="AO42" s="15"/>
+      <c r="AP42" s="15"/>
+      <c r="AQ42" s="15"/>
+      <c r="AR42" s="15"/>
+      <c r="AS42" s="15"/>
       <c r="AT42" s="8"/>
       <c r="AW42" s="10"/>
       <c r="AX42" s="11"/>
@@ -15076,14 +15102,16 @@
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
-      <c r="O43" s="36"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="O43" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
       <c r="R43" s="25"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="13" t="s">
-        <v>113</v>
-      </c>
+      <c r="S43" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="T43" s="13"/>
       <c r="U43" s="13"/>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
@@ -15108,7 +15136,7 @@
       <c r="AP43" s="13"/>
       <c r="AQ43" s="13"/>
       <c r="AR43" s="13"/>
-      <c r="AS43" s="20"/>
+      <c r="AS43" s="13"/>
       <c r="AT43" s="8"/>
       <c r="AW43" s="10"/>
       <c r="AX43" s="11"/>
@@ -15342,7 +15370,7 @@
       <c r="R44" s="25"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="U44" s="13"/>
       <c r="V44" s="13"/>
@@ -15368,7 +15396,7 @@
       <c r="AP44" s="13"/>
       <c r="AQ44" s="13"/>
       <c r="AR44" s="13"/>
-      <c r="AS44" s="20"/>
+      <c r="AS44" s="13"/>
       <c r="AT44" s="8"/>
       <c r="AW44" s="10"/>
       <c r="AX44" s="11"/>
@@ -15601,7 +15629,9 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="25"/>
       <c r="S45" s="13"/>
-      <c r="T45" s="14"/>
+      <c r="T45" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="U45" s="13"/>
       <c r="V45" s="13"/>
       <c r="W45" s="13"/>
@@ -15858,33 +15888,35 @@
       <c r="P46" s="13"/>
       <c r="Q46" s="13"/>
       <c r="R46" s="25"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="13"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="13"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46" s="13"/>
-      <c r="AB46" s="13"/>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="13"/>
-      <c r="AE46" s="13"/>
-      <c r="AF46" s="13"/>
-      <c r="AG46" s="13"/>
-      <c r="AH46" s="13"/>
-      <c r="AI46" s="13"/>
-      <c r="AJ46" s="13"/>
-      <c r="AK46" s="13"/>
-      <c r="AL46" s="13"/>
-      <c r="AM46" s="13"/>
-      <c r="AN46" s="13"/>
-      <c r="AO46" s="13"/>
-      <c r="AP46" s="13"/>
-      <c r="AQ46" s="13"/>
-      <c r="AR46" s="13"/>
-      <c r="AS46" s="13"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="20"/>
+      <c r="AC46" s="20"/>
+      <c r="AD46" s="20"/>
+      <c r="AE46" s="20"/>
+      <c r="AF46" s="20"/>
+      <c r="AG46" s="20"/>
+      <c r="AH46" s="20"/>
+      <c r="AI46" s="20"/>
+      <c r="AJ46" s="20"/>
+      <c r="AK46" s="20"/>
+      <c r="AL46" s="20"/>
+      <c r="AM46" s="20"/>
+      <c r="AN46" s="20"/>
+      <c r="AO46" s="20"/>
+      <c r="AP46" s="20"/>
+      <c r="AQ46" s="20"/>
+      <c r="AR46" s="20"/>
+      <c r="AS46" s="38"/>
       <c r="AT46" s="8"/>
       <c r="AW46" s="10"/>
       <c r="AX46" s="11"/>
@@ -16098,7 +16130,6 @@
       <c r="IX46" s="1"/>
     </row>
     <row r="47" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
@@ -16116,8 +16147,10 @@
       <c r="P47" s="13"/>
       <c r="Q47" s="13"/>
       <c r="R47" s="25"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="14"/>
+      <c r="S47" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="T47" s="13"/>
       <c r="U47" s="13"/>
       <c r="V47" s="13"/>
       <c r="W47" s="13"/>
@@ -16142,7 +16175,7 @@
       <c r="AP47" s="13"/>
       <c r="AQ47" s="13"/>
       <c r="AR47" s="13"/>
-      <c r="AS47" s="13"/>
+      <c r="AS47" s="38"/>
       <c r="AT47" s="8"/>
       <c r="AW47" s="10"/>
       <c r="AX47" s="11"/>
@@ -16356,7 +16389,7 @@
       <c r="IX47" s="1"/>
     </row>
     <row r="48" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="28"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
@@ -16375,6 +16408,9 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="25"/>
       <c r="S48" s="13"/>
+      <c r="T48" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="U48" s="13"/>
       <c r="V48" s="13"/>
       <c r="W48" s="13"/>
@@ -16399,7 +16435,7 @@
       <c r="AP48" s="13"/>
       <c r="AQ48" s="13"/>
       <c r="AR48" s="13"/>
-      <c r="AS48" s="13"/>
+      <c r="AS48" s="20"/>
       <c r="AT48" s="8"/>
       <c r="AW48" s="10"/>
       <c r="AX48" s="11"/>
@@ -16613,7 +16649,7 @@
       <c r="IX48" s="1"/>
     </row>
     <row r="49" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="28"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -16632,6 +16668,9 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="25"/>
       <c r="S49" s="13"/>
+      <c r="T49" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="U49" s="13"/>
       <c r="V49" s="13"/>
       <c r="W49" s="13"/>
@@ -16656,7 +16695,7 @@
       <c r="AP49" s="13"/>
       <c r="AQ49" s="13"/>
       <c r="AR49" s="13"/>
-      <c r="AS49" s="13"/>
+      <c r="AS49" s="20"/>
       <c r="AT49" s="8"/>
       <c r="AW49" s="10"/>
       <c r="AX49" s="11"/>
@@ -16870,7 +16909,7 @@
       <c r="IX49" s="1"/>
     </row>
     <row r="50" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="28"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
@@ -16889,6 +16928,8 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="25"/>
       <c r="S50" s="13"/>
+      <c r="T50" s="14"/>
+      <c r="U50" s="13"/>
       <c r="V50" s="13"/>
       <c r="W50" s="13"/>
       <c r="X50" s="13"/>
@@ -17126,7 +17167,7 @@
       <c r="IX50" s="1"/>
     </row>
     <row r="51" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="28"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
@@ -17145,6 +17186,8 @@
       <c r="Q51" s="13"/>
       <c r="R51" s="25"/>
       <c r="S51" s="13"/>
+      <c r="T51" s="14"/>
+      <c r="U51" s="13"/>
       <c r="V51" s="13"/>
       <c r="W51" s="13"/>
       <c r="X51" s="13"/>
@@ -17382,7 +17425,7 @@
       <c r="IX51" s="1"/>
     </row>
     <row r="52" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
+      <c r="A52" s="28"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
@@ -17401,8 +17444,9 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="25"/>
       <c r="S52" s="13"/>
+      <c r="T52" s="14"/>
       <c r="U52" s="13"/>
-      <c r="V52" s="14"/>
+      <c r="V52" s="13"/>
       <c r="W52" s="13"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="13"/>
@@ -17659,7 +17703,7 @@
       <c r="R53" s="25"/>
       <c r="S53" s="13"/>
       <c r="U53" s="13"/>
-      <c r="V53" s="14"/>
+      <c r="V53" s="13"/>
       <c r="W53" s="13"/>
       <c r="X53" s="13"/>
       <c r="Y53" s="13"/>
@@ -17915,6 +17959,7 @@
       <c r="Q54" s="13"/>
       <c r="R54" s="25"/>
       <c r="S54" s="13"/>
+      <c r="U54" s="13"/>
       <c r="V54" s="13"/>
       <c r="W54" s="13"/>
       <c r="X54" s="13"/>
@@ -18427,7 +18472,6 @@
       <c r="Q56" s="13"/>
       <c r="R56" s="25"/>
       <c r="S56" s="13"/>
-      <c r="U56" s="13"/>
       <c r="V56" s="13"/>
       <c r="W56" s="13"/>
       <c r="X56" s="13"/>
@@ -18685,7 +18729,7 @@
       <c r="R57" s="25"/>
       <c r="S57" s="13"/>
       <c r="U57" s="13"/>
-      <c r="V57" s="13"/>
+      <c r="V57" s="14"/>
       <c r="W57" s="13"/>
       <c r="X57" s="13"/>
       <c r="Y57" s="13"/>
@@ -18722,7 +18766,7 @@
       <c r="BF57" s="11"/>
       <c r="BG57" s="11"/>
       <c r="BH57" s="11"/>
-      <c r="BI57" s="51"/>
+      <c r="BI57" s="12"/>
       <c r="BJ57" s="1"/>
       <c r="BK57" s="1"/>
       <c r="BL57" s="1"/>
@@ -18942,7 +18986,7 @@
       <c r="R58" s="25"/>
       <c r="S58" s="13"/>
       <c r="U58" s="13"/>
-      <c r="V58" s="13"/>
+      <c r="V58" s="14"/>
       <c r="W58" s="13"/>
       <c r="X58" s="13"/>
       <c r="Y58" s="13"/>
@@ -18979,7 +19023,7 @@
       <c r="BF58" s="11"/>
       <c r="BG58" s="11"/>
       <c r="BH58" s="11"/>
-      <c r="BI58" s="51"/>
+      <c r="BI58" s="12"/>
       <c r="BJ58" s="1"/>
       <c r="BK58" s="1"/>
       <c r="BL58" s="1"/>
@@ -19198,7 +19242,6 @@
       <c r="Q59" s="13"/>
       <c r="R59" s="25"/>
       <c r="S59" s="13"/>
-      <c r="U59" s="13"/>
       <c r="V59" s="13"/>
       <c r="W59" s="13"/>
       <c r="X59" s="13"/>
@@ -19236,7 +19279,7 @@
       <c r="BF59" s="11"/>
       <c r="BG59" s="11"/>
       <c r="BH59" s="11"/>
-      <c r="BI59" s="51"/>
+      <c r="BI59" s="12"/>
       <c r="BJ59" s="1"/>
       <c r="BK59" s="1"/>
       <c r="BL59" s="1"/>
@@ -19455,7 +19498,6 @@
       <c r="Q60" s="13"/>
       <c r="R60" s="25"/>
       <c r="S60" s="13"/>
-      <c r="U60" s="13"/>
       <c r="V60" s="13"/>
       <c r="W60" s="13"/>
       <c r="X60" s="13"/>
@@ -19493,7 +19535,7 @@
       <c r="BF60" s="11"/>
       <c r="BG60" s="11"/>
       <c r="BH60" s="11"/>
-      <c r="BI60" s="51"/>
+      <c r="BI60" s="12"/>
       <c r="BJ60" s="1"/>
       <c r="BK60" s="1"/>
       <c r="BL60" s="1"/>
@@ -19750,7 +19792,7 @@
       <c r="BF61" s="11"/>
       <c r="BG61" s="11"/>
       <c r="BH61" s="11"/>
-      <c r="BI61" s="51"/>
+      <c r="BI61" s="12"/>
       <c r="BJ61" s="1"/>
       <c r="BK61" s="1"/>
       <c r="BL61" s="1"/>
@@ -21749,7 +21791,20 @@
       <c r="IX68" s="1"/>
     </row>
     <row r="69" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
+      <c r="A69" s="39"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
       <c r="O69" s="36"/>
       <c r="P69" s="13"/>
       <c r="Q69" s="13"/>
@@ -21781,265 +21836,1405 @@
       <c r="AR69" s="13"/>
       <c r="AS69" s="13"/>
       <c r="AT69" s="8"/>
+      <c r="AW69" s="10"/>
+      <c r="AX69" s="11"/>
+      <c r="AY69" s="11"/>
+      <c r="AZ69" s="11"/>
+      <c r="BA69" s="11"/>
+      <c r="BB69" s="11"/>
+      <c r="BC69" s="11"/>
+      <c r="BD69" s="11"/>
+      <c r="BE69" s="11"/>
+      <c r="BF69" s="11"/>
+      <c r="BG69" s="11"/>
+      <c r="BH69" s="11"/>
+      <c r="BI69" s="51"/>
+      <c r="BJ69" s="1"/>
+      <c r="BK69" s="1"/>
+      <c r="BL69" s="1"/>
+      <c r="BM69" s="1"/>
+      <c r="BN69" s="1"/>
+      <c r="BO69" s="1"/>
+      <c r="BP69" s="1"/>
+      <c r="BQ69" s="1"/>
+      <c r="BR69" s="1"/>
+      <c r="BS69" s="1"/>
+      <c r="BT69" s="1"/>
+      <c r="BU69" s="1"/>
+      <c r="BV69" s="1"/>
+      <c r="BW69" s="1"/>
+      <c r="BX69" s="1"/>
+      <c r="BY69" s="1"/>
+      <c r="BZ69" s="1"/>
+      <c r="CA69" s="1"/>
+      <c r="CB69" s="1"/>
+      <c r="CC69" s="1"/>
+      <c r="CD69" s="1"/>
+      <c r="CE69" s="1"/>
+      <c r="CF69" s="1"/>
+      <c r="CG69" s="1"/>
+      <c r="CH69" s="1"/>
+      <c r="CI69" s="1"/>
+      <c r="CJ69" s="1"/>
+      <c r="CK69" s="1"/>
+      <c r="CL69" s="1"/>
+      <c r="CM69" s="1"/>
+      <c r="CN69" s="1"/>
+      <c r="CO69" s="1"/>
+      <c r="CP69" s="1"/>
+      <c r="CQ69" s="1"/>
+      <c r="CR69" s="1"/>
+      <c r="CS69" s="1"/>
+      <c r="CT69" s="1"/>
+      <c r="CU69" s="1"/>
+      <c r="CV69" s="1"/>
+      <c r="CW69" s="1"/>
+      <c r="CX69" s="1"/>
+      <c r="CY69" s="1"/>
+      <c r="CZ69" s="1"/>
+      <c r="DA69" s="1"/>
+      <c r="DB69" s="1"/>
+      <c r="DC69" s="1"/>
+      <c r="DD69" s="1"/>
+      <c r="DE69" s="1"/>
+      <c r="DF69" s="1"/>
+      <c r="DG69" s="1"/>
+      <c r="DH69" s="1"/>
+      <c r="DI69" s="1"/>
+      <c r="DJ69" s="1"/>
+      <c r="DK69" s="1"/>
+      <c r="DL69" s="1"/>
+      <c r="DM69" s="1"/>
+      <c r="DN69" s="1"/>
+      <c r="DO69" s="1"/>
+      <c r="DP69" s="1"/>
+      <c r="DQ69" s="1"/>
+      <c r="DR69" s="1"/>
+      <c r="DS69" s="1"/>
+      <c r="DT69" s="1"/>
+      <c r="DU69" s="1"/>
+      <c r="DV69" s="1"/>
+      <c r="DW69" s="1"/>
+      <c r="DX69" s="1"/>
+      <c r="DY69" s="1"/>
+      <c r="DZ69" s="1"/>
+      <c r="EA69" s="1"/>
+      <c r="EB69" s="1"/>
+      <c r="EC69" s="1"/>
+      <c r="ED69" s="1"/>
+      <c r="EE69" s="1"/>
+      <c r="EF69" s="1"/>
+      <c r="EG69" s="1"/>
+      <c r="EH69" s="1"/>
+      <c r="EI69" s="1"/>
+      <c r="EJ69" s="1"/>
+      <c r="EK69" s="1"/>
+      <c r="EL69" s="1"/>
+      <c r="EM69" s="1"/>
+      <c r="EN69" s="1"/>
+      <c r="EO69" s="1"/>
+      <c r="EP69" s="1"/>
+      <c r="EQ69" s="1"/>
+      <c r="ER69" s="1"/>
+      <c r="ES69" s="1"/>
+      <c r="ET69" s="1"/>
+      <c r="EU69" s="1"/>
+      <c r="EV69" s="1"/>
+      <c r="EW69" s="1"/>
+      <c r="EX69" s="1"/>
+      <c r="EY69" s="1"/>
+      <c r="EZ69" s="1"/>
+      <c r="FA69" s="1"/>
+      <c r="FB69" s="1"/>
+      <c r="FC69" s="1"/>
+      <c r="FD69" s="1"/>
+      <c r="FE69" s="1"/>
+      <c r="FF69" s="1"/>
+      <c r="FG69" s="1"/>
+      <c r="FH69" s="1"/>
+      <c r="FI69" s="1"/>
+      <c r="FJ69" s="1"/>
+      <c r="FK69" s="1"/>
+      <c r="FL69" s="1"/>
+      <c r="FM69" s="1"/>
+      <c r="FN69" s="1"/>
+      <c r="FO69" s="1"/>
+      <c r="FP69" s="1"/>
+      <c r="FQ69" s="1"/>
+      <c r="FR69" s="1"/>
+      <c r="FS69" s="1"/>
+      <c r="FT69" s="1"/>
+      <c r="FU69" s="1"/>
+      <c r="FV69" s="1"/>
+      <c r="FW69" s="1"/>
+      <c r="FX69" s="1"/>
+      <c r="FY69" s="1"/>
+      <c r="FZ69" s="1"/>
+      <c r="GA69" s="1"/>
+      <c r="GB69" s="1"/>
+      <c r="GC69" s="1"/>
+      <c r="GD69" s="1"/>
+      <c r="GE69" s="1"/>
+      <c r="GF69" s="1"/>
+      <c r="GG69" s="1"/>
+      <c r="GH69" s="1"/>
+      <c r="GI69" s="1"/>
+      <c r="GJ69" s="1"/>
+      <c r="GK69" s="1"/>
+      <c r="GL69" s="1"/>
+      <c r="GM69" s="1"/>
+      <c r="GN69" s="1"/>
+      <c r="GO69" s="1"/>
+      <c r="GP69" s="1"/>
+      <c r="GQ69" s="1"/>
+      <c r="GR69" s="1"/>
+      <c r="GS69" s="1"/>
+      <c r="GT69" s="1"/>
+      <c r="GU69" s="1"/>
+      <c r="GV69" s="1"/>
+      <c r="GW69" s="1"/>
+      <c r="GX69" s="1"/>
+      <c r="GY69" s="1"/>
+      <c r="GZ69" s="1"/>
+      <c r="HA69" s="1"/>
+      <c r="HB69" s="1"/>
+      <c r="HC69" s="1"/>
+      <c r="HD69" s="1"/>
+      <c r="HE69" s="1"/>
+      <c r="HF69" s="1"/>
+      <c r="HG69" s="1"/>
+      <c r="HH69" s="1"/>
+      <c r="HI69" s="1"/>
+      <c r="HJ69" s="1"/>
+      <c r="HK69" s="1"/>
+      <c r="HL69" s="1"/>
+      <c r="HM69" s="1"/>
+      <c r="HN69" s="1"/>
+      <c r="HO69" s="1"/>
+      <c r="HP69" s="1"/>
+      <c r="HQ69" s="1"/>
+      <c r="HR69" s="1"/>
+      <c r="HS69" s="1"/>
+      <c r="HT69" s="1"/>
+      <c r="HU69" s="1"/>
+      <c r="HV69" s="1"/>
+      <c r="HW69" s="1"/>
+      <c r="HX69" s="1"/>
+      <c r="HY69" s="1"/>
+      <c r="HZ69" s="1"/>
+      <c r="IA69" s="1"/>
+      <c r="IB69" s="1"/>
+      <c r="IC69" s="1"/>
+      <c r="ID69" s="1"/>
+      <c r="IE69" s="1"/>
+      <c r="IF69" s="1"/>
+      <c r="IG69" s="1"/>
+      <c r="IH69" s="1"/>
+      <c r="II69" s="1"/>
+      <c r="IJ69" s="1"/>
+      <c r="IK69" s="1"/>
+      <c r="IL69" s="1"/>
+      <c r="IM69" s="1"/>
+      <c r="IN69" s="1"/>
+      <c r="IO69" s="1"/>
+      <c r="IP69" s="1"/>
+      <c r="IQ69" s="1"/>
+      <c r="IR69" s="1"/>
+      <c r="IS69" s="1"/>
+      <c r="IT69" s="1"/>
+      <c r="IU69" s="1"/>
+      <c r="IV69" s="1"/>
+      <c r="IW69" s="1"/>
+      <c r="IX69" s="1"/>
     </row>
     <row r="70" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="28"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
       <c r="O70" s="36"/>
-      <c r="P70" s="20"/>
-      <c r="Q70" s="20"/>
+      <c r="P70" s="13"/>
+      <c r="Q70" s="13"/>
       <c r="R70" s="25"/>
-      <c r="S70" s="20"/>
-      <c r="T70" s="43"/>
-      <c r="V70" s="20"/>
-      <c r="W70" s="20"/>
-      <c r="X70" s="20"/>
-      <c r="Y70" s="20"/>
-      <c r="Z70" s="20"/>
-      <c r="AA70" s="20"/>
-      <c r="AB70" s="20"/>
-      <c r="AC70" s="20"/>
-      <c r="AD70" s="20"/>
-      <c r="AE70" s="20"/>
-      <c r="AF70" s="20"/>
-      <c r="AG70" s="20"/>
-      <c r="AH70" s="20"/>
-      <c r="AI70" s="20"/>
-      <c r="AJ70" s="20"/>
-      <c r="AK70" s="20"/>
-      <c r="AL70" s="20"/>
-      <c r="AM70" s="20"/>
-      <c r="AN70" s="20"/>
-      <c r="AO70" s="20"/>
-      <c r="AP70" s="20"/>
-      <c r="AQ70" s="20"/>
-      <c r="AR70" s="20"/>
-      <c r="AS70" s="38"/>
+      <c r="S70" s="13"/>
+      <c r="U70" s="13"/>
+      <c r="V70" s="13"/>
+      <c r="W70" s="13"/>
+      <c r="X70" s="13"/>
+      <c r="Y70" s="13"/>
+      <c r="Z70" s="13"/>
+      <c r="AA70" s="13"/>
+      <c r="AB70" s="13"/>
+      <c r="AC70" s="13"/>
+      <c r="AD70" s="13"/>
+      <c r="AE70" s="13"/>
+      <c r="AF70" s="13"/>
+      <c r="AG70" s="13"/>
+      <c r="AH70" s="13"/>
+      <c r="AI70" s="13"/>
+      <c r="AJ70" s="13"/>
+      <c r="AK70" s="13"/>
+      <c r="AL70" s="13"/>
+      <c r="AM70" s="13"/>
+      <c r="AN70" s="13"/>
+      <c r="AO70" s="13"/>
+      <c r="AP70" s="13"/>
+      <c r="AQ70" s="13"/>
+      <c r="AR70" s="13"/>
+      <c r="AS70" s="13"/>
       <c r="AT70" s="8"/>
+      <c r="AW70" s="10"/>
+      <c r="AX70" s="11"/>
+      <c r="AY70" s="11"/>
+      <c r="AZ70" s="11"/>
+      <c r="BA70" s="11"/>
+      <c r="BB70" s="11"/>
+      <c r="BC70" s="11"/>
+      <c r="BD70" s="11"/>
+      <c r="BE70" s="11"/>
+      <c r="BF70" s="11"/>
+      <c r="BG70" s="11"/>
+      <c r="BH70" s="11"/>
+      <c r="BI70" s="51"/>
+      <c r="BJ70" s="1"/>
+      <c r="BK70" s="1"/>
+      <c r="BL70" s="1"/>
+      <c r="BM70" s="1"/>
+      <c r="BN70" s="1"/>
+      <c r="BO70" s="1"/>
+      <c r="BP70" s="1"/>
+      <c r="BQ70" s="1"/>
+      <c r="BR70" s="1"/>
+      <c r="BS70" s="1"/>
+      <c r="BT70" s="1"/>
+      <c r="BU70" s="1"/>
+      <c r="BV70" s="1"/>
+      <c r="BW70" s="1"/>
+      <c r="BX70" s="1"/>
+      <c r="BY70" s="1"/>
+      <c r="BZ70" s="1"/>
+      <c r="CA70" s="1"/>
+      <c r="CB70" s="1"/>
+      <c r="CC70" s="1"/>
+      <c r="CD70" s="1"/>
+      <c r="CE70" s="1"/>
+      <c r="CF70" s="1"/>
+      <c r="CG70" s="1"/>
+      <c r="CH70" s="1"/>
+      <c r="CI70" s="1"/>
+      <c r="CJ70" s="1"/>
+      <c r="CK70" s="1"/>
+      <c r="CL70" s="1"/>
+      <c r="CM70" s="1"/>
+      <c r="CN70" s="1"/>
+      <c r="CO70" s="1"/>
+      <c r="CP70" s="1"/>
+      <c r="CQ70" s="1"/>
+      <c r="CR70" s="1"/>
+      <c r="CS70" s="1"/>
+      <c r="CT70" s="1"/>
+      <c r="CU70" s="1"/>
+      <c r="CV70" s="1"/>
+      <c r="CW70" s="1"/>
+      <c r="CX70" s="1"/>
+      <c r="CY70" s="1"/>
+      <c r="CZ70" s="1"/>
+      <c r="DA70" s="1"/>
+      <c r="DB70" s="1"/>
+      <c r="DC70" s="1"/>
+      <c r="DD70" s="1"/>
+      <c r="DE70" s="1"/>
+      <c r="DF70" s="1"/>
+      <c r="DG70" s="1"/>
+      <c r="DH70" s="1"/>
+      <c r="DI70" s="1"/>
+      <c r="DJ70" s="1"/>
+      <c r="DK70" s="1"/>
+      <c r="DL70" s="1"/>
+      <c r="DM70" s="1"/>
+      <c r="DN70" s="1"/>
+      <c r="DO70" s="1"/>
+      <c r="DP70" s="1"/>
+      <c r="DQ70" s="1"/>
+      <c r="DR70" s="1"/>
+      <c r="DS70" s="1"/>
+      <c r="DT70" s="1"/>
+      <c r="DU70" s="1"/>
+      <c r="DV70" s="1"/>
+      <c r="DW70" s="1"/>
+      <c r="DX70" s="1"/>
+      <c r="DY70" s="1"/>
+      <c r="DZ70" s="1"/>
+      <c r="EA70" s="1"/>
+      <c r="EB70" s="1"/>
+      <c r="EC70" s="1"/>
+      <c r="ED70" s="1"/>
+      <c r="EE70" s="1"/>
+      <c r="EF70" s="1"/>
+      <c r="EG70" s="1"/>
+      <c r="EH70" s="1"/>
+      <c r="EI70" s="1"/>
+      <c r="EJ70" s="1"/>
+      <c r="EK70" s="1"/>
+      <c r="EL70" s="1"/>
+      <c r="EM70" s="1"/>
+      <c r="EN70" s="1"/>
+      <c r="EO70" s="1"/>
+      <c r="EP70" s="1"/>
+      <c r="EQ70" s="1"/>
+      <c r="ER70" s="1"/>
+      <c r="ES70" s="1"/>
+      <c r="ET70" s="1"/>
+      <c r="EU70" s="1"/>
+      <c r="EV70" s="1"/>
+      <c r="EW70" s="1"/>
+      <c r="EX70" s="1"/>
+      <c r="EY70" s="1"/>
+      <c r="EZ70" s="1"/>
+      <c r="FA70" s="1"/>
+      <c r="FB70" s="1"/>
+      <c r="FC70" s="1"/>
+      <c r="FD70" s="1"/>
+      <c r="FE70" s="1"/>
+      <c r="FF70" s="1"/>
+      <c r="FG70" s="1"/>
+      <c r="FH70" s="1"/>
+      <c r="FI70" s="1"/>
+      <c r="FJ70" s="1"/>
+      <c r="FK70" s="1"/>
+      <c r="FL70" s="1"/>
+      <c r="FM70" s="1"/>
+      <c r="FN70" s="1"/>
+      <c r="FO70" s="1"/>
+      <c r="FP70" s="1"/>
+      <c r="FQ70" s="1"/>
+      <c r="FR70" s="1"/>
+      <c r="FS70" s="1"/>
+      <c r="FT70" s="1"/>
+      <c r="FU70" s="1"/>
+      <c r="FV70" s="1"/>
+      <c r="FW70" s="1"/>
+      <c r="FX70" s="1"/>
+      <c r="FY70" s="1"/>
+      <c r="FZ70" s="1"/>
+      <c r="GA70" s="1"/>
+      <c r="GB70" s="1"/>
+      <c r="GC70" s="1"/>
+      <c r="GD70" s="1"/>
+      <c r="GE70" s="1"/>
+      <c r="GF70" s="1"/>
+      <c r="GG70" s="1"/>
+      <c r="GH70" s="1"/>
+      <c r="GI70" s="1"/>
+      <c r="GJ70" s="1"/>
+      <c r="GK70" s="1"/>
+      <c r="GL70" s="1"/>
+      <c r="GM70" s="1"/>
+      <c r="GN70" s="1"/>
+      <c r="GO70" s="1"/>
+      <c r="GP70" s="1"/>
+      <c r="GQ70" s="1"/>
+      <c r="GR70" s="1"/>
+      <c r="GS70" s="1"/>
+      <c r="GT70" s="1"/>
+      <c r="GU70" s="1"/>
+      <c r="GV70" s="1"/>
+      <c r="GW70" s="1"/>
+      <c r="GX70" s="1"/>
+      <c r="GY70" s="1"/>
+      <c r="GZ70" s="1"/>
+      <c r="HA70" s="1"/>
+      <c r="HB70" s="1"/>
+      <c r="HC70" s="1"/>
+      <c r="HD70" s="1"/>
+      <c r="HE70" s="1"/>
+      <c r="HF70" s="1"/>
+      <c r="HG70" s="1"/>
+      <c r="HH70" s="1"/>
+      <c r="HI70" s="1"/>
+      <c r="HJ70" s="1"/>
+      <c r="HK70" s="1"/>
+      <c r="HL70" s="1"/>
+      <c r="HM70" s="1"/>
+      <c r="HN70" s="1"/>
+      <c r="HO70" s="1"/>
+      <c r="HP70" s="1"/>
+      <c r="HQ70" s="1"/>
+      <c r="HR70" s="1"/>
+      <c r="HS70" s="1"/>
+      <c r="HT70" s="1"/>
+      <c r="HU70" s="1"/>
+      <c r="HV70" s="1"/>
+      <c r="HW70" s="1"/>
+      <c r="HX70" s="1"/>
+      <c r="HY70" s="1"/>
+      <c r="HZ70" s="1"/>
+      <c r="IA70" s="1"/>
+      <c r="IB70" s="1"/>
+      <c r="IC70" s="1"/>
+      <c r="ID70" s="1"/>
+      <c r="IE70" s="1"/>
+      <c r="IF70" s="1"/>
+      <c r="IG70" s="1"/>
+      <c r="IH70" s="1"/>
+      <c r="II70" s="1"/>
+      <c r="IJ70" s="1"/>
+      <c r="IK70" s="1"/>
+      <c r="IL70" s="1"/>
+      <c r="IM70" s="1"/>
+      <c r="IN70" s="1"/>
+      <c r="IO70" s="1"/>
+      <c r="IP70" s="1"/>
+      <c r="IQ70" s="1"/>
+      <c r="IR70" s="1"/>
+      <c r="IS70" s="1"/>
+      <c r="IT70" s="1"/>
+      <c r="IU70" s="1"/>
+      <c r="IV70" s="1"/>
+      <c r="IW70" s="1"/>
+      <c r="IX70" s="1"/>
     </row>
     <row r="71" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="28"/>
-      <c r="O71" s="40"/>
-      <c r="P71" s="16"/>
-      <c r="Q71" s="16"/>
-      <c r="R71" s="26"/>
-      <c r="S71" s="16"/>
-      <c r="T71" s="23"/>
-      <c r="V71" s="16"/>
-      <c r="W71" s="16"/>
-      <c r="X71" s="16"/>
-      <c r="Y71" s="16"/>
-      <c r="Z71" s="16"/>
-      <c r="AA71" s="16"/>
-      <c r="AB71" s="16"/>
-      <c r="AC71" s="16"/>
-      <c r="AD71" s="16"/>
-      <c r="AE71" s="16"/>
-      <c r="AF71" s="16"/>
-      <c r="AG71" s="16"/>
-      <c r="AH71" s="16"/>
-      <c r="AI71" s="16"/>
-      <c r="AJ71" s="16"/>
-      <c r="AK71" s="16"/>
-      <c r="AL71" s="16"/>
-      <c r="AM71" s="16"/>
-      <c r="AN71" s="16"/>
-      <c r="AO71" s="16"/>
-      <c r="AP71" s="16"/>
-      <c r="AQ71" s="16"/>
-      <c r="AR71" s="16"/>
-      <c r="AS71" s="19"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="36"/>
+      <c r="P71" s="13"/>
+      <c r="Q71" s="13"/>
+      <c r="R71" s="25"/>
+      <c r="S71" s="13"/>
+      <c r="U71" s="13"/>
+      <c r="V71" s="13"/>
+      <c r="W71" s="13"/>
+      <c r="X71" s="13"/>
+      <c r="Y71" s="13"/>
+      <c r="Z71" s="13"/>
+      <c r="AA71" s="13"/>
+      <c r="AB71" s="13"/>
+      <c r="AC71" s="13"/>
+      <c r="AD71" s="13"/>
+      <c r="AE71" s="13"/>
+      <c r="AF71" s="13"/>
+      <c r="AG71" s="13"/>
+      <c r="AH71" s="13"/>
+      <c r="AI71" s="13"/>
+      <c r="AJ71" s="13"/>
+      <c r="AK71" s="13"/>
+      <c r="AL71" s="13"/>
+      <c r="AM71" s="13"/>
+      <c r="AN71" s="13"/>
+      <c r="AO71" s="13"/>
+      <c r="AP71" s="13"/>
+      <c r="AQ71" s="13"/>
+      <c r="AR71" s="13"/>
+      <c r="AS71" s="13"/>
       <c r="AT71" s="8"/>
+      <c r="AW71" s="10"/>
+      <c r="AX71" s="11"/>
+      <c r="AY71" s="11"/>
+      <c r="AZ71" s="11"/>
+      <c r="BA71" s="11"/>
+      <c r="BB71" s="11"/>
+      <c r="BC71" s="11"/>
+      <c r="BD71" s="11"/>
+      <c r="BE71" s="11"/>
+      <c r="BF71" s="11"/>
+      <c r="BG71" s="11"/>
+      <c r="BH71" s="11"/>
+      <c r="BI71" s="51"/>
+      <c r="BJ71" s="1"/>
+      <c r="BK71" s="1"/>
+      <c r="BL71" s="1"/>
+      <c r="BM71" s="1"/>
+      <c r="BN71" s="1"/>
+      <c r="BO71" s="1"/>
+      <c r="BP71" s="1"/>
+      <c r="BQ71" s="1"/>
+      <c r="BR71" s="1"/>
+      <c r="BS71" s="1"/>
+      <c r="BT71" s="1"/>
+      <c r="BU71" s="1"/>
+      <c r="BV71" s="1"/>
+      <c r="BW71" s="1"/>
+      <c r="BX71" s="1"/>
+      <c r="BY71" s="1"/>
+      <c r="BZ71" s="1"/>
+      <c r="CA71" s="1"/>
+      <c r="CB71" s="1"/>
+      <c r="CC71" s="1"/>
+      <c r="CD71" s="1"/>
+      <c r="CE71" s="1"/>
+      <c r="CF71" s="1"/>
+      <c r="CG71" s="1"/>
+      <c r="CH71" s="1"/>
+      <c r="CI71" s="1"/>
+      <c r="CJ71" s="1"/>
+      <c r="CK71" s="1"/>
+      <c r="CL71" s="1"/>
+      <c r="CM71" s="1"/>
+      <c r="CN71" s="1"/>
+      <c r="CO71" s="1"/>
+      <c r="CP71" s="1"/>
+      <c r="CQ71" s="1"/>
+      <c r="CR71" s="1"/>
+      <c r="CS71" s="1"/>
+      <c r="CT71" s="1"/>
+      <c r="CU71" s="1"/>
+      <c r="CV71" s="1"/>
+      <c r="CW71" s="1"/>
+      <c r="CX71" s="1"/>
+      <c r="CY71" s="1"/>
+      <c r="CZ71" s="1"/>
+      <c r="DA71" s="1"/>
+      <c r="DB71" s="1"/>
+      <c r="DC71" s="1"/>
+      <c r="DD71" s="1"/>
+      <c r="DE71" s="1"/>
+      <c r="DF71" s="1"/>
+      <c r="DG71" s="1"/>
+      <c r="DH71" s="1"/>
+      <c r="DI71" s="1"/>
+      <c r="DJ71" s="1"/>
+      <c r="DK71" s="1"/>
+      <c r="DL71" s="1"/>
+      <c r="DM71" s="1"/>
+      <c r="DN71" s="1"/>
+      <c r="DO71" s="1"/>
+      <c r="DP71" s="1"/>
+      <c r="DQ71" s="1"/>
+      <c r="DR71" s="1"/>
+      <c r="DS71" s="1"/>
+      <c r="DT71" s="1"/>
+      <c r="DU71" s="1"/>
+      <c r="DV71" s="1"/>
+      <c r="DW71" s="1"/>
+      <c r="DX71" s="1"/>
+      <c r="DY71" s="1"/>
+      <c r="DZ71" s="1"/>
+      <c r="EA71" s="1"/>
+      <c r="EB71" s="1"/>
+      <c r="EC71" s="1"/>
+      <c r="ED71" s="1"/>
+      <c r="EE71" s="1"/>
+      <c r="EF71" s="1"/>
+      <c r="EG71" s="1"/>
+      <c r="EH71" s="1"/>
+      <c r="EI71" s="1"/>
+      <c r="EJ71" s="1"/>
+      <c r="EK71" s="1"/>
+      <c r="EL71" s="1"/>
+      <c r="EM71" s="1"/>
+      <c r="EN71" s="1"/>
+      <c r="EO71" s="1"/>
+      <c r="EP71" s="1"/>
+      <c r="EQ71" s="1"/>
+      <c r="ER71" s="1"/>
+      <c r="ES71" s="1"/>
+      <c r="ET71" s="1"/>
+      <c r="EU71" s="1"/>
+      <c r="EV71" s="1"/>
+      <c r="EW71" s="1"/>
+      <c r="EX71" s="1"/>
+      <c r="EY71" s="1"/>
+      <c r="EZ71" s="1"/>
+      <c r="FA71" s="1"/>
+      <c r="FB71" s="1"/>
+      <c r="FC71" s="1"/>
+      <c r="FD71" s="1"/>
+      <c r="FE71" s="1"/>
+      <c r="FF71" s="1"/>
+      <c r="FG71" s="1"/>
+      <c r="FH71" s="1"/>
+      <c r="FI71" s="1"/>
+      <c r="FJ71" s="1"/>
+      <c r="FK71" s="1"/>
+      <c r="FL71" s="1"/>
+      <c r="FM71" s="1"/>
+      <c r="FN71" s="1"/>
+      <c r="FO71" s="1"/>
+      <c r="FP71" s="1"/>
+      <c r="FQ71" s="1"/>
+      <c r="FR71" s="1"/>
+      <c r="FS71" s="1"/>
+      <c r="FT71" s="1"/>
+      <c r="FU71" s="1"/>
+      <c r="FV71" s="1"/>
+      <c r="FW71" s="1"/>
+      <c r="FX71" s="1"/>
+      <c r="FY71" s="1"/>
+      <c r="FZ71" s="1"/>
+      <c r="GA71" s="1"/>
+      <c r="GB71" s="1"/>
+      <c r="GC71" s="1"/>
+      <c r="GD71" s="1"/>
+      <c r="GE71" s="1"/>
+      <c r="GF71" s="1"/>
+      <c r="GG71" s="1"/>
+      <c r="GH71" s="1"/>
+      <c r="GI71" s="1"/>
+      <c r="GJ71" s="1"/>
+      <c r="GK71" s="1"/>
+      <c r="GL71" s="1"/>
+      <c r="GM71" s="1"/>
+      <c r="GN71" s="1"/>
+      <c r="GO71" s="1"/>
+      <c r="GP71" s="1"/>
+      <c r="GQ71" s="1"/>
+      <c r="GR71" s="1"/>
+      <c r="GS71" s="1"/>
+      <c r="GT71" s="1"/>
+      <c r="GU71" s="1"/>
+      <c r="GV71" s="1"/>
+      <c r="GW71" s="1"/>
+      <c r="GX71" s="1"/>
+      <c r="GY71" s="1"/>
+      <c r="GZ71" s="1"/>
+      <c r="HA71" s="1"/>
+      <c r="HB71" s="1"/>
+      <c r="HC71" s="1"/>
+      <c r="HD71" s="1"/>
+      <c r="HE71" s="1"/>
+      <c r="HF71" s="1"/>
+      <c r="HG71" s="1"/>
+      <c r="HH71" s="1"/>
+      <c r="HI71" s="1"/>
+      <c r="HJ71" s="1"/>
+      <c r="HK71" s="1"/>
+      <c r="HL71" s="1"/>
+      <c r="HM71" s="1"/>
+      <c r="HN71" s="1"/>
+      <c r="HO71" s="1"/>
+      <c r="HP71" s="1"/>
+      <c r="HQ71" s="1"/>
+      <c r="HR71" s="1"/>
+      <c r="HS71" s="1"/>
+      <c r="HT71" s="1"/>
+      <c r="HU71" s="1"/>
+      <c r="HV71" s="1"/>
+      <c r="HW71" s="1"/>
+      <c r="HX71" s="1"/>
+      <c r="HY71" s="1"/>
+      <c r="HZ71" s="1"/>
+      <c r="IA71" s="1"/>
+      <c r="IB71" s="1"/>
+      <c r="IC71" s="1"/>
+      <c r="ID71" s="1"/>
+      <c r="IE71" s="1"/>
+      <c r="IF71" s="1"/>
+      <c r="IG71" s="1"/>
+      <c r="IH71" s="1"/>
+      <c r="II71" s="1"/>
+      <c r="IJ71" s="1"/>
+      <c r="IK71" s="1"/>
+      <c r="IL71" s="1"/>
+      <c r="IM71" s="1"/>
+      <c r="IN71" s="1"/>
+      <c r="IO71" s="1"/>
+      <c r="IP71" s="1"/>
+      <c r="IQ71" s="1"/>
+      <c r="IR71" s="1"/>
+      <c r="IS71" s="1"/>
+      <c r="IT71" s="1"/>
+      <c r="IU71" s="1"/>
+      <c r="IV71" s="1"/>
+      <c r="IW71" s="1"/>
+      <c r="IX71" s="1"/>
     </row>
     <row r="72" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="28"/>
-      <c r="O72" s="41">
-        <v>6</v>
-      </c>
-      <c r="P72" s="20"/>
-      <c r="Q72" s="20"/>
+      <c r="A72" s="39"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="36"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
       <c r="R72" s="25"/>
-      <c r="S72" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="T72" s="43"/>
-      <c r="U72" s="46"/>
-      <c r="V72" s="20"/>
-      <c r="W72" s="20"/>
-      <c r="X72" s="20"/>
-      <c r="Y72" s="20"/>
-      <c r="Z72" s="20"/>
-      <c r="AA72" s="20"/>
-      <c r="AB72" s="20"/>
-      <c r="AC72" s="20"/>
-      <c r="AD72" s="20"/>
-      <c r="AE72" s="20"/>
-      <c r="AF72" s="20"/>
-      <c r="AG72" s="20"/>
-      <c r="AH72" s="20"/>
-      <c r="AI72" s="20"/>
-      <c r="AJ72" s="20"/>
-      <c r="AK72" s="20"/>
-      <c r="AL72" s="20"/>
-      <c r="AM72" s="20"/>
-      <c r="AN72" s="20"/>
-      <c r="AO72" s="20"/>
-      <c r="AP72" s="20"/>
-      <c r="AQ72" s="20"/>
-      <c r="AR72" s="20"/>
-      <c r="AS72" s="20"/>
+      <c r="S72" s="13"/>
+      <c r="U72" s="13"/>
+      <c r="V72" s="13"/>
+      <c r="W72" s="13"/>
+      <c r="X72" s="13"/>
+      <c r="Y72" s="13"/>
+      <c r="Z72" s="13"/>
+      <c r="AA72" s="13"/>
+      <c r="AB72" s="13"/>
+      <c r="AC72" s="13"/>
+      <c r="AD72" s="13"/>
+      <c r="AE72" s="13"/>
+      <c r="AF72" s="13"/>
+      <c r="AG72" s="13"/>
+      <c r="AH72" s="13"/>
+      <c r="AI72" s="13"/>
+      <c r="AJ72" s="13"/>
+      <c r="AK72" s="13"/>
+      <c r="AL72" s="13"/>
+      <c r="AM72" s="13"/>
+      <c r="AN72" s="13"/>
+      <c r="AO72" s="13"/>
+      <c r="AP72" s="13"/>
+      <c r="AQ72" s="13"/>
+      <c r="AR72" s="13"/>
+      <c r="AS72" s="13"/>
       <c r="AT72" s="8"/>
+      <c r="AW72" s="10"/>
+      <c r="AX72" s="11"/>
+      <c r="AY72" s="11"/>
+      <c r="AZ72" s="11"/>
+      <c r="BA72" s="11"/>
+      <c r="BB72" s="11"/>
+      <c r="BC72" s="11"/>
+      <c r="BD72" s="11"/>
+      <c r="BE72" s="11"/>
+      <c r="BF72" s="11"/>
+      <c r="BG72" s="11"/>
+      <c r="BH72" s="11"/>
+      <c r="BI72" s="51"/>
+      <c r="BJ72" s="1"/>
+      <c r="BK72" s="1"/>
+      <c r="BL72" s="1"/>
+      <c r="BM72" s="1"/>
+      <c r="BN72" s="1"/>
+      <c r="BO72" s="1"/>
+      <c r="BP72" s="1"/>
+      <c r="BQ72" s="1"/>
+      <c r="BR72" s="1"/>
+      <c r="BS72" s="1"/>
+      <c r="BT72" s="1"/>
+      <c r="BU72" s="1"/>
+      <c r="BV72" s="1"/>
+      <c r="BW72" s="1"/>
+      <c r="BX72" s="1"/>
+      <c r="BY72" s="1"/>
+      <c r="BZ72" s="1"/>
+      <c r="CA72" s="1"/>
+      <c r="CB72" s="1"/>
+      <c r="CC72" s="1"/>
+      <c r="CD72" s="1"/>
+      <c r="CE72" s="1"/>
+      <c r="CF72" s="1"/>
+      <c r="CG72" s="1"/>
+      <c r="CH72" s="1"/>
+      <c r="CI72" s="1"/>
+      <c r="CJ72" s="1"/>
+      <c r="CK72" s="1"/>
+      <c r="CL72" s="1"/>
+      <c r="CM72" s="1"/>
+      <c r="CN72" s="1"/>
+      <c r="CO72" s="1"/>
+      <c r="CP72" s="1"/>
+      <c r="CQ72" s="1"/>
+      <c r="CR72" s="1"/>
+      <c r="CS72" s="1"/>
+      <c r="CT72" s="1"/>
+      <c r="CU72" s="1"/>
+      <c r="CV72" s="1"/>
+      <c r="CW72" s="1"/>
+      <c r="CX72" s="1"/>
+      <c r="CY72" s="1"/>
+      <c r="CZ72" s="1"/>
+      <c r="DA72" s="1"/>
+      <c r="DB72" s="1"/>
+      <c r="DC72" s="1"/>
+      <c r="DD72" s="1"/>
+      <c r="DE72" s="1"/>
+      <c r="DF72" s="1"/>
+      <c r="DG72" s="1"/>
+      <c r="DH72" s="1"/>
+      <c r="DI72" s="1"/>
+      <c r="DJ72" s="1"/>
+      <c r="DK72" s="1"/>
+      <c r="DL72" s="1"/>
+      <c r="DM72" s="1"/>
+      <c r="DN72" s="1"/>
+      <c r="DO72" s="1"/>
+      <c r="DP72" s="1"/>
+      <c r="DQ72" s="1"/>
+      <c r="DR72" s="1"/>
+      <c r="DS72" s="1"/>
+      <c r="DT72" s="1"/>
+      <c r="DU72" s="1"/>
+      <c r="DV72" s="1"/>
+      <c r="DW72" s="1"/>
+      <c r="DX72" s="1"/>
+      <c r="DY72" s="1"/>
+      <c r="DZ72" s="1"/>
+      <c r="EA72" s="1"/>
+      <c r="EB72" s="1"/>
+      <c r="EC72" s="1"/>
+      <c r="ED72" s="1"/>
+      <c r="EE72" s="1"/>
+      <c r="EF72" s="1"/>
+      <c r="EG72" s="1"/>
+      <c r="EH72" s="1"/>
+      <c r="EI72" s="1"/>
+      <c r="EJ72" s="1"/>
+      <c r="EK72" s="1"/>
+      <c r="EL72" s="1"/>
+      <c r="EM72" s="1"/>
+      <c r="EN72" s="1"/>
+      <c r="EO72" s="1"/>
+      <c r="EP72" s="1"/>
+      <c r="EQ72" s="1"/>
+      <c r="ER72" s="1"/>
+      <c r="ES72" s="1"/>
+      <c r="ET72" s="1"/>
+      <c r="EU72" s="1"/>
+      <c r="EV72" s="1"/>
+      <c r="EW72" s="1"/>
+      <c r="EX72" s="1"/>
+      <c r="EY72" s="1"/>
+      <c r="EZ72" s="1"/>
+      <c r="FA72" s="1"/>
+      <c r="FB72" s="1"/>
+      <c r="FC72" s="1"/>
+      <c r="FD72" s="1"/>
+      <c r="FE72" s="1"/>
+      <c r="FF72" s="1"/>
+      <c r="FG72" s="1"/>
+      <c r="FH72" s="1"/>
+      <c r="FI72" s="1"/>
+      <c r="FJ72" s="1"/>
+      <c r="FK72" s="1"/>
+      <c r="FL72" s="1"/>
+      <c r="FM72" s="1"/>
+      <c r="FN72" s="1"/>
+      <c r="FO72" s="1"/>
+      <c r="FP72" s="1"/>
+      <c r="FQ72" s="1"/>
+      <c r="FR72" s="1"/>
+      <c r="FS72" s="1"/>
+      <c r="FT72" s="1"/>
+      <c r="FU72" s="1"/>
+      <c r="FV72" s="1"/>
+      <c r="FW72" s="1"/>
+      <c r="FX72" s="1"/>
+      <c r="FY72" s="1"/>
+      <c r="FZ72" s="1"/>
+      <c r="GA72" s="1"/>
+      <c r="GB72" s="1"/>
+      <c r="GC72" s="1"/>
+      <c r="GD72" s="1"/>
+      <c r="GE72" s="1"/>
+      <c r="GF72" s="1"/>
+      <c r="GG72" s="1"/>
+      <c r="GH72" s="1"/>
+      <c r="GI72" s="1"/>
+      <c r="GJ72" s="1"/>
+      <c r="GK72" s="1"/>
+      <c r="GL72" s="1"/>
+      <c r="GM72" s="1"/>
+      <c r="GN72" s="1"/>
+      <c r="GO72" s="1"/>
+      <c r="GP72" s="1"/>
+      <c r="GQ72" s="1"/>
+      <c r="GR72" s="1"/>
+      <c r="GS72" s="1"/>
+      <c r="GT72" s="1"/>
+      <c r="GU72" s="1"/>
+      <c r="GV72" s="1"/>
+      <c r="GW72" s="1"/>
+      <c r="GX72" s="1"/>
+      <c r="GY72" s="1"/>
+      <c r="GZ72" s="1"/>
+      <c r="HA72" s="1"/>
+      <c r="HB72" s="1"/>
+      <c r="HC72" s="1"/>
+      <c r="HD72" s="1"/>
+      <c r="HE72" s="1"/>
+      <c r="HF72" s="1"/>
+      <c r="HG72" s="1"/>
+      <c r="HH72" s="1"/>
+      <c r="HI72" s="1"/>
+      <c r="HJ72" s="1"/>
+      <c r="HK72" s="1"/>
+      <c r="HL72" s="1"/>
+      <c r="HM72" s="1"/>
+      <c r="HN72" s="1"/>
+      <c r="HO72" s="1"/>
+      <c r="HP72" s="1"/>
+      <c r="HQ72" s="1"/>
+      <c r="HR72" s="1"/>
+      <c r="HS72" s="1"/>
+      <c r="HT72" s="1"/>
+      <c r="HU72" s="1"/>
+      <c r="HV72" s="1"/>
+      <c r="HW72" s="1"/>
+      <c r="HX72" s="1"/>
+      <c r="HY72" s="1"/>
+      <c r="HZ72" s="1"/>
+      <c r="IA72" s="1"/>
+      <c r="IB72" s="1"/>
+      <c r="IC72" s="1"/>
+      <c r="ID72" s="1"/>
+      <c r="IE72" s="1"/>
+      <c r="IF72" s="1"/>
+      <c r="IG72" s="1"/>
+      <c r="IH72" s="1"/>
+      <c r="II72" s="1"/>
+      <c r="IJ72" s="1"/>
+      <c r="IK72" s="1"/>
+      <c r="IL72" s="1"/>
+      <c r="IM72" s="1"/>
+      <c r="IN72" s="1"/>
+      <c r="IO72" s="1"/>
+      <c r="IP72" s="1"/>
+      <c r="IQ72" s="1"/>
+      <c r="IR72" s="1"/>
+      <c r="IS72" s="1"/>
+      <c r="IT72" s="1"/>
+      <c r="IU72" s="1"/>
+      <c r="IV72" s="1"/>
+      <c r="IW72" s="1"/>
+      <c r="IX72" s="1"/>
     </row>
     <row r="73" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="28"/>
-      <c r="O73" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="P73" s="20"/>
-      <c r="Q73" s="20"/>
+      <c r="A73" s="39"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="36"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
       <c r="R73" s="25"/>
-      <c r="S73" s="20"/>
-      <c r="T73" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="U73" s="20"/>
-      <c r="V73" s="20"/>
-      <c r="W73" s="20"/>
-      <c r="X73" s="20"/>
-      <c r="Y73" s="20"/>
-      <c r="Z73" s="20"/>
-      <c r="AA73" s="20"/>
-      <c r="AB73" s="20"/>
-      <c r="AC73" s="20"/>
-      <c r="AD73" s="20"/>
-      <c r="AE73" s="20"/>
-      <c r="AF73" s="20"/>
-      <c r="AG73" s="20"/>
-      <c r="AH73" s="20"/>
-      <c r="AI73" s="20"/>
-      <c r="AJ73" s="20"/>
-      <c r="AK73" s="20"/>
-      <c r="AL73" s="20"/>
-      <c r="AM73" s="20"/>
-      <c r="AN73" s="20"/>
-      <c r="AO73" s="20"/>
-      <c r="AP73" s="20"/>
-      <c r="AQ73" s="20"/>
-      <c r="AR73" s="20"/>
-      <c r="AS73" s="20"/>
+      <c r="S73" s="13"/>
+      <c r="U73" s="13"/>
+      <c r="V73" s="13"/>
+      <c r="W73" s="13"/>
+      <c r="X73" s="13"/>
+      <c r="Y73" s="13"/>
+      <c r="Z73" s="13"/>
+      <c r="AA73" s="13"/>
+      <c r="AB73" s="13"/>
+      <c r="AC73" s="13"/>
+      <c r="AD73" s="13"/>
+      <c r="AE73" s="13"/>
+      <c r="AF73" s="13"/>
+      <c r="AG73" s="13"/>
+      <c r="AH73" s="13"/>
+      <c r="AI73" s="13"/>
+      <c r="AJ73" s="13"/>
+      <c r="AK73" s="13"/>
+      <c r="AL73" s="13"/>
+      <c r="AM73" s="13"/>
+      <c r="AN73" s="13"/>
+      <c r="AO73" s="13"/>
+      <c r="AP73" s="13"/>
+      <c r="AQ73" s="13"/>
+      <c r="AR73" s="13"/>
+      <c r="AS73" s="13"/>
       <c r="AT73" s="8"/>
+      <c r="AW73" s="10"/>
+      <c r="AX73" s="11"/>
+      <c r="AY73" s="11"/>
+      <c r="AZ73" s="11"/>
+      <c r="BA73" s="11"/>
+      <c r="BB73" s="11"/>
+      <c r="BC73" s="11"/>
+      <c r="BD73" s="11"/>
+      <c r="BE73" s="11"/>
+      <c r="BF73" s="11"/>
+      <c r="BG73" s="11"/>
+      <c r="BH73" s="11"/>
+      <c r="BI73" s="51"/>
+      <c r="BJ73" s="1"/>
+      <c r="BK73" s="1"/>
+      <c r="BL73" s="1"/>
+      <c r="BM73" s="1"/>
+      <c r="BN73" s="1"/>
+      <c r="BO73" s="1"/>
+      <c r="BP73" s="1"/>
+      <c r="BQ73" s="1"/>
+      <c r="BR73" s="1"/>
+      <c r="BS73" s="1"/>
+      <c r="BT73" s="1"/>
+      <c r="BU73" s="1"/>
+      <c r="BV73" s="1"/>
+      <c r="BW73" s="1"/>
+      <c r="BX73" s="1"/>
+      <c r="BY73" s="1"/>
+      <c r="BZ73" s="1"/>
+      <c r="CA73" s="1"/>
+      <c r="CB73" s="1"/>
+      <c r="CC73" s="1"/>
+      <c r="CD73" s="1"/>
+      <c r="CE73" s="1"/>
+      <c r="CF73" s="1"/>
+      <c r="CG73" s="1"/>
+      <c r="CH73" s="1"/>
+      <c r="CI73" s="1"/>
+      <c r="CJ73" s="1"/>
+      <c r="CK73" s="1"/>
+      <c r="CL73" s="1"/>
+      <c r="CM73" s="1"/>
+      <c r="CN73" s="1"/>
+      <c r="CO73" s="1"/>
+      <c r="CP73" s="1"/>
+      <c r="CQ73" s="1"/>
+      <c r="CR73" s="1"/>
+      <c r="CS73" s="1"/>
+      <c r="CT73" s="1"/>
+      <c r="CU73" s="1"/>
+      <c r="CV73" s="1"/>
+      <c r="CW73" s="1"/>
+      <c r="CX73" s="1"/>
+      <c r="CY73" s="1"/>
+      <c r="CZ73" s="1"/>
+      <c r="DA73" s="1"/>
+      <c r="DB73" s="1"/>
+      <c r="DC73" s="1"/>
+      <c r="DD73" s="1"/>
+      <c r="DE73" s="1"/>
+      <c r="DF73" s="1"/>
+      <c r="DG73" s="1"/>
+      <c r="DH73" s="1"/>
+      <c r="DI73" s="1"/>
+      <c r="DJ73" s="1"/>
+      <c r="DK73" s="1"/>
+      <c r="DL73" s="1"/>
+      <c r="DM73" s="1"/>
+      <c r="DN73" s="1"/>
+      <c r="DO73" s="1"/>
+      <c r="DP73" s="1"/>
+      <c r="DQ73" s="1"/>
+      <c r="DR73" s="1"/>
+      <c r="DS73" s="1"/>
+      <c r="DT73" s="1"/>
+      <c r="DU73" s="1"/>
+      <c r="DV73" s="1"/>
+      <c r="DW73" s="1"/>
+      <c r="DX73" s="1"/>
+      <c r="DY73" s="1"/>
+      <c r="DZ73" s="1"/>
+      <c r="EA73" s="1"/>
+      <c r="EB73" s="1"/>
+      <c r="EC73" s="1"/>
+      <c r="ED73" s="1"/>
+      <c r="EE73" s="1"/>
+      <c r="EF73" s="1"/>
+      <c r="EG73" s="1"/>
+      <c r="EH73" s="1"/>
+      <c r="EI73" s="1"/>
+      <c r="EJ73" s="1"/>
+      <c r="EK73" s="1"/>
+      <c r="EL73" s="1"/>
+      <c r="EM73" s="1"/>
+      <c r="EN73" s="1"/>
+      <c r="EO73" s="1"/>
+      <c r="EP73" s="1"/>
+      <c r="EQ73" s="1"/>
+      <c r="ER73" s="1"/>
+      <c r="ES73" s="1"/>
+      <c r="ET73" s="1"/>
+      <c r="EU73" s="1"/>
+      <c r="EV73" s="1"/>
+      <c r="EW73" s="1"/>
+      <c r="EX73" s="1"/>
+      <c r="EY73" s="1"/>
+      <c r="EZ73" s="1"/>
+      <c r="FA73" s="1"/>
+      <c r="FB73" s="1"/>
+      <c r="FC73" s="1"/>
+      <c r="FD73" s="1"/>
+      <c r="FE73" s="1"/>
+      <c r="FF73" s="1"/>
+      <c r="FG73" s="1"/>
+      <c r="FH73" s="1"/>
+      <c r="FI73" s="1"/>
+      <c r="FJ73" s="1"/>
+      <c r="FK73" s="1"/>
+      <c r="FL73" s="1"/>
+      <c r="FM73" s="1"/>
+      <c r="FN73" s="1"/>
+      <c r="FO73" s="1"/>
+      <c r="FP73" s="1"/>
+      <c r="FQ73" s="1"/>
+      <c r="FR73" s="1"/>
+      <c r="FS73" s="1"/>
+      <c r="FT73" s="1"/>
+      <c r="FU73" s="1"/>
+      <c r="FV73" s="1"/>
+      <c r="FW73" s="1"/>
+      <c r="FX73" s="1"/>
+      <c r="FY73" s="1"/>
+      <c r="FZ73" s="1"/>
+      <c r="GA73" s="1"/>
+      <c r="GB73" s="1"/>
+      <c r="GC73" s="1"/>
+      <c r="GD73" s="1"/>
+      <c r="GE73" s="1"/>
+      <c r="GF73" s="1"/>
+      <c r="GG73" s="1"/>
+      <c r="GH73" s="1"/>
+      <c r="GI73" s="1"/>
+      <c r="GJ73" s="1"/>
+      <c r="GK73" s="1"/>
+      <c r="GL73" s="1"/>
+      <c r="GM73" s="1"/>
+      <c r="GN73" s="1"/>
+      <c r="GO73" s="1"/>
+      <c r="GP73" s="1"/>
+      <c r="GQ73" s="1"/>
+      <c r="GR73" s="1"/>
+      <c r="GS73" s="1"/>
+      <c r="GT73" s="1"/>
+      <c r="GU73" s="1"/>
+      <c r="GV73" s="1"/>
+      <c r="GW73" s="1"/>
+      <c r="GX73" s="1"/>
+      <c r="GY73" s="1"/>
+      <c r="GZ73" s="1"/>
+      <c r="HA73" s="1"/>
+      <c r="HB73" s="1"/>
+      <c r="HC73" s="1"/>
+      <c r="HD73" s="1"/>
+      <c r="HE73" s="1"/>
+      <c r="HF73" s="1"/>
+      <c r="HG73" s="1"/>
+      <c r="HH73" s="1"/>
+      <c r="HI73" s="1"/>
+      <c r="HJ73" s="1"/>
+      <c r="HK73" s="1"/>
+      <c r="HL73" s="1"/>
+      <c r="HM73" s="1"/>
+      <c r="HN73" s="1"/>
+      <c r="HO73" s="1"/>
+      <c r="HP73" s="1"/>
+      <c r="HQ73" s="1"/>
+      <c r="HR73" s="1"/>
+      <c r="HS73" s="1"/>
+      <c r="HT73" s="1"/>
+      <c r="HU73" s="1"/>
+      <c r="HV73" s="1"/>
+      <c r="HW73" s="1"/>
+      <c r="HX73" s="1"/>
+      <c r="HY73" s="1"/>
+      <c r="HZ73" s="1"/>
+      <c r="IA73" s="1"/>
+      <c r="IB73" s="1"/>
+      <c r="IC73" s="1"/>
+      <c r="ID73" s="1"/>
+      <c r="IE73" s="1"/>
+      <c r="IF73" s="1"/>
+      <c r="IG73" s="1"/>
+      <c r="IH73" s="1"/>
+      <c r="II73" s="1"/>
+      <c r="IJ73" s="1"/>
+      <c r="IK73" s="1"/>
+      <c r="IL73" s="1"/>
+      <c r="IM73" s="1"/>
+      <c r="IN73" s="1"/>
+      <c r="IO73" s="1"/>
+      <c r="IP73" s="1"/>
+      <c r="IQ73" s="1"/>
+      <c r="IR73" s="1"/>
+      <c r="IS73" s="1"/>
+      <c r="IT73" s="1"/>
+      <c r="IU73" s="1"/>
+      <c r="IV73" s="1"/>
+      <c r="IW73" s="1"/>
+      <c r="IX73" s="1"/>
     </row>
     <row r="74" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="28"/>
-      <c r="O74" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="16"/>
-      <c r="R74" s="26"/>
-      <c r="S74" s="16"/>
-      <c r="T74" s="23"/>
-      <c r="U74" s="16"/>
-      <c r="V74" s="16"/>
-      <c r="W74" s="16"/>
-      <c r="X74" s="16"/>
-      <c r="Y74" s="16"/>
-      <c r="Z74" s="16"/>
-      <c r="AA74" s="16"/>
-      <c r="AB74" s="16"/>
-      <c r="AC74" s="16"/>
-      <c r="AD74" s="16"/>
-      <c r="AE74" s="16"/>
-      <c r="AF74" s="16"/>
-      <c r="AG74" s="16"/>
-      <c r="AH74" s="16"/>
-      <c r="AI74" s="16"/>
-      <c r="AJ74" s="16"/>
-      <c r="AK74" s="16"/>
-      <c r="AL74" s="16"/>
-      <c r="AM74" s="16"/>
-      <c r="AN74" s="16"/>
-      <c r="AO74" s="16"/>
-      <c r="AP74" s="16"/>
-      <c r="AQ74" s="16"/>
-      <c r="AR74" s="16"/>
-      <c r="AS74" s="19"/>
+      <c r="O74" s="36"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="13"/>
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+      <c r="X74" s="13"/>
+      <c r="Y74" s="13"/>
+      <c r="Z74" s="13"/>
+      <c r="AA74" s="13"/>
+      <c r="AB74" s="13"/>
+      <c r="AC74" s="13"/>
+      <c r="AD74" s="13"/>
+      <c r="AE74" s="13"/>
+      <c r="AF74" s="13"/>
+      <c r="AG74" s="13"/>
+      <c r="AH74" s="13"/>
+      <c r="AI74" s="13"/>
+      <c r="AJ74" s="13"/>
+      <c r="AK74" s="13"/>
+      <c r="AL74" s="13"/>
+      <c r="AM74" s="13"/>
+      <c r="AN74" s="13"/>
+      <c r="AO74" s="13"/>
+      <c r="AP74" s="13"/>
+      <c r="AQ74" s="13"/>
+      <c r="AR74" s="13"/>
+      <c r="AS74" s="13"/>
       <c r="AT74" s="8"/>
     </row>
     <row r="75" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="28"/>
-      <c r="O75" s="41">
-        <v>7</v>
-      </c>
-      <c r="P75" s="13"/>
-      <c r="Q75" s="13"/>
+      <c r="O75" s="36"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
       <c r="R75" s="25"/>
-      <c r="S75" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT75" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="S75" s="20"/>
+      <c r="T75" s="43"/>
+      <c r="V75" s="20"/>
+      <c r="W75" s="20"/>
+      <c r="X75" s="20"/>
+      <c r="Y75" s="20"/>
+      <c r="Z75" s="20"/>
+      <c r="AA75" s="20"/>
+      <c r="AB75" s="20"/>
+      <c r="AC75" s="20"/>
+      <c r="AD75" s="20"/>
+      <c r="AE75" s="20"/>
+      <c r="AF75" s="20"/>
+      <c r="AG75" s="20"/>
+      <c r="AH75" s="20"/>
+      <c r="AI75" s="20"/>
+      <c r="AJ75" s="20"/>
+      <c r="AK75" s="20"/>
+      <c r="AL75" s="20"/>
+      <c r="AM75" s="20"/>
+      <c r="AN75" s="20"/>
+      <c r="AO75" s="20"/>
+      <c r="AP75" s="20"/>
+      <c r="AQ75" s="20"/>
+      <c r="AR75" s="20"/>
+      <c r="AS75" s="38"/>
+      <c r="AT75" s="8"/>
     </row>
     <row r="76" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="28"/>
-      <c r="O76" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="P76" s="13"/>
-      <c r="Q76" s="13"/>
-      <c r="R76" s="25"/>
+      <c r="O76" s="40"/>
+      <c r="P76" s="16"/>
+      <c r="Q76" s="16"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="16"/>
+      <c r="T76" s="23"/>
+      <c r="V76" s="16"/>
+      <c r="W76" s="16"/>
+      <c r="X76" s="16"/>
+      <c r="Y76" s="16"/>
+      <c r="Z76" s="16"/>
+      <c r="AA76" s="16"/>
+      <c r="AB76" s="16"/>
+      <c r="AC76" s="16"/>
+      <c r="AD76" s="16"/>
+      <c r="AE76" s="16"/>
+      <c r="AF76" s="16"/>
+      <c r="AG76" s="16"/>
+      <c r="AH76" s="16"/>
+      <c r="AI76" s="16"/>
+      <c r="AJ76" s="16"/>
+      <c r="AK76" s="16"/>
+      <c r="AL76" s="16"/>
+      <c r="AM76" s="16"/>
+      <c r="AN76" s="16"/>
+      <c r="AO76" s="16"/>
+      <c r="AP76" s="16"/>
+      <c r="AQ76" s="16"/>
+      <c r="AR76" s="16"/>
+      <c r="AS76" s="19"/>
       <c r="AT76" s="8"/>
     </row>
     <row r="77" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="28"/>
-      <c r="O77" s="40"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="16"/>
-      <c r="R77" s="26"/>
-      <c r="S77" s="49"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="16"/>
-      <c r="W77" s="16"/>
-      <c r="X77" s="16"/>
-      <c r="Y77" s="16"/>
-      <c r="Z77" s="16"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="22"/>
-      <c r="AC77" s="22"/>
-      <c r="AD77" s="22"/>
-      <c r="AE77" s="22"/>
-      <c r="AF77" s="22"/>
-      <c r="AG77" s="22"/>
-      <c r="AH77" s="22"/>
-      <c r="AI77" s="22"/>
-      <c r="AJ77" s="22"/>
-      <c r="AK77" s="22"/>
-      <c r="AL77" s="22"/>
-      <c r="AM77" s="22"/>
-      <c r="AN77" s="22"/>
-      <c r="AO77" s="22"/>
-      <c r="AP77" s="22"/>
-      <c r="AQ77" s="22"/>
-      <c r="AR77" s="16"/>
-      <c r="AS77" s="19"/>
+      <c r="O77" s="41">
+        <v>6</v>
+      </c>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="25"/>
+      <c r="S77" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="T77" s="43"/>
+      <c r="U77" s="46"/>
+      <c r="V77" s="20"/>
+      <c r="W77" s="20"/>
+      <c r="X77" s="20"/>
+      <c r="Y77" s="20"/>
+      <c r="Z77" s="20"/>
+      <c r="AA77" s="20"/>
+      <c r="AB77" s="20"/>
+      <c r="AC77" s="20"/>
+      <c r="AD77" s="20"/>
+      <c r="AE77" s="20"/>
+      <c r="AF77" s="20"/>
+      <c r="AG77" s="20"/>
+      <c r="AH77" s="20"/>
+      <c r="AI77" s="20"/>
+      <c r="AJ77" s="20"/>
+      <c r="AK77" s="20"/>
+      <c r="AL77" s="20"/>
+      <c r="AM77" s="20"/>
+      <c r="AN77" s="20"/>
+      <c r="AO77" s="20"/>
+      <c r="AP77" s="20"/>
+      <c r="AQ77" s="20"/>
+      <c r="AR77" s="20"/>
+      <c r="AS77" s="20"/>
       <c r="AT77" s="8"/>
     </row>
     <row r="78" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="28"/>
-      <c r="O78" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="P78" s="13"/>
-      <c r="Q78" s="13"/>
+      <c r="O78" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="P78" s="20"/>
+      <c r="Q78" s="20"/>
       <c r="R78" s="25"/>
-      <c r="S78" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="X78" s="33"/>
-      <c r="Y78" s="33"/>
-      <c r="Z78" s="33"/>
-      <c r="AA78" s="33"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="U78" s="20"/>
+      <c r="V78" s="20"/>
+      <c r="W78" s="20"/>
+      <c r="X78" s="20"/>
+      <c r="Y78" s="20"/>
+      <c r="Z78" s="20"/>
+      <c r="AA78" s="20"/>
       <c r="AB78" s="20"/>
       <c r="AC78" s="20"/>
       <c r="AD78" s="20"/>
@@ -22056,102 +23251,241 @@
       <c r="AO78" s="20"/>
       <c r="AP78" s="20"/>
       <c r="AQ78" s="20"/>
+      <c r="AR78" s="20"/>
+      <c r="AS78" s="20"/>
       <c r="AT78" s="8"/>
     </row>
     <row r="79" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="28"/>
-      <c r="O79" s="36"/>
-      <c r="P79" s="13"/>
-      <c r="Q79" s="13"/>
-      <c r="R79" s="25"/>
-      <c r="T79" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="O79" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="P79" s="16"/>
+      <c r="Q79" s="16"/>
+      <c r="R79" s="26"/>
+      <c r="S79" s="16"/>
+      <c r="T79" s="23"/>
+      <c r="U79" s="16"/>
+      <c r="V79" s="16"/>
+      <c r="W79" s="16"/>
+      <c r="X79" s="16"/>
+      <c r="Y79" s="16"/>
+      <c r="Z79" s="16"/>
+      <c r="AA79" s="16"/>
+      <c r="AB79" s="16"/>
+      <c r="AC79" s="16"/>
+      <c r="AD79" s="16"/>
+      <c r="AE79" s="16"/>
+      <c r="AF79" s="16"/>
+      <c r="AG79" s="16"/>
+      <c r="AH79" s="16"/>
+      <c r="AI79" s="16"/>
+      <c r="AJ79" s="16"/>
+      <c r="AK79" s="16"/>
+      <c r="AL79" s="16"/>
+      <c r="AM79" s="16"/>
+      <c r="AN79" s="16"/>
+      <c r="AO79" s="16"/>
+      <c r="AP79" s="16"/>
+      <c r="AQ79" s="16"/>
+      <c r="AR79" s="16"/>
+      <c r="AS79" s="19"/>
       <c r="AT79" s="8"/>
     </row>
     <row r="80" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="28"/>
-      <c r="O80" s="36"/>
+      <c r="O80" s="41">
+        <v>7</v>
+      </c>
       <c r="P80" s="13"/>
       <c r="Q80" s="13"/>
       <c r="R80" s="25"/>
-      <c r="T80" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AT80" s="8"/>
+      <c r="S80" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT80" s="8" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="28"/>
-      <c r="O81" s="36"/>
+      <c r="O81" s="36" t="s">
+        <v>127</v>
+      </c>
       <c r="P81" s="13"/>
       <c r="Q81" s="13"/>
       <c r="R81" s="25"/>
-      <c r="S81" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP81" s="33"/>
       <c r="AT81" s="8"/>
     </row>
     <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="33"/>
-      <c r="O82" s="36"/>
-      <c r="P82" s="13"/>
-      <c r="Q82" s="13"/>
-      <c r="R82" s="25"/>
-      <c r="T82" s="11" t="s">
-        <v>62</v>
-      </c>
+      <c r="A82" s="28"/>
+      <c r="O82" s="40"/>
+      <c r="P82" s="16"/>
+      <c r="Q82" s="16"/>
+      <c r="R82" s="26"/>
+      <c r="S82" s="49"/>
+      <c r="T82" s="22"/>
+      <c r="U82" s="22"/>
+      <c r="V82" s="16"/>
+      <c r="W82" s="16"/>
+      <c r="X82" s="16"/>
+      <c r="Y82" s="16"/>
+      <c r="Z82" s="16"/>
+      <c r="AA82" s="16"/>
+      <c r="AB82" s="22"/>
+      <c r="AC82" s="22"/>
+      <c r="AD82" s="22"/>
+      <c r="AE82" s="22"/>
+      <c r="AF82" s="22"/>
+      <c r="AG82" s="22"/>
+      <c r="AH82" s="22"/>
+      <c r="AI82" s="22"/>
+      <c r="AJ82" s="22"/>
+      <c r="AK82" s="22"/>
+      <c r="AL82" s="22"/>
+      <c r="AM82" s="22"/>
+      <c r="AN82" s="22"/>
+      <c r="AO82" s="22"/>
+      <c r="AP82" s="22"/>
+      <c r="AQ82" s="22"/>
+      <c r="AR82" s="16"/>
+      <c r="AS82" s="19"/>
       <c r="AT82" s="8"/>
     </row>
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="33"/>
-      <c r="O83" s="36"/>
+      <c r="A83" s="28"/>
+      <c r="O83" s="42" t="s">
+        <v>53</v>
+      </c>
       <c r="P83" s="13"/>
       <c r="Q83" s="13"/>
       <c r="R83" s="25"/>
-      <c r="T83" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="S83" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X83" s="33"/>
+      <c r="Y83" s="33"/>
+      <c r="Z83" s="33"/>
+      <c r="AA83" s="33"/>
+      <c r="AB83" s="20"/>
+      <c r="AC83" s="20"/>
+      <c r="AD83" s="20"/>
+      <c r="AE83" s="20"/>
+      <c r="AF83" s="20"/>
+      <c r="AG83" s="20"/>
+      <c r="AH83" s="20"/>
+      <c r="AI83" s="20"/>
+      <c r="AJ83" s="20"/>
+      <c r="AK83" s="20"/>
+      <c r="AL83" s="20"/>
+      <c r="AM83" s="20"/>
+      <c r="AN83" s="20"/>
+      <c r="AO83" s="20"/>
+      <c r="AP83" s="20"/>
+      <c r="AQ83" s="20"/>
       <c r="AT83" s="8"/>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="28"/>
       <c r="O84" s="36"/>
       <c r="P84" s="13"/>
       <c r="Q84" s="13"/>
       <c r="R84" s="25"/>
-      <c r="S84" s="2" t="s">
-        <v>57</v>
+      <c r="T84" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="AT84" s="8"/>
     </row>
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="28"/>
       <c r="O85" s="36"/>
       <c r="P85" s="13"/>
       <c r="Q85" s="13"/>
       <c r="R85" s="25"/>
-      <c r="T85" s="11" t="s">
-        <v>62</v>
+      <c r="T85" s="103" t="s">
+        <v>60</v>
       </c>
       <c r="AT85" s="8"/>
     </row>
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="28"/>
       <c r="O86" s="36"/>
       <c r="P86" s="13"/>
       <c r="Q86" s="13"/>
       <c r="R86" s="25"/>
-      <c r="T86" s="2" t="s">
+      <c r="S86" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP86" s="33"/>
+      <c r="AT86" s="8"/>
+    </row>
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="33"/>
+      <c r="O87" s="36"/>
+      <c r="P87" s="13"/>
+      <c r="Q87" s="13"/>
+      <c r="R87" s="25"/>
+      <c r="T87" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT87" s="8"/>
+    </row>
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="33"/>
+      <c r="O88" s="36"/>
+      <c r="P88" s="13"/>
+      <c r="Q88" s="13"/>
+      <c r="R88" s="25"/>
+      <c r="T88" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="AT86" s="8"/>
+      <c r="AT88" s="8"/>
+    </row>
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O89" s="36"/>
+      <c r="P89" s="13"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="25"/>
+      <c r="S89" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT89" s="8"/>
+    </row>
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O90" s="36"/>
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="25"/>
+      <c r="T90" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT90" s="8"/>
+    </row>
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O91" s="36"/>
+      <c r="P91" s="13"/>
+      <c r="Q91" s="13"/>
+      <c r="R91" s="25"/>
+      <c r="T91" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="AT91" s="8"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="65">
+  <mergeCells count="69">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:O9"/>
     <mergeCell ref="P9:AD9"/>
     <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="AT20:BI20"/>
+    <mergeCell ref="AE13:BI13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:O14"/>
+    <mergeCell ref="P14:AD14"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:O12"/>
+    <mergeCell ref="P12:AD12"/>
+    <mergeCell ref="AE12:BI12"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D10:O10"/>
     <mergeCell ref="P10:AD10"/>
@@ -22160,9 +23494,6 @@
     <mergeCell ref="D11:O11"/>
     <mergeCell ref="P11:AD11"/>
     <mergeCell ref="AE11:BI11"/>
-    <mergeCell ref="S20:AS20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="AE16:BI16"/>
     <mergeCell ref="AE8:BI8"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:O7"/>
@@ -22185,9 +23516,9 @@
     <mergeCell ref="A1:L2"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:O16"/>
-    <mergeCell ref="P16:AD16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:O17"/>
+    <mergeCell ref="P17:AD17"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
     <mergeCell ref="A5:F5"/>
@@ -22195,30 +23526,30 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:O8"/>
     <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:O12"/>
-    <mergeCell ref="P12:AD12"/>
-    <mergeCell ref="AE12:BI12"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:O13"/>
     <mergeCell ref="P13:AD13"/>
-    <mergeCell ref="AE13:BI13"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:O14"/>
-    <mergeCell ref="P14:AD14"/>
     <mergeCell ref="AE14:BI14"/>
+    <mergeCell ref="A21:N21"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:O15"/>
     <mergeCell ref="P15:AD15"/>
     <mergeCell ref="AE15:BI15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:O16"/>
+    <mergeCell ref="P16:AD16"/>
+    <mergeCell ref="AE16:BI16"/>
+    <mergeCell ref="AT21:BI21"/>
+    <mergeCell ref="S21:AS21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="AE17:BI17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A17:A18" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A18:A19" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"引数,戻り値,例外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A8:A16" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A8:A17" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"引数,戻り値,例外,変数"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22323,19 +23654,19 @@
       <c r="R10" s="99"/>
     </row>
     <row r="11" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="142" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="143"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="143"/>
-      <c r="M11" s="143"/>
-      <c r="N11" s="143"/>
-      <c r="O11" s="144"/>
+      <c r="E11" s="127" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="129"/>
       <c r="P11" s="99"/>
       <c r="Q11" s="99"/>
       <c r="R11" s="99"/>
@@ -22378,11 +23709,11 @@
       <c r="P12" s="99"/>
       <c r="Q12" s="99"/>
       <c r="R12" s="99"/>
-      <c r="T12" s="126" t="s">
-        <v>100</v>
+      <c r="T12" s="130" t="s">
+        <v>98</v>
       </c>
       <c r="U12" s="85" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V12" s="86"/>
       <c r="W12" s="87"/>
@@ -22390,107 +23721,107 @@
       <c r="Y12" s="88"/>
     </row>
     <row r="13" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="129" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>97</v>
+      <c r="B13" s="133" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="136" t="s">
+        <v>95</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E13" s="74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H13" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I13" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J13" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L13" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M13" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N13" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O13" s="75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P13" s="99"/>
       <c r="Q13" s="99"/>
       <c r="R13" s="99"/>
-      <c r="T13" s="127"/>
+      <c r="T13" s="131"/>
       <c r="U13" s="89"/>
       <c r="V13" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W13" s="58"/>
       <c r="X13" s="58"/>
       <c r="Y13" s="90"/>
     </row>
     <row r="14" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="130"/>
-      <c r="C14" s="133"/>
+      <c r="B14" s="134"/>
+      <c r="C14" s="137"/>
       <c r="D14" s="67" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H14" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I14" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J14" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K14" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L14" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M14" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N14" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O14" s="75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P14" s="99"/>
       <c r="Q14" s="99"/>
       <c r="R14" s="99"/>
-      <c r="T14" s="127" t="s">
-        <v>101</v>
+      <c r="T14" s="131" t="s">
+        <v>99</v>
       </c>
       <c r="U14" s="91" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="V14" s="55"/>
       <c r="W14" s="55"/>
@@ -22498,151 +23829,151 @@
       <c r="Y14" s="92"/>
     </row>
     <row r="15" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="130"/>
-      <c r="C15" s="134" t="s">
-        <v>132</v>
+      <c r="B15" s="134"/>
+      <c r="C15" s="138" t="s">
+        <v>128</v>
       </c>
       <c r="D15" s="67" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E15" s="74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H15" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I15" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J15" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K15" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L15" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M15" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N15" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O15" s="75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P15" s="99"/>
       <c r="R15" s="99"/>
-      <c r="T15" s="127"/>
+      <c r="T15" s="131"/>
       <c r="U15" s="93"/>
       <c r="V15" s="20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="W15" s="20"/>
       <c r="X15" s="54"/>
       <c r="Y15" s="94"/>
     </row>
     <row r="16" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="130"/>
-      <c r="C16" s="132"/>
+      <c r="B16" s="134"/>
+      <c r="C16" s="136"/>
       <c r="D16" s="67" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E16" s="76" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G16" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H16" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I16" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J16" s="60" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K16" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L16" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M16" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N16" s="61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O16" s="75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P16" s="99"/>
       <c r="R16" s="99"/>
-      <c r="T16" s="127"/>
+      <c r="T16" s="131"/>
       <c r="U16" s="95"/>
       <c r="V16" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W16" s="57"/>
       <c r="X16" s="58"/>
       <c r="Y16" s="90"/>
     </row>
     <row r="17" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="131"/>
-      <c r="C17" s="135"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="139"/>
       <c r="D17" s="102" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F17" s="63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G17" s="64" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J17" s="64" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K17" s="63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L17" s="63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M17" s="63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N17" s="63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O17" s="78" t="s">
-        <v>106</v>
-      </c>
-      <c r="T17" s="127" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="T17" s="131" t="s">
+        <v>100</v>
       </c>
       <c r="U17" s="91" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="V17" s="59"/>
       <c r="W17" s="56"/>
@@ -22650,15 +23981,15 @@
       <c r="Y17" s="92"/>
     </row>
     <row r="18" spans="2:25" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="136" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="137"/>
+      <c r="B18" s="140" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="141"/>
       <c r="D18" s="69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F18" s="62"/>
       <c r="G18" s="62"/>
@@ -22672,27 +24003,27 @@
       <c r="O18" s="80"/>
       <c r="P18" s="99"/>
       <c r="R18" s="99"/>
-      <c r="T18" s="127"/>
+      <c r="T18" s="131"/>
       <c r="U18" s="93"/>
       <c r="V18" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="W18" s="54"/>
       <c r="X18" s="54"/>
       <c r="Y18" s="94"/>
     </row>
     <row r="19" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="138"/>
-      <c r="C19" s="139"/>
+      <c r="B19" s="142"/>
+      <c r="C19" s="143"/>
       <c r="D19" s="68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E19" s="76"/>
       <c r="F19" s="60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G19" s="60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H19" s="60"/>
       <c r="I19" s="60"/>
@@ -22704,26 +24035,26 @@
       <c r="O19" s="75"/>
       <c r="P19" s="99"/>
       <c r="R19" s="99"/>
-      <c r="T19" s="127"/>
+      <c r="T19" s="131"/>
       <c r="U19" s="95"/>
       <c r="V19" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W19" s="58"/>
       <c r="X19" s="58"/>
       <c r="Y19" s="90"/>
     </row>
     <row r="20" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="138"/>
-      <c r="C20" s="139"/>
+      <c r="B20" s="142"/>
+      <c r="C20" s="143"/>
       <c r="D20" s="68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E20" s="76"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
       <c r="H20" s="60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I20" s="60"/>
       <c r="J20" s="60"/>
@@ -22735,11 +24066,11 @@
       <c r="P20" s="99"/>
       <c r="Q20" s="99"/>
       <c r="R20" s="99"/>
-      <c r="T20" s="127" t="s">
-        <v>103</v>
+      <c r="T20" s="131" t="s">
+        <v>101</v>
       </c>
       <c r="U20" s="91" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="V20" s="55"/>
       <c r="W20" s="55"/>
@@ -22747,20 +24078,20 @@
       <c r="Y20" s="92"/>
     </row>
     <row r="21" spans="2:25" ht="15" x14ac:dyDescent="0.3">
-      <c r="B21" s="138"/>
-      <c r="C21" s="139"/>
+      <c r="B21" s="142"/>
+      <c r="C21" s="143"/>
       <c r="D21" s="68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E21" s="76"/>
       <c r="F21" s="60"/>
       <c r="G21" s="60"/>
       <c r="H21" s="60"/>
       <c r="I21" s="60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J21" s="60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K21" s="60"/>
       <c r="L21" s="60"/>
@@ -22770,20 +24101,20 @@
       <c r="P21" s="99"/>
       <c r="Q21" s="99"/>
       <c r="R21" s="99"/>
-      <c r="T21" s="127"/>
+      <c r="T21" s="131"/>
       <c r="U21" s="93"/>
       <c r="V21" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="W21" s="20"/>
       <c r="X21" s="54"/>
       <c r="Y21" s="94"/>
     </row>
     <row r="22" spans="2:25" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="145"/>
       <c r="D22" s="70" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E22" s="81"/>
       <c r="F22" s="82"/>
@@ -22792,27 +24123,27 @@
       <c r="I22" s="82"/>
       <c r="J22" s="82"/>
       <c r="K22" s="83" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L22" s="83" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M22" s="83" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N22" s="83" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O22" s="84" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P22" s="99"/>
       <c r="Q22" s="99"/>
       <c r="R22" s="99"/>
-      <c r="T22" s="128"/>
+      <c r="T22" s="132"/>
       <c r="U22" s="96"/>
       <c r="V22" s="97" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W22" s="97"/>
       <c r="X22" s="65"/>
@@ -22826,15 +24157,15 @@
     <row r="26" spans="2:25" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="B18:C22"/>
     <mergeCell ref="E11:O11"/>
     <mergeCell ref="T12:T13"/>
     <mergeCell ref="T14:T16"/>
     <mergeCell ref="T17:T19"/>
     <mergeCell ref="T20:T22"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="B18:C22"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
